--- a/data/corpus/HVB_004_parallel.xlsx
+++ b/data/corpus/HVB_004_parallel.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C997"/>
+  <dimension ref="A1:C998"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,7 +679,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>卯脆油傳荒唐。杏貽玄鳥生商悟也</t>
+          <t>卯脆油傳荒唐。杏貽玄鳥生商悟也。</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>雄王都於州峯。意己白鶴合淵泥江</t>
+          <t>雄王都於州峯。意己白鶴合淵泥江，</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mưa tuôn gió thổi mịt mù, Ào ào rừng nọ, ùù núi kia.</t>
+          <t>Mưa tuôn gió thổi mịt mù,</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>歲滄奄啼剝誓。告影沒，化術蓬州</t>
+          <t>歲滄奄啼剝誓。告影沒，化術蓬州。</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>沒調父道響危，耀昴唐帝難齊報王</t>
+          <t>沒調父道響危，耀昴唐帝難齊報王。</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>王恢邴令將臣。臨娘挾瀝塘塵沒方</t>
+          <t>王恢邴令將臣。臨娘挾瀝塘塵沒方。</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>術陽運濺業茲。鈴界國難外界敵人</t>
+          <t>術陽運濺業兹。鈴界國難外界敵人</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Kể từ Triệu lịch kỷ niên, Năm ngoài chín chục, ngôi truyền năm vua. Trách ai gây việc tranh đua, Vắn dài vận nước, được thua cơ trời.</t>
+          <t>Kể từ Triệu lịch kỷ niên, Năm ngoài chín chục, ngôi truyền năm vua.</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Giao Châu mới thuộc nước người, Ấy về Tây Hán là đời Nguyên Phong.</t>
+          <t>Trách ai gây việc tranh đua, Vắn dài vận nước, được thua cơ trời.</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bản đồ vào sách hỗn đồng, Đất chia chín quận, quan phong thú thần.</t>
+          <t>Giao Châu mới thuộc nước người, Ấy về Tây Hán là đời Nguyên Phong.</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Đầu sai Thạch Đái trị dân, Cầm quyền tiết việt giữ phần phong cương.</t>
+          <t>Bản đồ vào sách hỗn đồng, Đất chia chín quận, quan phong thú thần.</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Tuần tuyên mới có Tích Quang, Dạy dân lễ nghĩa theo đường hoa phong.</t>
+          <t>Đầu sai Thạch Đái trị dân, Cầm quyền tiết việt giữ phần phong cương.</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Đường ca lâu đã vắng lời, Đến như Tô Định lại người chí hung.</t>
+          <t>Tuần tuyên mới có Tích Quang, Dạy dân lễ nghĩa theo đường hoa phong.</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bà Trưng quê ở Châu Phong, Giận người tham bạo, thù chồng chẳng quên.</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Chị em nặng một lời nguyền, Phất cờ nương tử thay quyền tướng quân.</t>
+          <t>Nhâm Diên khuyên việc canh nông, Đổi nghề ngư liệp về trong khuê điền.</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ngàn Tây nổi áng phong trần, Ầm ầm binh mã xuống gần Long Biên.</t>
+          <t>Sính nghi lại giúp bổng tiền, Khiến người bần khổ thoả nguyền thất gia.</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Hồng quần nhẹ bức chinh yên, Đuổi ngay Tô Định, dẹp tan biên thành.</t>
+          <t>Văn phong nhức dấy gần xa, Tự hai hiền thú ấy là khai tiên.</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Đô kỳ đóng cõi Mê Linh, Lĩnh Nam riêng một triều đình nước ta.</t>
+          <t>Luân hồi trăm có dư niên, Trải qua Đông Hán thừa tuyên mấy người.</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ba thu gánh vác sơn hà, Một là báo phục, hai là bá vương.</t>
+          <t>Đường ca lâu đã vắng lời, Đến như Tô Định lại người chí hung.</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Uy thanh động đến Bắc phương, Hán sai Mã Viện lên đường tiến công.</t>
+          <t>Bà Trưng quê ở Châu Phong, Giận người tham bạo, thù chồng chẳng quên.</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Hồ Tây đua sức vẫy vùng, Nữ nhi chống với anh hùng được nao?</t>
+          <t>Chị em nặng một lời nguyền, Phất cờ nương tử thay quyền tướng quân.</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Cấm Khê đến lúc hiểm nghèo, Chị em thất thế cũng liều với sông.</t>
+          <t>Ngàn Tây nổi áng phong trần, Ầm ầm binh mã xuống gần Long Biên.</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Phục Ba mới dựng cột đồng, Ải quan truyền dấu biên công cõi ngoài.</t>
+          <t>Hồng quần nhẹ bức chinh yên, Đuổi ngay Tô Định, dẹp tan biên thành.</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Trưng Vương vắng mặt còn ai? Đi về thay đổi mặc người Hán quan.</t>
+          <t>Đô kỳ đóng cõi Mê Linh, Lĩnh Nam riêng một triều đình nước ta.</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Trải Minh, Chương đến Hiếu, An, Tuần lương đã ít, tham tàn thiếu đâu.</t>
+          <t>Ba thu gánh vác sơn hà, Một là báo phục, hai là bá vương.</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Mới từ Thuận Đế về sau, Đặt quan thứ sử thuộc vào chức phương.</t>
+          <t>Uy thanh động đến Bắc phương, Hán sai Mã Viện lên đường tiến công.</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Kìa như Phàn Diễn, Giả Xương, Chu Ngu, Lưu Tảo dung thường kể chi.</t>
+          <t>Hồ Tây đua sức vẫy vùng, Nữ nhi chống với anh hùng được nao?</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Trương Kiều thành tín phủ tuy, Chúc Lương uy đức man di cũng gần.</t>
+          <t>Cấm Khê đến lúc hiểm nghèo, Chị em thất thế cũng liều với sông.</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hạ Phương ân trạch ngấm nhuần, Một châu tiết việt hai lần thừa tuyên.</t>
+          <t>Phục Ba mới dựng cột đồng, Ải quan truyền dấu biên công cõi ngoài.</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Tuần lương lại có Mạnh Kiên, Khúc ca Giả Phủ vang miền trung châu.</t>
+          <t>Trưng Vương vắng mặt còn ai? Đi về thay đổi mặc người Hán quan.</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ba năm thăng trạc về chầu, Thổ quan Lý Tiến mới đầu Nam nhân.</t>
+          <t>Trải Minh, Chương đến Hiếu, An, Tuần lương đã ít, tham tàn thiếu đâu.</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sớ kêu: Ai chẳng vương thần, Sĩ đồ chi để xa gần khác nhau?</t>
+          <t>Mới từ Thuận Đế về sau, Đặt quan thứ sử thuộc vào chức phương.</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tình từ động đến thần lưu, Chiếu cho cống sĩ bổ châu huyện ngoài.</t>
+          <t>Kìa như Phàn Diễn, Giả Xương, Chu Ngu, Lưu Tảo dung thường kể chi.</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Lý Cầm chầu chực điện đài, Nhân khi Nguyên Đán kêu lời xa xôi.</t>
+          <t>Trương Kiều thành tín phủ tuy, Chúc Lương uy đức man di cũng gần.</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Rằng: Sao phủ tái hẹp hòi? Gió mưa để một cõi ngoài viêm phương. Tấm thành cũng thấu quân vương, Trung châu lại mới bổ sang hai người.</t>
+          <t>Hạ Phương ân trạch ngấm nhuần, Một châu tiết việt hai lần thừa tuyên.</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Nước Nam mấy kẻ nhân tài, Mới cùng người Hán chen vai từ rầy.</t>
+          <t>Tuần lương lại có Mạnh Kiên, Khúc ca Giả Phủ vang miền trung châu.</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Lửa lò Viêm Hán gần bay, Thế chia chân vạc nào hay cơ trời.</t>
+          <t>Ba năm thăng trạc về chầu, Thổ quan Lý Tiến mới đầu Nam nhân.</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tranh nhau ba nước ba nơi, Cầm quyền sinh sát mặc người phong cương.</t>
+          <t>Sớ kêu: Ai chẳng vương thần, Sĩ đồ chi để xa gần khác nhau?</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Nho lưu lại có Sĩ Vương, Khơi nguồn Thù Tứ mở đường lễ văn.</t>
+          <t>Tình từ động đến thần lưu, Chiếu cho cống sĩ bổ châu huyện ngoài.</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Phong tiêu rất mực thú thần, Sánh vai Đậu Mục, chen chân Triệu Đà.</t>
+          <t>Lý Cầm chầu chực điện đài, Nhân khi Nguyên Đán kêu lời xa xôi.</t>
         </is>
       </c>
     </row>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>浪輿覆載狹細，邁湄抵沒墜外炎方</t>
+          <t>浪輿覆載狹細，邁湄抵沒墜外炎方。</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Sĩ Huy nối giữ tước nha, Dứt đường thông hiếu gây ra cừu thù.</t>
+          <t>Rằng: Sao phủ tái hẹp hòi? Gió mưa để một cõi ngoài viêm phương.</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Cửa hiên phút bỗng hệ tù, Tiết mao lại thuộc về Ngô tử rầy.</t>
+          <t>Tấm thành cũng thấu quân vương, Trung châu lại mới bổ sang hai người.</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Binh qua trải bấy nhiêu ngày, Mới sai Lục Dận sang thay phiên thần.</t>
+          <t>Nước Nam mấy kẻ nhân tài, Mới cùng người Hán chen vai từ rầy.</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Anh hùng chán mặt phong trần, Nữ nhi lại cũng có lần cung đao.</t>
+          <t>Lửa lò Viêm Hán gần bay, Thế chia chân vạc nào hay cơ trời.</t>
         </is>
       </c>
     </row>
@@ -3705,12 +3705,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>爭燒臨滄臨尼矜權生殺默封疆</t>
+          <t>爭燒臨滄臨尼　矜權生殺默封疆</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Cửu Chân có ả Triệu Kiều, Vú dài ba thước tài cao muôn người.</t>
+          <t>Tranh nhau ba nước ba nơi, Cầm quyền sinh sát mặc người phong cương.</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Gặp cơn thảo muội cơ trời, Đem thân bồ liễu theo loài bồng lang.</t>
+          <t>Nho lưu lại có Sĩ Vương, Khơi nguồn Thù Tứ mở đường lễ văn.</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Đầu voi phất ngọn cờ vàng, Sơn thôn mấy cõi chiến trường xông pha.</t>
+          <t>Phong tiêu rất mực thú thần, Sánh vai Đậu Mục, chen chân Triệu Đà.</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Chông gai một cuộc quan hà, Dẫu khi chiến tử còn là hiển linh.</t>
+          <t>Sĩ Huy nối giữ tước nha, Dứt đường thông hiếu gây ra cừu thù.</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3773,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>謂軒，倖繫囚。節旄吏屬術吳自側</t>
+          <t>謂軒，倖繫囚。節旄吏屬術吳自側。</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Từ giờ Ngô lại tung hoành, Đặt làm Giao, Quảng hai thành mới phân.</t>
+          <t>Cửa hiên phút bỗng hệ tù, Tiết mao lại thuộc về Ngô tử rầy.</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tôn Tư rồi lại Đặng Tuân, Lữ Hưng, Dương Tắc mấy lần đổi thay.</t>
+          <t>Binh qua trải bấy nhiêu ngày, Mới sai Lục Dận sang thay phiên thần.</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Đồng Nguyên, Lưu Tuấn đua tay, Kẻ Ngô, người Tấn những ngày phân tranh.</t>
+          <t>Anh hùng chán mặt phong trần, Nữ nhi lại cũng có lần cung đao.</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Đào Hoàng nối dựng sứ tinh, Tân Xương, Cửu Đức, Vũ Bình lại chia.</t>
+          <t>Cửu Chân có ả Triệu Kiều, Vú dài ba thước tài cao muôn người.</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Mười năm chuyên mặt phiên ly, Uy gia bốn cõi, ân thuỳ một châu.</t>
+          <t>Gặp cơn thảo muội cơ trời, Đem thân bồ liễu theo loài bồng lang.</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Khi đi dân đã nguyện lưu, Khi già thương khóc khác nào từ thân.</t>
+          <t>Đầu voi phất ngọn cờ vàng, Sơn thôn mấy cõi chiến trường xông pha.</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Ngô công nối dấu phương trần, Hai mươi năm lẻ nhân tuần cũng yên.</t>
+          <t>Chông gai một cuộc quan hà, Dẫu khi chiến tử còn là hiển linh.</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Dân tình cảm kết đã bền, Tước nhà Cố Bật lại truyền Cố Tham.</t>
+          <t>Từ giờ Ngô lại tung hoành, Đặt làm Giao, Quảng hai thành mới phân.</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Dân tình khi đã chẳng kham, Dẫu là Cố Thọ muốn làm ai nghe.</t>
+          <t>Tôn Tư rồi lại Đặng Tuân, Lữ Hưng, Dương Tắc mấy lần đổi thay.</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Quận phù lại thuộc Đào Uy, Rồi ra Đào Thục, Đào Tuy kế truyền.</t>
+          <t>Đồng Nguyên, Lưu Tuấn đua tay, Kẻ Ngô, người Tấn những ngày phân tranh.</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Bốn đời tiết việt cầm quyền, Phiên binh muôn dặm trung hiền một môn.</t>
+          <t>Đào Hoàng nối dựng sứ tinh, Tân Xương, Cửu Đức, Vũ Bình lại chia.</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Tham tàn những lũ Vương Ôn, Binh qua nối gót nước non nhuộm trần.</t>
+          <t>Mười năm chuyên mặt phiên ly, Uy gia bốn cõi, ân thuỳ một châu.</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Tấn sai đô đốc tướng quân, Sĩ Hành là kẻ danh thần chức cao.</t>
+          <t>Khi đi dân đã nguyện lưu, Khi già thương khóc khác nào từ thân.</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Dẹp yên rồi lại về trào, Uy danh nào kém họ Đào thuở xưa.</t>
+          <t>Ngô công nối dấu phương trần, Hai mươi năm lẻ nhân tuần cũng yên.</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Nguyễn Phu tài trí có thừa, Phá năm mươi luỹ tảo trừ giặc Man.</t>
+          <t>Dân tình cảm kết đã bền, Tước nhà Cố Bật lại truyền Cố Tham.</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Châu Diên lại có thổ quan, Đỗ Công tên Viện dẹp đoàn Cửu Chân.</t>
+          <t>Dân tình khi đã chẳng kham, Dẫu là Cố Thọ muốn làm ai nghe.</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Tướng môn nối chức phiên thần, Con là Tuệ Độ thêm phần uy danh. Bổng riêng tán cấp cùng manh, Cơm rau áo vải như hình kẻ quê.</t>
+          <t>Quận phù lại thuộc Đào Uy, Rồi ra Đào Thục, Đào Tuy kế truyền.</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Dâm từ cấm thói ngu mê, Dựng nhà học hiệu giảng bề minh luân.</t>
+          <t>Bốn đời tiết việt cầm quyền, Phiên binh muôn dặm trung hiền một môn.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Ân uy ra khắp xa gần, Cửa thành đêm mở gió xuân một trời.</t>
+          <t>Tham tàn những lũ Vương Ôn, Binh qua nối gót nước non nhuộm trần.</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Hoằng Văn phủ ngữ cũng tài, Một nhà kế tập ba đời tuần lương.</t>
+          <t>Tấn sai đô đốc tướng quân, Sĩ Hành là kẻ danh thần chức cao.</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Đến triều Lưu Tống hưng vương, Hoà Chi, Nguyên Cán sai sang hội đồng.</t>
+          <t>Dẹp yên rồi lại về trào, Uy danh nào kém họ Đào thuở xưa.</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Đuổi Dương Mại, giết Phù Long, Khải ca một khúc tấu công về trào.</t>
+          <t>Nguyễn Phu tài trí có thừa, Phá năm mươi luỹ tảo trừ giặc Man.</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Gió thu cuốn bức chinh bào, Y thường một gánh qui thiều nhẹ không.</t>
+          <t>Châu Diên lại có thổ quan, Đỗ Công tên Viện dẹp đoàn Cửu Chân.</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Từ khi vắng kẻ chiết xung, Tràng Nhân, Lưu Mục tranh hùng mấy phen.</t>
+          <t>Tướng môn nối chức phiên thần, Con là Tuệ Độ thêm phần uy danh.</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Pháp Thừa cũng chức tuần tuyên, Những chăm việc sách để quyền lại ty.</t>
+          <t>Bổng riêng tán cấp cùng manh, Cơm rau áo vải như hình kẻ quê.</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Dưới màn có Phục Đăng Chi, Cướp quyền châu mục lộng uy triều đình.</t>
+          <t>Dâm từ cấm thói ngu mê, Dựng nhà học hiệu giảng bề minh luân.</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tề suy, Nguyên Khải tung hoành, Hùng phiên chiếm giữ cô thành một phương.</t>
+          <t>Ân uy ra khắp xa gần, Cửa thành đêm mở gió xuân một trời.</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bắc triều đã thuộc về Lương, Lại sai Lý Thốc chiêu hàng nẻo xa.</t>
+          <t>Hoằng Văn phủ ngữ cũng tài, Một nhà kế tập ba đời tuần lương.</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Giao Châu một giải sơn hà, Ái Châu lại mới đặt ra từ rầy.</t>
+          <t>Đến triều Lưu Tống hưng vương, Hoà Chi, Nguyên Cán sai sang hội đồng.</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Kể từ Ngô Tấn lại đây, Hai trăm mười bốn năm chầy cát phân.</t>
+          <t>Đuổi Dương Mại, giết Phù Long, Khải ca một khúc tấu công về trào.</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Cỏ cây chan chứa bụi trần, Thái bình mới có Lý Phần hưng vương.</t>
+          <t>Gió thu cuốn bức chinh bào, Y thường một gánh qui thiều nhẹ không.</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Vốn xưa nhập sĩ nước Lương, Binh qua gặp lúc phân nhương lại về.</t>
+          <t>Từ khi vắng kẻ chiết xung, Tràng Nhân, Lưu Mục tranh hùng mấy phen.</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Cửu dân đã quyết lời thề, Văn thần, vũ tướng ứng kỳ đều ra.</t>
+          <t>Pháp Thừa cũng chức tuần tuyên, Những chăm việc sách để quyền lại ty.</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Tiêu Tư nghe gió chạy xa, Đông tây muôn dặm quan hà quét thanh.</t>
+          <t>Dưới màn có Phục Đăng Chi, Cướp quyền châu mục lộng uy triều đình.</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Vạn Xuân mới đặt quốc danh, Cải nguyên Thiên Đức, đô thành Long Biên.</t>
+          <t>Tề suy, Nguyên Khải tung hoành, Hùng phiên chiếm giữ cô thành một phương.</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Lịch đồ vừa mới kỷ niên, Hưng vương khí tượng cũng nên một đời.</t>
+          <t>Bắc triều đã thuộc về Lương, Lại sai Lý Thốc chiêu hàng nẻo xa.</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Quân Lương đâu đã đến ngoài, Bá Tiên là tướng đeo bài chuyên chinh.</t>
+          <t>Giao Châu một giải sơn hà, Ái Châu lại mới đặt ra từ rầy.</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Cùng nhau mấy trận giao binh, Thất cơ Tô Lịch, Gia Ninh đôi đường.</t>
+          <t>Kể từ Ngô Tấn lại đây, Hai trăm mười bốn năm chầy cát phân.</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Thu quân vào ở Tân Xương, Để cho Quang Phục chống Lương mặt ngoài.</t>
+          <t>Cỏ cây chan chứa bụi trần, Thái bình mới có Lý Phần hưng vương.</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Mới hay nhật phụ mộc lai, Sấm văn trước đã an bài những khi.</t>
+          <t>Vốn xưa nhập sĩ nước Lương, Binh qua gặp lúc phân nhương lại về.</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Bấy giờ Triệu mới thừa cơ, Cứ đầm Dạ Trạch liệu bền tấn công.</t>
+          <t>Cửu dân đã quyết lời thề, Văn thần, vũ tướng ứng kỳ đều ra.</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Lý Vương phút trở xe rồng, Triệu Quang Phục mới chuyên lòng kinh doanh.</t>
+          <t>Tiêu Tư nghe gió chạy xa, Đông tây muôn dặm quan hà quét thanh.</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Hương nguyền trời cũng chứng minh, Rồng vàng trao vuốt giắt vành đâu mâu.</t>
+          <t>Vạn Xuân mới đặt quốc danh, Cải nguyên Thiên Đức, đô thành Long Biên.</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Từ khi long trảo đội đầu, Hổ hùng thêm mạnh quân nào dám đương.</t>
+          <t>Lịch đồ vừa mới kỷ niên, Hưng vương khí tượng cũng nên một đời.</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Bá Tiên đã trở về Lương, Dương Sàn còn ở chiến trường tranh đua.</t>
+          <t>Quân Lương đâu đã đến ngoài, Bá Tiên là tướng đeo bài chuyên chinh.</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Một cơn gió bẻ chồi khô, Ải Lang dứt dấu ngựa Hồ vào ra.</t>
+          <t>Cùng nhau mấy trận giao binh, Thất cơ Tô Lịch, Gia Ninh đôi đường.</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Bốn phương phẳng lặng can qua, Theo nền nếp cũ lại ra Long Thành.</t>
+          <t>Thu quân vào ở Tân Xương, Để cho Quang Phục chống Lương mặt ngoài.</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Lý xưa còn có một cành, Tên là Thiên Bảo náu mình Ai Lao.</t>
+          <t>Mới hay nhật phụ mộc lai, Sấm văn trước đã an bài những khi.</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Chiêu binh lên ở Động Đào, Họ là Phật Tử cũng vào hội minh.</t>
+          <t>Bấy giờ Triệu mới thừa cơ, Cứ đầm Dạ Trạch liệu bền tấn công.</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Đào Lang lại đổi quốc danh, Cũng toan thu phục cựu kinh của nhà.</t>
+          <t>Lý Vương phút trở xe rồng, Triệu Quang Phục mới chuyên lòng kinh doanh.</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Cành dâu mây khoá bóng tà, Bấy giờ Phật Tử mới ra nối dòng.</t>
+          <t>Hương nguyền trời cũng chứng minh, Rồng vàng trao vuốt giắt vành đâu mâu.</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Rừng xanh gió phất cờ hồng, Đề binh kéo xuống bên sông tung hoành.</t>
+          <t>Từ khi long trảo đội đầu, Hổ hùng thêm mạnh quân nào dám đương.</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Triệu Vương giáp trận Thái Bình, Lý thua rồi mới lui binh xin hoà.</t>
+          <t>Bá Tiên đã trở về Lương, Dương Sàn còn ở chiến trường tranh đua.</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Triệu về Long Đỗ Nhị Hà, Lý về Hạ Mỗ, ấy là Ô Diên.</t>
+          <t>Một cơn gió bẻ chồi khô, Ải Lang dứt dấu ngựa Hồ vào ra.</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Hai nhà lại kết nhân duyên, Nhã Lang sánh với gái hiền Cảo Nương. Có người Hống, Hát họ Trương, Vũ biền nhưng cũng biết đường cơ mưu.</t>
+          <t>Bốn phương phẳng lặng can qua, Theo nền nếp cũ lại ra Long Thành.</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Rằng: Xưa Trọng Thuỷ, Mỵ Châu, Hôn nhân là giả, khấu thù là chân.</t>
+          <t>Lý xưa còn có một cành, Tên là Thiên Bảo náu mình Ai Lao.</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Mảnh gương vâng sự còn gần, Lại toan đắc mối Châu Trần sao nên?</t>
+          <t>Chiêu binh lên ở Động Đào, Họ là Phật Tử cũng vào hội minh.</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>桃郎夌樹國名。拱算收復首京賜茄</t>
+          <t>桃郎夌樹國名。拱算收復首京賜茄。</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Trăng già sao nỡ xe duyên? Để cho Hậu Lý gây nền nội công.</t>
+          <t>Đào Lang lại đổi quốc danh, Cũng toan thu phục cựu kinh của nhà.</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Tình con rể, nghĩa vợ chồng, Tin nhau ai biết ra lòng lừa nhau.</t>
+          <t>Cành dâu mây khoá bóng tà, Bấy giờ Phật Tử mới ra nối dòng.</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Lân la mới ngỏ tình đầu, Nhã Lang trộm lấy đâu mâu đổi liền.</t>
+          <t>Rừng xanh gió phất cờ hồng, Đề binh kéo xuống bên sông tung hoành.</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Trở về giả chước vấn yên, Giáp binh đâu đã băng miền kéo sang.</t>
+          <t>Triệu Vương giáp trận Thái Bình, Lý thua rồi mới lui binh xin hoà.</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Triệu Vương đến bước vội vàng, Tình riêng còn chửa dứt đường cho qua.</t>
+          <t>Triệu về Long Đỗ Nhị Hà, Lý về Hạ Mỗ, ấy là Ô Diên.</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Đem con chạy đến Đại Nha, Than thân bách chiến phải ra đường cùng!</t>
+          <t>Hai nhà lại kết nhân duyên, Nhã Lang sánh với gái hiền Cảo Nương.</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Từ nay Phật Tử xưng hùng, Hiệu là Nam Đế nối dòng Lý Vương.</t>
+          <t>Có người Hống, Hát họ Trương, Vũ biền nhưng cũng biết đường cơ mưu.</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Phong Châu mới mở triều đường, Ô Diên, Long Đỗ giữ giàng hai kinh.</t>
+          <t>Rằng: Xưa Trọng Thuỷ, Mỵ Châu, Hôn nhân là giả, khấu thù là chân.</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Tuỳ sai đại tướng tổng binh, Lưu Phương là chức quản hành Giao Châu.</t>
+          <t>Mảnh gương vâng sự còn gần, Lại toan đắc mối Châu Trần sao nên?</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Đô Long một trận giáp nhau, Xin hàng Lý phải sang chầu Tấn Dương.</t>
+          <t>Trăng già sao nỡ xe duyên? Để cho Hậu Lý gây nền nội công.</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Từ giờ lại thuộc Bắc phương, Mấy năm Tuỳ loạn rồi Đường mới ra.</t>
+          <t>Tình con rể, nghĩa vợ chồng, Tin nhau ai biết ra lòng lừa nhau.</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Quan Tuỳ lại có Khâu Hoà, Đem dâng đồ tịch nước ta về Đường.</t>
+          <t>Lân la mới ngỏ tình đầu, Nhã Lang trộm lấy đâu mâu đổi liền.</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>An Nam lại mới canh trương, Đặt Đô Hộ Phủ theo đường Trung Hoa.</t>
+          <t>Trở về giả chước vấn yên, Giáp binh đâu đã băng miền kéo sang.</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Mười hai châu lại chia ra: Giao, Phong, Lục, Ái, Chi, Nga, Diễn, Tràng;</t>
+          <t>Triệu Vương đến bước vội vàng, Tình riêng còn chửa dứt đường cho qua.</t>
         </is>
       </c>
     </row>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Vũ An, Phúc Lộc, Hoan, Thang, Cơ mi các bộ man hoang ở ngoài.</t>
+          <t>Đem con chạy đến Đại Nha, Than thân bách chiến phải ra đường cùng!</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Quan Đường lắm kẻ tham tài, Bình dân hàm oán, trong ngoài hợp mưu.</t>
+          <t>Từ nay Phật Tử xưng hùng, Hiệu là Nam Đế nối dòng Lý Vương.</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Mai Thúc Loan ở Hoan Châu, Quân ba mươi vạn ruổi vào ải xa.</t>
+          <t>Phong Châu mới mở triều đường, Ô Diên, Long Đỗ giữ giàng hai kinh.</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Hiệu cờ Hắc Đế mở ra, Cũng toan quét dẹp sơn hà một phương.</t>
+          <t>Tuỳ sai đại tướng tổng binh, Lưu Phương là chức quản hành Giao Châu.</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Đường sai Tư Húc tiếp sang, Hợp cùng Sở Khách hai đàng giáp công.</t>
+          <t>Đô Long một trận giáp nhau, Xin hàng Lý phải sang chầu Tấn Dương.</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Vận đời còn chửa hanh thông, Nước non để giận anh hùng nghìn thu.</t>
+          <t>Từ giờ lại thuộc Bắc phương, Mấy năm Tuỳ loạn rồi Đường mới ra.</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Trấn Nam lại đổi tên châu, Một đời canh cải trước sau mấy kỳ.</t>
+          <t>Quan Tuỳ lại có Khâu Hoà, Đem dâng đồ tịch nước ta về Đường.</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Xa khơi ngoài chốn biên thuỳ, Đồ Bà giặc mọi đua bề phân tranh.</t>
+          <t>An Nam lại mới canh trương, Đặt Đô Hộ Phủ theo đường Trung Hoa.</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Bá Nghi hợp với Chính Bình, Dẹp đoàn tiểu khấu xây thành Đại La.</t>
+          <t>Mười hai châu lại chia ra: Giao, Phong, Lục, Ái, Chi, Nga, Diễn, Tràng;</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Xiết bao phú trọng, chính hà, Sinh đàn sầu khổ ai là xót chăng?</t>
+          <t>Vũ An, Phúc Lộc, Hoan, Thang, Cơ mi các bộ man hoang ở ngoài.</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Đường Lâm mới có Phùng Hưng, Đã tài kiêu dũng lại lưng phú hào.</t>
+          <t>Quan Đường lắm kẻ tham tài, Bình dân hàm oán, trong ngoài hợp mưu.</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Cõi Tây nổi việc cung đao, Đô Quân tôn hiệu, Tản Thao hiệp tình.</t>
+          <t>Mai Thúc Loan ở Hoan Châu, Quân ba mươi vạn ruổi vào ải xa.</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>號旗黑帝綱羅，挾算挾攘山河浚方</t>
+          <t>號旗黑帝綱羅，挾算挾攘山河浚方。</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Đem quân thẳng đến vây thành, Đại La thế bức, Chính Bình hồn tiêu.</t>
+          <t>Hiệu cờ Hắc Đế mở ra, Cũng toan quét dẹp sơn hà một phương.</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Đường sai người đến hợp cùng khách Sở, Đài, Đường cùng đánh.</t>
+          <t>Đường sai Tư Húc tiếp sang, Hợp cùng Sở Khách hai đàng giáp công.</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Vận may các nơi thông suốt, che chở, thương xót anh hùng mùa thu.</t>
+          <t>Vận đời còn chửa hanh thông, Nước non để giận anh hùng nghìn thu.</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Nhìn về Nam, tụ tập ở châu. Hết hoang tàn, thay đổi, rực rỡ khó lường.</t>
+          <t>Trấn Nam lại đổi tên châu, Một đời canh cải trước sau mấy kỳ.</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Huyện lọt vào biên giới Hoài, giặc Hợp Bà xúi giục, đều cùng tranh chấp.</t>
+          <t>Xa khơi ngoài chốn biên thuỳ, Đồ Bà giặc mọi đua bề phân tranh.</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Bá Nghi hợp với Chính Bình, dẹp đoàn tiểu khấu, phá thành Đại La.</t>
+          <t>Bá Nghi hợp với Chính Bình, Dẹp đoàn tiểu khấu xây thành Đại La.</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Xiết bao phú trọng, chính hà, sinh dân sầu khổ, ai là xót chăng?</t>
+          <t>Xiết bao phú trọng, chính hà, Sinh đàn sầu khổ ai là xót chăng?</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Đường Lâm mới có Phùng Hưng, tài kiêu dũng, lại lưng phú hào.</t>
+          <t>Đường Lâm mới có Phùng Hưng, Đã tài kiêu dũng lại lưng phú hào.</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Đem quân thẳng đến vây thành, Đại La thế bức, Chính Bình hồn tiêu.</t>
+          <t>Đường Lâm mới có Phùng Hưng, Đã tài kiêu dũng lại lưng phú hào.</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Nhân phủ trị mở ngôi triều, Phong Châu một giải nhiếp điều mấy niên.</t>
+          <t>Cõi Tây nổi việc cung đao, Đô Quân tôn hiệu, Tản Thao hiệp tình.</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Đế hương phút trở xe biền, Đại Vương Bố Cái tiếng truyền muôn thu.</t>
+          <t>Đem quân thẳng đến vây thành, Đại La thế bức, Chính Bình hồn tiêu.</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Phùng An con nối thơ ngu, nghe quan Nhu Viễn bày mưu hàng Đường.</t>
+          <t>Nhân phủ trị mở ngôi triều, Phong Châu một giải nhiếp điều mấy niên.</t>
         </is>
       </c>
     </row>
@@ -5405,12 +5405,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>詐自都護趙昌。城界壌吏伉驥紛響</t>
+          <t>詐自都護趙昌。城界壌吏伉驥紛響。</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Kể từ đô hộ Triệu Xương, thành La xây lại vững vàng hơn xưa.</t>
+          <t>Đế hương phút trở xe biền, Đại Vương Bố Cái tiếng truyền muôn thu.</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Thuyền chơi qua bến sông Từ.</t>
+          <t>Phùng An con nối thơ ngu, Nghe quan Nhu Viễn bày mưu hàng Đường.</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Giấc nồng đâu bỗng tình cờ lạ sao.</t>
+          <t>Kể từ đô hộ Triệu Xương, Thành La xây lại vững vàng hơn xưa.</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Thấy người hai trượng dài cao, bàn kinh, giảng truyện khác nào văn nhân.</t>
+          <t>Thuyền chơi qua bến sông Từ, Giấc nồng đâu bỗng tình cờ lạ sao.</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Cùng nhau như gửi tâm thần, tỉnh ra mới hỏi nguyên căn tỏ tường.</t>
+          <t>Thấy người hai trượng dài cao, Bàn kinh, giảng truyện khác nào văn nhân.</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Lý Ông Trọng ở Thuỵ Hương, người đời vua Thục mà sang thi Tần.</t>
+          <t>Cùng nhau như gửi tâm thần, Tỉnh ra mới hỏi nguyên căn tỏ tường.</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Hiếu liêm nhẹ bước thanh vân, làm quan hiệu uý đem quân ngữ Hồ.</t>
+          <t>Lý Ông Trọng ở Thuỵ Hương, Người đời vua Thục mà sang thi Tần.</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Uy danh đã khiếp Hung Nô, người về Nam Quốc, hình đồ Bắc phương.</t>
+          <t>Hiếu liêm nhẹ bước thanh vân, Làm quan hiệu uý đem quân ngữ Hồ.</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Hàm Dương đúc tượng người vàng, uy thừa còn giúp Tần Hoàng phục xa.</t>
+          <t>Uy danh đã khiếp Hung Nô, Người về Nam Quốc, hình đồ Bắc phương.</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Hương thôn cổ miếu tà tà, từ nay tu lý mới là phong quang.</t>
+          <t>Hàm Dương đúc tượng người vàng, Uy thừa còn giúp Tần Hoàng phục xa.</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Triệu Công tuổi tác về Đường, Quý Nguyên, Bùi Thái tranh quyền với nhau.</t>
+          <t>Hương thôn cổ miếu tà tà, Từ nay tu lý mới là phong quang.</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Triều đình kén kẻ trị châu, Triệu Công vâng mệnh xe thiều lại sang.</t>
+          <t>Triệu Công tuổi tác về Đường, Quý Nguyên, Bùi Thái tranh quyền với nhau.</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Bản kiều vừa nhận dấu sương, bến hồng đã định khói lang cũng tàn.</t>
+          <t>Bản kiều vừa nhận dấu sương, Bến hồng đã định khói lang cũng tàn.</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Trương Đan thay chức phiên hàn, tập nghề thuỷ chiến, tạo thuyền đồng mông.</t>
+          <t>Trương Đan thay chức phiên hàn, Tập nghề thuỷ chiến, tạo thuyền đồng mông.</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Quan tham ai chẳng oán thù, kìa như Tượng Cổ sư đồ bạn ly.</t>
+          <t>Quan tham ai chẳng oán thù, Kìa như Tượng Cổ sư đồ bạn ly.</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Quan hiền ai chẳng uý uy, kìa như Mã Tổng man di đầu hàng.</t>
+          <t>Quan hiền ai chẳng uý uy, Kìa như Mã Tổng man di đầu hàng.</t>
         </is>
       </c>
     </row>
@@ -5694,12 +5694,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>元嘉遷府蘇江。璣蘄寶晉遷趣宋平</t>
+          <t>元嘉遷府蘇江。璣蘄寶晉遷趣宋平。</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Nguyên Gia dời phủ Tô Giang, đến năm Bảo Lịch dời sang Tống Bình.</t>
+          <t>Nguyên Gia dời phủ Tô Giang, Đến năm Bảo Lịch dời sang Tống Bình.</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Tiết thanh cảm vật mới kỳ, dưới dòng Hợp Phố châu đi cũng về.</t>
+          <t>Tiết thanh cảm vật mới kỳ, Dưới dòng Hợp Phố châu đi cũng về.</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Kiềm Châu xa ruổi mã đề, hồng bay còn dấu, tuyết nê chưa mòn.</t>
+          <t>Kiềm Châu xa ruổi mã đề, Hồng bay còn dấu, tuyết nê chưa mòn.</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Nhũng quan lại gặp Vũ Hồn, thành lâu lửa cháy, dinh đồn quân reo.</t>
+          <t>Nhũng quan lại gặp Vũ Hồn, Thành lâu lửa cháy, dinh đồn quân reo.</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Đoàn Công vâng mệnh Đường Triều, trước quân phủ dụ giặc nào chẳng tan.</t>
+          <t>Đoàn Công vâng mệnh Đường Triều, Trước quân phủ dụ giặc nào chẳng tan.</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Nho môn có kẻ tướng thần, họ Vương tên Thức kinh luân gồm tài.</t>
+          <t>Nho môn có kẻ tướng thần, Họ Vương tên Thức kinh luân gồm tài.</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>城門嚴備郵外。掩櫓竹木習牌弓刀</t>
+          <t>城門嚴備郵外。掩櫓竹木習牌弓刀。</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Thành môn nghiêm bị trong ngoài, trồng cây trúc mộc, tập bài cung đao.</t>
+          <t>Thành môn nghiêm bị trong ngoài, Trồng cây trúc mộc, tập bài cung đao.</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Dùng dằng nào dám tiến sang, Tám ngàn quân bỏ cương tràng sạch không.</t>
+          <t>Xe thiều vừa trở về Đông, Giặc Man thừa khích ruổi giong cõi ngoài.</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Dối tâu lại muốn cầu công, Rồi ra sự phát đều cùng nghị lưu.</t>
+          <t>Đường sai Thái Tập lĩnh bài Giao Châu.</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Cao Biền là tướng lạc điêu, Tài danh sớm đã dự vào giản tri.</t>
+          <t>Biên thư mấy bức về tâu, Kẻ xin lưu thú, người cầu bãi binh.</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Quân phù vâng lệnh chỉ huy, Tiệp thư sai một tiểu ty về chầu.</t>
+          <t>Ghen công vì hoặc Thái Kinh, Thờ ơ để việc biên tình mặc ai.</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Gia quan cho lĩnh tiết mao, Đặt quân Tĩnh Hải biên vào bản chương.</t>
+          <t>Tiếc thay muôn dặm thành dài, Cô quân nên nỗi thiệt tài chiết xung.</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Một châu hùng cứ xưng vương, Thành La rộng mở kim thang vững bền.</t>
+          <t>Ngu Hầu tiếp chiến bên sông, Quyết liều một trận đều cùng quyên sinh.</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Tuần hành trải khắp sơn xuyên, Đào Thiên Uy cảng thông thuyền vãng lai.</t>
+          <t>Vua Đường tuyên chỉ triệu binh, Bỏ hàm Đô Hộ đặt hành Giao Châu.</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Chín năm khép mở ra tài, Thành trì truyền dấu, miếu đài ghi công.</t>
+          <t>Trấn đồn cửa bể đâu đâu, Tống Nhung, Thừa Huấn hợp nhau một đường.</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Rồi khi trở ngựa Hán Trung, Cao Tầm là cháu nối dòng xưng phiên.</t>
+          <t>Dùng dằng nào dám tiến sang, Tám ngàn quân bỏ cương tràng sạch không.</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Họ Tăng tên Cổn cũng hiền, Giao Châu di ký còn truyền một chương.</t>
+          <t>Dối tâu lại muốn cầu công, Rồi ra sự phát đều cùng nghị lưu.</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Ba trăm năm lẻ Tùy, Đường, Lại trong Ngũ Quý tang thương cũng dài.</t>
+          <t>Cao Biền là tướng lạc điêu, Tài danh sớm đã dự vào giản tri.</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Hồng châu Khúc Hạo hùng tài, Gặp đời thúc quý toan bài bá vương.</t>
+          <t>Quân phù vâng lệnh chỉ huy, Tiệp thư sai một tiểu ty về chầu.</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Cõi nhà hùng cứ nam phương, Cung cầu một lễ, Hán Lương hai lòng.</t>
+          <t>Gia quan cho lĩnh tiết mao, Đặt quân Tĩnh Hải biên vào bản chương.</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Qui mô cũng rắp hỗn đồng, Điền tô, đinh ngạch đều cùng định nên.</t>
+          <t>Một châu hùng cứ xưng vương, Thành La rộng mở kim thang vững bền.</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Thừa gia vừa được tái truyền, Bởi cầu Lương tiết hóa nên Hán tù.</t>
+          <t>Tuần hành trải khắp sơn xuyên, Đào Thiên Uy cảng thông thuyền vãng lai.</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Dương Đình Nghệ lại báo thù, Đuổi người Hán, lĩnh châu phù vừa xong.</t>
+          <t>Chín năm khép mở ra tài, Thành trì truyền dấu, miếu đài ghi công.</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Nghĩa nhi gặp đứa gian hùng, Kiều Công Tiện lại nỡ lòng sao nên.</t>
+          <t>Rồi khi trở ngựa Hán Trung, Cao Tầm là cháu nối dòng xưng phiên.</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Dương công xưa có rể hiền, Đường Lâm hào hữu, tên Quyền họ Ngô.</t>
+          <t>Họ Tăng tên Cổn cũng hiền, Giao Châu di ký còn truyền một chương.</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Vì thầy quyết chí phục thù, Nghĩa binh từ cõi Ái châu kéo vào.</t>
+          <t>Ba trăm năm lẻ Tùy, Đường, Lại trong Ngũ Quý tang thương cũng dài.</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Hán sai thái tử Hoằng Thao, Đem quân ứng viện toan vào giúp công.</t>
+          <t>Hồng châu Khúc Hạo hùng tài, Gặp đời thúc quý toan bài bá vương.</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Bạch Đằng một trận giao phong, Hoằng Thao lạc vía, Kiều Công nộp đầu.</t>
+          <t>Cõi nhà hùng cứ nam phương, Cung cầu một lễ, Hán Lương hai lòng.</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Quân thân đã chính cương trù, Giang sơn rầy có vương hầu chủ trương.</t>
+          <t>Qui mô cũng rắp hỗn đồng, Điền tô, đinh ngạch đều cùng định nên.</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Về Loa Thành mới đăng quang, Quan danh cải định, triều chương đặt bày.</t>
+          <t>Thừa gia vừa được tái truyền, Bởi cầu Lương tiết hóa nên Hán tù.</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Nền vương vừa mới dựng xây, Tiếc cho hưởng nước chưa đầy sáu năm.</t>
+          <t>Dương Đình Nghệ lại báo thù, Đuổi người Hán, lĩnh châu phù vừa xong.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Đến cơn loạn mệnh nên nhầm, Cán Long Tuyền để trao cầm tay ai?</t>
+          <t>Nghĩa nhi gặp đứa gian hùng, Kiều Công Tiện lại nỡ lòng sao nên.</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Tam Kha là đứa gian hồi, Lấy bè thích lý chịu lời thác cô.</t>
+          <t>Dương công xưa có rể hiền, Đường Lâm hào hữu, tên Quyền họ Ngô.</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Cành Dương đè lấn chồi Ngô, Bình Vương tiếm hiệu quốc đô tranh quyền.</t>
+          <t>Vì thầy quyết chí phục thù, Nghĩa binh từ cõi Ái châu kéo vào.</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Ngô Vương vốn có con hiền, Trưởng là Xương Ngập nối truyền thế gia.</t>
+          <t>Hán sai thái tử Hoằng Thao, Đem quân ứng viện toan vào giúp công.</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Trà Hương lánh dấu yên hà, Hộ trì lại gặp tôi là Phạm Công.</t>
+          <t>Bạch Đằng một trận giao phong, Hoằng Thao lạc vía, Kiều Công nộp đầu.</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Xương Văn em thứ con dòng, Nương mình phủ dưỡng cam lòng kinh doanh.</t>
+          <t>Quân thân đã chính cương trù, Giang sơn rầy có vương hầu chủ trương.</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Nhàn khi ra đánh Thái Bình, Vén tay tả đản về thành tập công.</t>
+          <t>Về Loa Thành mới đăng quang, Quan danh cải định, triều chương đặt bày.</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Khoan hình rồi lại giáng phong, Tư tình, công nghĩa thủy chung lưỡng tuyền.</t>
+          <t>Nền vương vừa mới dựng xây, Tiếc cho hưởng nước chưa đầy sáu năm.</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Yên vui lại nhớ anh hiền, Rước tìm Xương Ngập chung quyền quốc gia.</t>
+          <t>Đến cơn loạn mệnh nên nhầm, Cán Long Tuyền để trao cầm tay ai?</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Chi lan xum họp một nhà, Anh xưng Thiên Sách, em là Tấn Vương.</t>
+          <t>Tam Kha là đứa gian hồi, Lấy bè thích lý chịu lời thác cô.</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Cùng nhau đều hưởng giầu sang, Dù khi chếch lệch biên tường cũng nguôi.</t>
+          <t>Cành Dương đè lấn chồi Ngô, Bình Vương tiếm hiệu quốc đô tranh quyền.</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Bốn năm Thiên Sách vừa rồi, Tấn Vương rầy mới chuyên ngôi một mình.</t>
+          <t>Ngô Vương vốn có con hiền, Trưởng là Xương Ngập nối truyền thế gia.</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Sính tài lại hiếu việc binh, Thao Giang đã tĩnh, Thái Bình lại vây.</t>
+          <t>Trà Hương lánh dấu yên hà, Hộ trì lại gặp tôi là Phạm Công.</t>
         </is>
       </c>
     </row>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Trận tiền một mũi tên bay, Khinh thân vàng ngọc, trách này bởi ai?</t>
+          <t>Xương Văn em thứ con dòng, Nương mình phủ dưỡng cam lòng kinh doanh.</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Tiếc thay chửa được lâu dài, Mười lăm năm mới hai đời đến đây.</t>
+          <t>Nhàn khi ra đánh Thái Bình, Vén tay tả đản về thành tập công.</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Nghiệp Ngô rầy có ai thay? Đua nhau lại phó mặc tay quần hùng.</t>
+          <t>Khoan hình rồi lại giáng phong, Tư tình, công nghĩa thủy chung lưỡng tuyền.</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Tiên Du riêng một đề phong, Nguyễn Công Thủ Tiệp cứ vùng Nguyệt Thiên.</t>
+          <t>Yên vui lại nhớ anh hiền, Rước tìm Xương Ngập chung quyền quốc gia.</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Đường Lâm riêng một sơn xuyên, Ngô Công Nhật Khánh cứ miền Tản Thao.</t>
+          <t>Chi lan xum họp một nhà, Anh xưng Thiên Sách, em là Tấn Vương.</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Tây Phù Liệt có Nguyễn Siêu, Ngô Xương Sí giữ Bình Kiều một phương.</t>
+          <t>Cùng nhau đều hưởng giầu sang, Dù khi chếch lệch biên tường cũng nguôi.</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Tế Giang này có Lữ Đường, Nguyễn Khoan hùng cứ Vĩnh Tường phải chăng?</t>
+          <t>Bốn năm Thiên Sách vừa rồi, Tấn Vương rầy mới chuyên ngôi một mình.</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Phạm Phòng Át giữ Châu Đằng, Kiều Tam Chế giữ ngàn rừng Châu Phong.</t>
+          <t>Sính tài lại hiếu việc binh, Thao Giang đã tĩnh, Thái Bình lại vây.</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Đỗ Giang kìa Đỗ Cảnh Công, Kiều Công tên Thuận ở trong Hồi Hồ.</t>
+          <t>Trận tiền một mũi tên bay, Khinh thân vàng ngọc, trách này bởi ai?</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Kiến Ong, Siêu Loại tranh đua, Lý Khuê một cõi trì khu dầu lòng.</t>
+          <t>Tiếc thay chửa được lâu dài, Mười lăm năm mới hai đời đến đây.</t>
         </is>
       </c>
     </row>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Kình nghê Bố Hải vẫy vùng, Trần Công tên Lãm xưng hùng một nơi.</t>
+          <t>Nghiệp Ngô rầy có ai thay? Đua nhau lại phó mặc tay quần hùng.</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Phân tranh hội ấy nực cười! Mười hai quan sứ mỗi người mỗi phương.</t>
+          <t>Tiên Du riêng một đề phong, Nguyễn Công Thủ Tiệp cứ vùng Nguyệt Thiên.</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Xoay vần trong cuộc tang thương, Trải bao phân loạn mới sang trị bình.</t>
+          <t>Đường Lâm riêng một sơn xuyên, Ngô Công Nhật Khánh cứ miền Tản Thao.</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Có ông Bộ Lĩnh họ Đinh, Con quan thứ sử ở thành Hoa Lư.</t>
+          <t>Tây Phù Liệt có Nguyễn Siêu, Ngô Xương Sí giữ Bình Kiều một phương.</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Khác thường từ thuở còn thơ, Rủ đoàn mục thụ mở cờ bông lau.</t>
+          <t>Tế Giang này có Lữ Đường, Nguyễn Khoan hùng cứ Vĩnh Tường phải chăng?</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Dập dìu kẻ trước người sau, Trần ai đã thấy vương hầu uy dung.</t>
+          <t>Phạm Phòng Át giữ Châu Đằng, Kiều Tam Chế giữ ngàn rừng Châu Phong.</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Một mai về với Trần Công, Hiệu xưng Vạn Thắng, anh hùng ai qua.</t>
+          <t>Đỗ Giang kìa Đỗ Cảnh Công, Kiều Công tên Thuận ở trong Hồi Hồ.</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Bốn phương thu lại một nhà, Mười hai sứ tướng đều là quét thanh.</t>
+          <t>Kiến Ong, Siêu Loại tranh đua, Lý Khuê một cõi trì khu dầu lòng.</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Trường Yên đầu dựng đô thành, Cải nguyên là hiệu Thái Bình từ đây.</t>
+          <t>Kình nghê Bố Hải vẫy vùng, Trần Công tên Lãm xưng hùng một nơi.</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Nghìn năm cơ tự mới xây, Lên ngôi hoàng đế đặt bầy trăm quan.</t>
+          <t>Phân tranh hội ấy nực cười! Mười hai quan sứ mỗi người mỗi phương.</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Có đường bệ có y quan, Đẳng uy có biệt, giai ban có thường.</t>
+          <t>Xoay vần trong cuộc tang thương, Trải bao phân loạn mới sang trị bình.</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Tống phong Giao Chỉ quận vương, Cha con đều chịu sủng chương một ngày. Hồng Bàng để mối đến nay, Kể trong chính thống từ đây là đầu.</t>
+          <t>Có ông Bộ Lĩnh họ Đinh, Con quan thứ sử ở thành Hoa Lư.</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Tiếc không học vấn công phu, Già tăng cũng dự quan sang,</t>
+          <t>Khác thường từ thuở còn thơ, Rủ đoàn mục thụ mở cờ bông lau.</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Bặc, Điền, Cơ, Tú đều phường vũ nhân. Nội đình năm vị nữ quân,</t>
+          <t>Dập dìu kẻ trước người sau, Trần ai đã thấy vương hầu uy dung.</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Nặng tình kiêm ái, quên phần di mưu. Đã phong Đinh Liễn con đầu,</t>
+          <t>Một mai về với Trần Công, Hiệu xưng Vạn Thắng, anh hùng ai qua.</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Hạng Lang là thứ nhẽ nào đổi thay? Pháp hình cũng lạ xưa nay,</t>
+          <t>Bốn phương thu lại một nhà, Mười hai sứ tướng đều là quét thanh.</t>
         </is>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Hùm nuôi trong cũi, vạc bầy ngoài sân. Chơi bời gần lũ tiểu nhân,</t>
+          <t>Trường Yên đầu dựng đô thành, Cải nguyên là hiệu Thái Bình từ đây.</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Rượu hoa ngọt giọng, đền xuân mê lòng. Trùng môn thưa hở đề phòng,</t>
+          <t>Nghìn năm cơ tự mới xây, Lên ngôi hoàng đế đặt bầy trăm quan.</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Để cho Đỗ Thích gian hùng nỡ tay. Nối sau Thiếu Đế thơ ngây,</t>
+          <t>Có đường bệ có y quan, Đẳng uy có biệt, giai ban có thường.</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Lê Hoàn tiếp chính từ rầy dọc ngang. Tiếm xưng là Phó Quốc Vương,</t>
+          <t>Tống phong Giao Chỉ quận vương, Cha con đều chịu sủng chương một ngày.</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Ra vào cùng ả họ Dương chung tình. Bặc, Điền vì nước liều mình,</t>
+          <t>Hồng Bàng để mối đến nay, Kể trong chính thống từ đây là đầu.</t>
         </is>
       </c>
     </row>
@@ -7037,12 +7037,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>惜空斈問工夫轉碧也別壚鄰俸塘</t>
+          <t>惜空斈問工夫　轉碧也別壚鄰俸塘</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Trách sao Cự Lạng tán thành mưu gian. Chợt nghe binh báo Nam Quan,</t>
+          <t>Tiếc không học vấn công phu,</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Cùng nhau phù lập Lê Hoàn làm vương. Trước mành vâng lệnh nàng Dương,</t>
+          <t>Già tăng cũng dự quan sang, Bặc, Điền, Cơ, Tú đều phường vũ nhân.</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Trong cung đã thấy áo vàng đưa ra. Trường Yên đổi mặt sơn hà,</t>
+          <t>Nội đình năm vị nữ quân, Nặng tình kiêm ái, quên phần di mưu.</t>
         </is>
       </c>
     </row>
@@ -7088,12 +7088,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>色封丁璉猟頭。項郎異次鍾帝拊台</t>
+          <t>色封丁璉猟頭。項郎異次鍾帝拊台。</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Đại Hành tri lược thực là cũng ghê. Vạc Đinh đã trở sang Lê,</t>
+          <t>Đã phong Đinh Liễn con đầu, Hạng Lang là thứ nhẽ nào đổi thay?</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Nàng Dương chăn gối cũng về hậu cung. Nguy nga ngói bạc, cột đồng,</t>
+          <t>Pháp hình cũng lạ xưa nay, Hùm nuôi trong cũi, vạc bầy ngoài sân.</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Cung đài trang sức buông lòng xa hoang. Tự mình đã trái luân thường,</t>
+          <t>Chơi bời gần lũ tiểu nhân, Rượu hoa ngọt giọng, đền xuân mê lòng.</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Lấy chi rủ mối dựng giường về sau. Đoàn con đích, thứ tranh nhau,</t>
+          <t>Trùng môn thưa hở đề phòng, Để cho Đỗ Thích gian hùng nỡ tay.</t>
         </is>
       </c>
     </row>
@@ -7156,12 +7156,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>毀嶷少帝踐廢，黎桓接政自勗育昂</t>
+          <t>毀嶷少帝踐廢，黎桓接政自勗育昂。</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Để cho cốt nhục thành cừu bởi ai? Trung Tông vừa mới nối dời,</t>
+          <t>Nối sau Thiếu Đế thơ ngây, Lê Hoàn tiếp chính từ rầy dọc ngang.</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Cấm đình thoắt đã có người sinh hung. Ngoạ Triều thí nghịch hôn dung,</t>
+          <t>Tiếm xưng là Phó Quốc Vương, Ra vào cùng ả họ Dương chung tình.</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Trong mê tửu sắc, ngoài nồng hình danh. Đao sơn, kiếm thụ đầy thành,</t>
+          <t>Bặc, Điền vì nước liều mình, Trách sao Cự Lạng tán thành mưu gian.</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Thuỷ lao bào lạc ngục hình gớm thay. Bốn năm sầu oán đã đầy,</t>
+          <t>Chợt nghe binh báo Nam Quan, Cùng nhau phù lập Lê Hoàn làm vương.</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Vừa tuần Lê rụng đến ngày Lý sinh. Bắc Giang trời mở thánh minh,</t>
+          <t>Trước mành vâng lệnh nàng Dương, Trong cung đã thấy áo vàng đưa ra.</t>
         </is>
       </c>
     </row>
@@ -7241,12 +7241,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>長安撈麵山河</t>
+          <t>長安撈麵山河，大行智覺是乎拱嘗</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Thăng Long mới đổi đặt tên kinh thành.</t>
+          <t>Trường Yên đổi mặt sơn hà, Đại Hành tri lược thực là cũng ghê.</t>
         </is>
       </c>
     </row>
@@ -7263,7 +7263,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Định ra thuế lệ phân minh,</t>
+          <t>Vạc Đinh đã trở sang Lê, Nàng Dương chăn gối cũng về hậu cung.</t>
         </is>
       </c>
     </row>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Túc Xa quản giáp quân danh cũng tường.</t>
+          <t>Nguy nga ngói bạc, cột đồng, Cung đài trang sức buông lòng xa hoang.</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Hỗn đồng một mối phong cương,</t>
+          <t>Tự mình đã trái luân thường, Lấy chi rủ mối dựng giường về sau.</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Hai mươi bốn lộ các đường mới chia.</t>
+          <t>Đoàn con đích, thứ tranh nhau, Để cho cốt nhục thành cừu bởi ai?</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Cử Long sấm dậy binh uy,</t>
+          <t>Trung Tông vừa mới nối dời, Cấm đình thoắt đã có người sinh hung.</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Diễn Châu gió động tinh kỳ thân chinh.</t>
+          <t>Ngoạ Triều thí nghịch hôn dung, Trong mê tửu sắc, ngoài nồng hình danh.</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Biện Loan gặp lúc hối minh,</t>
+          <t>Đao sơn, kiếm thụ đầy thành, Thuỷ lao bào lạc ngục hình gớm thay.</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Hương nguyền cảm cách, sóng kình cũng êm.</t>
+          <t>Bốn năm sầu oán đã đầy, Vừa tuần Lê rụng đến ngày Lý sinh.</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Bốn phương trong trị, ngoài nghiêm,</t>
+          <t>Bắc Giang trời mở thánh minh, Lý Công tên Uẩn nhân tình đới suy.</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Chiêm Thành, Chân Lạp xa đem cung cầu.</t>
+          <t>Lê triều làm chức chỉ huy, Lũ Đào Cam Mộc ứng kỳ phù lên.</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Ngựa Man sang tiến Bắc triều,</t>
+          <t>Đầu năm cải hiệu Thuận Thiên, Thăng Long mới đổi đặt tên kinh thành.</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Tống Hoàng ban thưởng quan bào thêm vinh.</t>
+          <t>Định ra thuế lệ phân minh, Túc Xa quản giáp quân danh cũng tường.</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Ví hay đạo học tinh minh,</t>
+          <t>Hỗn đồng một mối phong cương, Hai mươi bốn lộ các đường mới chia.</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Đế vương sự nghiệp nước mình ai hơn?</t>
+          <t>Cử Long sấm dậy binh uy, Diễn Châu gió động tinh kỳ thân chinh.</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Cớ sao tín hoặc dị đoan,</t>
+          <t>Biện Loan gặp lúc hối minh, Hương nguyền cảm cách, sóng kình cũng êm.</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Say vui đạo Phật, lưu liên cảnh chùa?</t>
+          <t>Bốn phương trong trị, ngoài nghiêm, Chiêm Thành, Chân Lạp xa đem cung cầu.</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Để cho dân tục tranh đua,</t>
+          <t>Ngựa Man sang tiến Bắc triều, Tống Hoàng ban thưởng quan bào thêm vinh.</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Ni cô nối gót, tăng đồ chen vai.</t>
+          <t>Ví hay đạo học tinh minh, Đế vương sự nghiệp nước mình ai hơn?</t>
         </is>
       </c>
     </row>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Bởi vì sinh cửa Như Lai,</t>
+          <t>Cớ sao tín hoặc dị đoan, Say vui đạo Phật, lưu liên cảnh chùa?</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Tiêu Sơn từ thuở anh hài mới ra.</t>
+          <t>Để cho dân tục tranh đua, Ni cô nối gót, tăng đồ chen vai.</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Sóng tình chìm nổi ái hà,</t>
+          <t>Bởi vì sinh cửa Như Lai, Tiêu Sơn từ thuở anh hài mới ra.</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Chín ngôi hoàng hậu, phép nhà cũng sai.</t>
+          <t>Sóng tình chìm nổi ái hà, Chín ngôi hoàng hậu, phép nhà cũng sai.</t>
         </is>
       </c>
     </row>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Tự mình đã dựng lệ giai,</t>
+          <t>Tự mình đã dựng lệ giai, Khiến nên con cái, thêm bài tương tranh.</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Khiến nên con cái, thêm bài tương tranh.</t>
+          <t>Thái Tông nối nghiệp thủ thành, Anh em lại rắp đua giành ngôi cao.</t>
         </is>
       </c>
     </row>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Thái Tông nối nghiệp thủ thành,</t>
+          <t>Cùng nhau binh mã sấn vào, Cấm thành bỗng chốc xôn xao chiến trường.</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Anh em lại rắp đua giành ngôi cao.</t>
+          <t>Trận tiền giết Vũ Đức Vương, Đông Chinh, Dực Thánh tin đường chạy xa.</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Cùng nhau binh mã sấn vào,</t>
+          <t>Khoan hình lại xuống chiếu tha, Thân phiên đã định, nước nhà mới yên.</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Cấm thành bỗng chốc xôn xao chiến trường.</t>
+          <t>Ban hình luật, canh tịch điền, Mở đồ nhất thống cầm quyền tứ chinh.</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Trận tiền giết Vũ Đức Vương, Đông Chinh, Dực Thánh tin đường chạy xa.</t>
+          <t>Mừng xem Phiên phục Nùng bình, Huy xưng có chữ rành rành biểu tiên.</t>
         </is>
       </c>
     </row>
@@ -7756,7 +7756,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Khoan hình lại xuống chiếu tha,</t>
+          <t>Vắn dài là số tự nhiên, Tụng kinh cầu thọ khéo nên chuyện cười.</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Thân phiên đã định, nước nhà mới yên.</t>
+          <t>Thánh Tông văn học hơn đời, Bình Chiêm đánh Tống đủ tài kinh luân.</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Ban hình luật, canh tịch điền,</t>
+          <t>Khuyến nông chăm việc cần dân, Chiếu chăn thương kẻ tù nhân lạnh lùng.</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Mở đồ nhất thống cầm quyền tứ chinh.</t>
+          <t>Thánh hiền tô tượng học cung, Đặt khoa bác sĩ, ưu dung đại thần.</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7824,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Mừng xem Phiên phục Nùng bình,</t>
+          <t>Ân riêng mưa móc đượm nhuần, Đã tiền lại lúa ân cần dưỡng liêm.</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Huy xưng có chữ rành rành biểu tiên.</t>
+          <t>Hồ Tây vui thú Dâm Đàm, Nỡ đem của nước xây làm cung tiên.</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Vắn dài là số tự nhiên,</t>
+          <t>Chuông Sùng Khánh tháp Báo Thiên, Phật vàng đúc tượng, say thiền lạ sao!</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Tụng kinh cầu thọ khéo nên chuyện cười.</t>
+          <t>Nhân Tông tuổi chửa là bao, Ngoài ra triều yết, trong vào giảng minh,</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Thánh Tông văn học hơn đời,</t>
+          <t>Thụ di có Lý Đạo Thành, Ỷ Lan hoàng hậu buông mành giúp nên.</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Bình Chiêm đánh Tống đủ tài kinh luân.</t>
+          <t>Mở khoa bác học cầu hiền, Ba thăng một mẫu, thuế điền nhẹ thay!</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Thông minh học vấn kiêm toàn cả hai.</t>
+          <t>Có khi xem gặt xem cầy, Lòng chăm điền dã một ngày mấy tao.</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Năm đầu vừa mới lên ngôi, Giảng cầu trước đã mở bài kinh diên.</t>
+          <t>Mưa ân ngấm khắp dồi dào, Chuộc người bần nữ gả vào quan phu.</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Qui nông cho lính canh phiên, Rộng ân lại trả quan điền cho dân.</t>
+          <t>Thân chinh xe ngựa trì khu, Phá Sa Động bắt man tù Ngụy Phang.</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Anh Tông còn thủa xung nhân, Đỗ Anh Vũ lấy ngoại thân lộng hành.</t>
+          <t>Chiêm Thành nộp đất xin hàng, Ba châu qui phụ một đường thanh di.</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Ra vào trong trướng, ngoài mành, Cùng Lê Thái Hậu có tình riêng chung.</t>
+          <t>Tống binh xâm nhiễu biên thùy, Tướng quân Thường Kiệt dựng kỳ cờ Bắc chinh.</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Tống giam đã bắt vào trong, Mà Lê hậu lại còn lòng đeo đai.</t>
+          <t>Bên sông Như Nguyệt trú dinh, Giang sơn dường có thần linh hộ trì.</t>
         </is>
       </c>
     </row>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Rượu cơm vẫn cứ đưa mời, Vàng cho ngục tốt liệu bài thoát ra.</t>
+          <t>Miếu tiền phảng phất ngâm thi, Như phân địa thế, như trì thiên binh.</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Nghị đồ rồi lại được tha, Để đoàn Vũ Đái đều là thác oan.</t>
+          <t>Bấy giờ Tống mới hư kinh, Giảng hòa lại trả mấy thành cố cương.</t>
         </is>
       </c>
     </row>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Rồi ra vắng mặt quyền gian, Hiến Thành hết sức cán toàn mới nên.</t>
+          <t>Lại còn hối hận một chương, Tham voi Giao Chỉ, mất vàng Quảng Nguyên.</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Khi triều Tống, khi sính Nguyên, Một niềm cung thuận đôi bên được lòng.</t>
+          <t>Năm mươi năm lẻ lâu bền, Vũ công, văn đức rạng truyền sử xanh.</t>
         </is>
       </c>
     </row>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>An Nam Tống mới cải phong, Quốc danh từ ấy rạng dòng Viêm Phương.</t>
+          <t>Thượng Dương sao nỡ bạc tình, Để bà Dương hậu một mình ngậm oan.</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Thành Nam mở chốn võ tràng, Tập tành cung ngựa phô trương tinh kỳ.</t>
+          <t>Kìa Lê Văn Thịnh mưu gian, Thương chi quái hổ mà khoan lưới hình!</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Uy thanh giậy đến biên thùy, Chiêm Thành Ngưu Hống man di cũng bình.</t>
+          <t>Phật từ như quả chứng minh, Chuông chùa Diên Hựu đã thành phúc cai.</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Tuần du đã tỏ dân tình, Sơn xuyên trải khắp địa hình gần xa.</t>
+          <t>Cớ sao chi thứ nối đời, Trừ quân lại thác vào người hóa duyên?</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Trừ quân vì một nết tà, Đổi sang Long Cán còn là ấu niên.</t>
+          <t>Thần Tông sinh cửa Sùng Hiền, Dấu hang thi giải còn truyền Sài Sơn.</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Thác cô nhờ có tôi hiền, Dẫu người hối chúc mà quyền chẳng sai.</t>
+          <t>Thức nồng nhuộm vẻ chi lan, Thông minh học vấn kiêm toàn cả hai.</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Cao Tông ba tuổi nối đời, Hiến Thành cư nhiếp trong ngoài đều yên.</t>
+          <t>Năm đầu vừa mới lên ngôi, Giảng cầu trước đã mở bài kinh diên.</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Di lưu còn muốn tiến hiền, Đem Trần Trung Tá thay quyền tán tương.</t>
+          <t>Qui nông cho lính canh phiên, Rộng ân lại trả quan điền cho dân.</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Tiếc không dùng kẻ trung lương, Cao Tông hoang túng mọi đường ai can?</t>
+          <t>Anh Tông còn thủa xung nhân, Đỗ Anh Vũ lấy ngoại thân lộng hành.</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Dấu xe quanh khắp giang san, Chính hình lỗi tiết, du quan quá thường.</t>
+          <t>Ra vào trong trướng, ngoài mành, Cùng Lê Thái Hậu có tình riêng chung.</t>
         </is>
       </c>
     </row>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Lại thêm thổ mộc cung tường, Mua quan bán ngục nhiều đường riêng tây.</t>
+          <t>Tống giam đã bắt vào trong, Mà Lê hậu lại còn lòng đeo đai.</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Nhạc Chiêm rầu rĩ khéo bầy, Những là tai biến từ này hiện ra.</t>
+          <t>Rượu cơm vẫn cứ đưa mời, Vàng cho ngục tốt liệu bài thoát ra.</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Trâu đâu lên ngọn Am La, Thước đâu làm tổ góc nhà Kính Thiên.</t>
+          <t>Nghị đồ rồi lại được tha, Để đoàn Vũ Đái đều là thác oan.</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Bốn phương trộm cướp nổi lên, Quân Chiêm, người Tống xâm biên mấy kỳ.</t>
+          <t>Rồi ra vắng mặt quyền gian, Hiến Thành hết sức cán toàn mới nên.</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Vui chơi nào có biết gì, Thờ ơ phó chuyện an nguy mặc trời.</t>
+          <t>Khi triều Tống, khi sính Nguyên, Một niềm cung thuận đôi bên được lòng.</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Quyền cương ngày một đổi dời, Phạm Du đã phản lại vời về kinh.</t>
+          <t>An Nam Tống mới cải phong, Quốc danh từ ấy rạng dòng Viêm Phương.</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Bỉnh Di là kẻ trung thành, Nghe dèm mà nỡ gia hình cớ sao?</t>
+          <t>Thành Nam mở chốn võ tràng, Tập tành cung ngựa phô trương tinh kỳ.</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Bởi ai gây việc oan cừu, Để cho Quách Bốc sấn vào kim giai.</t>
+          <t>Uy thanh giậy đến biên thùy, Chiêm Thành Ngưu Hống man di cũng bình.</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Xe loan lánh chạy ra ngoài, Hoàng thân đế thích mỗi người một phương.</t>
+          <t>Tuần du đã tỏ dân tình, Sơn xuyên trải khắp địa hình gần xa.</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Trừ quân đi đến Thiên Trường, Tình cờ lại gặp một nường tiểu thư.</t>
+          <t>Trừ quân vì một nết tà, Đổi sang Long Cán còn là ấu niên.</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Con nhà Trần Lý công ngư, Lưới chài nhưng cũng phong tư khác thường.</t>
+          <t>Thác cô nhờ có tôi hiền, Dẫu người hối chúc mà quyền chẳng sai.</t>
         </is>
       </c>
     </row>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Trăng già đưa mối tơ vương, Mới hay con tạo mở đường di duyên.</t>
+          <t>Cao Tông ba tuổi nối đời, Hiến Thành cư nhiếp trong ngoài đều yên.</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Họ Trần từ ấy nổi lên, Kết bè thích lý, dựng nền tiếm giai.</t>
+          <t>Di lưu còn muốn tiến hiền, Đem Trần Trung Tá thay quyền tán tương.</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Trần Tự Khánh ở phương ngoài, Đem quân Hải Ấp vào nơi đô thành.</t>
+          <t>Tiếc không dùng kẻ trung lương, Cao Tông hoang túng mọi đường ai can?</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Huệ Tông gặp bước gập ghềnh, Nhẹ ân mẫu hậu, nặng tình phu nhân.</t>
+          <t>Dấu xe quanh khắp giang san, Chính hình lỗi tiết, du quan quá thường.</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Lạng Châu xe đã Bắc tuần, Nửa đêm riêng với nàng Trần lẻn đi.</t>
+          <t>Lại thêm thổ mộc cung tường, Mua quan bán ngục nhiều đường riêng tây.</t>
         </is>
       </c>
     </row>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Gặp quân Tự Khánh rước về, Đương cơn gió bụi bốn bề chưa êm.</t>
+          <t>Nhạc Chiêm rầu rĩ khéo bầy, Những là tai biến từ này hiện ra.</t>
         </is>
       </c>
     </row>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Huệ Tông cuồng tật lại thêm, Khi ngày đứng múa khi đêm nằm dài.</t>
+          <t>Trâu đâu lên ngọn Am La, Thước đâu làm tổ góc nhà Kính Thiên.</t>
         </is>
       </c>
     </row>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Xuất gia lại muốn tu trai, Ngôi thiêng phó thác cho người đào thơ.</t>
+          <t>Bốn phương trộm cướp nổi lên, Quân Chiêm, người Tống xâm biên mấy kỳ.</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Đăng sơn bóng nhật đã mờ, Hai trăm mười sáu Lý cơ còn gì?</t>
+          <t>Vui chơi nào có biết gì, Thờ ơ phó chuyện an nguy mặc trời.</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Bỗng xui Trần Cảnh hiện vào hầu trong.</t>
+          <t>Quyền cương ngày một đổi dời, Phạm Du đã phản lại vời về kinh.</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Người yểu điệu, kẻ tư phong,</t>
+          <t>Bỉnh Di là kẻ trung thành, Nghe dèm mà nỡ gia hình cớ sao?</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Bén hơi rơm lửa, động phòng mưa mây.</t>
+          <t>Bởi ai gây việc oan cừu, Để cho Quách Bốc sấn vào kim giai.</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Vẩy nước chậu, vắt khăn tay,</t>
+          <t>Xe loan lánh chạy ra ngoài, Hoàng thân đế thích mỗi người một phương.</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Khi đêm đạp bóng, khi ngày ngồi chung.</t>
+          <t>Trừ quân đi đến Thiên Trường, Tình cờ lại gặp một nường tiểu thư.</t>
         </is>
       </c>
     </row>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Hoa đào đã dạn gió đông,</t>
+          <t>Con nhà Trần Lý công ngư, Lưới chài nhưng cũng phong tư khác thường.</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Vua tôi phận đẹp, vợ chồng duyên may.</t>
+          <t>Trăng già đưa mối tơ vương, Mới hay con tạo mở đường di duyên.</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Chiếu rồng ban xuống năm mây,</t>
+          <t>Họ Trần từ ấy nổi lên, Kết bè thích lý, dựng nền tiếm giai.</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Mừng rằng nữ chúa ngày nay có chồng.</t>
+          <t>Trần Tự Khánh ở phương ngoài, Đem quân Hải Ấp vào nơi đô thành.</t>
         </is>
       </c>
     </row>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Đông A tỏ mặt vừng hồng,</t>
+          <t>Huệ Tông gặp bước gập ghềnh, Nhẹ ân mẫu hậu, nặng tình phu nhân.</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Thái Tông cải hiệu Kiến Trung rõ ràng.</t>
+          <t>Lạng Châu xe đã Bắc tuần, Nửa đêm riêng với nàng Trần lẻn đi.</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Trần Thừa là Thái thượng hoàng,</t>
+          <t>Gặp quân Tự Khánh rước về, Đương cơn gió bụi bốn bề chưa êm.</t>
         </is>
       </c>
     </row>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Chuyên quyền thính đoán, gồm đường kinh luân.</t>
+          <t>Huệ Tông cuồng tật lại thêm, Khi ngày đứng múa khi đêm nằm dài.</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Soạn làm thông chế lễ văn,</t>
+          <t>Xuất gia lại muốn tu trai, Ngôi thiêng phó thác cho người đào thơ.</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Thuế điền đã định, số dân cũng tường.</t>
+          <t>Đăng sơn bóng nhật đã mờ, Hai trăm mười sáu Lý cơ còn gì?</t>
         </is>
       </c>
     </row>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Tướng thần mới đặt binh chương,</t>
+          <t>Chiêu Hoàng là phận nữ nhi, Phấn son gánh việc gian nguy được nào!</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Huyện châu sai kẻ khoa trường trị dân.</t>
+          <t>Xây vần cơ tạo khéo sao? Bỗng xui Trần Cảnh hiện vào hầu trong.</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Bạ đầu thi kẻ lại nhân,</t>
+          <t>Người yểu điệu, kẻ tư phong, Bén hơi rơm lửa, động phòng mưa mây.</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Hiệu quân Tứ thánh, Tứ thần mới chia.</t>
+          <t>Vẩy nước chậu, vắt khăn tay, Khi đêm đạp bóng, khi ngày ngồi chung.</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Hà phòng rày mới có đê,</t>
+          <t>Hoa đào đã dạn gió đông, Vua tôi phận đẹp, vợ chồng duyên may.</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Trăm quan áo mạo, rủ xe thêm tường.</t>
+          <t>Chiếu rồng ban xuống năm mây, Mừng rằng nữ chúa ngày nay có chồng.</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Việc ngoài đánh dẹp bốn phương,</t>
+          <t>Đông A tỏ mặt vừng hồng, Thái Tông cải hiệu Kiến Trung rõ ràng.</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Phó cho Thủ Độ chuyên đường trị quân.</t>
+          <t>Trần Thừa là Thái thượng hoàng, Chuyên quyền thính đoán, gồm đường kinh luân.</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Thượng hoàng phút đã từ trần,</t>
+          <t>Soạn làm thông chế lễ văn, Thuế điền đã định, số dân cũng tường.</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Thái Tông tuổi mới đến tuần mười hai.</t>
+          <t>Tướng thần mới đặt binh chương, Huyện châu sai kẻ khoa trường trị dân.</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Cao minh đã có tư trời,</t>
+          <t>Bạ đầu thi kẻ lại nhân, Hiệu quân Tứ thánh, Tứ thần mới chia.</t>
         </is>
       </c>
     </row>
@@ -9048,7 +9048,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Lại thêm Thủ Độ vẽ vời khôn ngoan.</t>
+          <t>Hà phòng rày mới có đê, Trăm quan áo mạo, rủ xe thêm tường.</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Sùng văn tô tượng Khổng, Nhan,</t>
+          <t>Việc ngoài đánh dẹp bốn phương, Phó cho Thủ Độ chuyên đường trị quân.</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Dựng nhà Quốc học, đặt quan Giám thần.</t>
+          <t>Thượng hoàng phút đã từ trần, Thái Tông tuổi mới đến tuần mười hai.</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Bảy năm một hội thanh vân,</t>
+          <t>Cao minh đã có tư trời, Lại thêm Thủ Độ vẽ vời khôn ngoan.</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Anh tài náo nức dần dần mới ra.</t>
+          <t>Sùng văn tô tượng Khổng, Nhan, Dựng nhà Quốc học, đặt quan Giám thần.</t>
         </is>
       </c>
     </row>
@@ -9133,7 +9133,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Trạng nguyên, bảng nhãn, thám hoa,</t>
+          <t>Bảy năm một hội thanh vân, Anh tài náo nức dần dần mới ra.</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Kẻ kinh, người trại cũng là tài danh.</t>
+          <t>Trạng nguyên, bảng nhãn, thám hoa, Kẻ kinh, người trại cũng là tài danh.</t>
         </is>
       </c>
     </row>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Lại thi Thái học chư sinh,</t>
+          <t>Lại thi Thái học chư sinh, Lại thi tam giáo chia rành ba khoa.</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Lại thi tam giáo chia rành ba khoa.</t>
+          <t>Thân chinh trỏ ngọn thiên qua, Chiêm Nam, Nguyên Bắc đều là dẹp tan.</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Thân chinh trỏ ngọn thiên qua,</t>
+          <t>Vì ai đạt gánh giang san, Mà đem cố chúa gia oan nỡ nào!</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Chiêm Nam, Nguyên Bắc đều là dẹp tan.</t>
+          <t>Chiêu Hoàng duyên trước làm sao? Gả đi bán lại, coi vào khó nghe!</t>
         </is>
       </c>
     </row>
@@ -9235,7 +9235,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Vì ai đạt gánh giang san,</t>
+          <t>Phép nhà chẳng sửa buồng the, Vợ anh sao nỡ đem về hậu cung.</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Mà đem cố chúa gia oan nỡ nào!</t>
+          <t>Bởi ai đầu mở hôn phong, Khiến nên một đạo khuê phòng thẹn riêng!</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Chiêu Hoàng duyên trước làm sao?</t>
+          <t>Thuần bôn dòng thói ngửa nghiêng, Họ dương lấy lẫn nào kiêng sợ gì.</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Thiên Thành công chúa lấy chồng, Về nhà Trần Quốc Tuấn, ban đầu được phong朱亭.</t>
+          <t>Thiên Thành công chúa vu quy, Sao Trần Quốc Tuấn cướp đi cho đành?</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Lễ vật dâng lên trời, điềm lành, muốn vua凌行 trung thành, tốt đẹp.</t>
+          <t>Sính nghi đem đến thiên đình, Thụy Bà lăng líu, Trung Thành ngẩn ngơ.</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Tà đạo mê hoặc, trừ bỏ, dọn dẹp, thờ Phật, Thích Ca.</t>
+          <t>Dị đoan mê hoặc khôn chừa, Chùa tô phật tượng, đình thờ Thích Ca.</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Tin vào phong thủy, lừa dối tà ma, tìm kiếm, chim hải âu, cung kính, đài cao.</t>
+          <t>Tin lời phong thủy khí tà, Đào sông đục núi cũng là nhọc thay!</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Lễ nghi sáng tỏ, yến tiệc mở ra, tỉnh táo, đội hình tan vỡ, rượu ngon, dơ bẩn, thở dài.</t>
+          <t>Lễ đâu yến ẩm quá say, Đội mo rót rượu, dan tay vui cười.</t>
         </is>
       </c>
     </row>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Kéo dài tiến lên, chiến tranh thịnh vượng, truyền bá, hủy hoại, tà ác, cung Bắc.</t>
+          <t>Ba mươi năm chán cuộc đời, Truyền cho con nối, ra ngoài bắc cung.</t>
         </is>
       </c>
     </row>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Thánh Tông hiếu thảo, bạn bè sâu sắc. Núi cao, ngược dòng, cửa sổ trong, đài thanh.</t>
+          <t>Thánh Tông hiếu hữu một dòng, Sớm hôm chầu chực, mát nồng thảnh thơi.</t>
         </is>
       </c>
     </row>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Anh kiệt, đẹp đẽ, thiền định, kỳ lạ, vẽ, khắc, đáng chạy, yến tiệc, vui vẻ, che phủ, phong ấn.</t>
+          <t>Anh em nệm cả gối dài, Sân trong yến lạc cõi ngoài ấm phong.</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Không có bài viết, truyền thụ pháp thuật, mưu đồ ác độc, báo thù, chiếu chỉ.</t>
+          <t>Một thiên truyền thụ phép lòng, Di mưu cho kẻ nối dòng ngày sau.</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Văn nhân ràng buộc, giảng giải, báo thù, tu sửa, ghi chép, kể lại, theo kinh điển.</t>
+          <t>Văn nho khuya sớm giảng cầu, Kẻ tu sử ký, người chầu kinh diên.</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Bạn bè, màu sắc, nghiêm túc, phục vụ, phòng thủ biên giới, quy định, quân đoàn, luyện tập, thuyền, chín cồn cát.</t>
+          <t>Bề ngoài nghiêm việc phòng biên, Kén quân đoàn luyện, tập thuyền Cửu Sa.</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Quyết tâm truyền lại, dấu vết, pháp thuật. Nhân Tông anh hùng, mở ra, quan lại, tài năng vui mừng.</t>
+          <t>Trao truyền theo lối phép nhà, Nhân Tông hùng lược lại là tài hơn.</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Sư tử, nguyên nhân, buồn bã, góa bụa, tham lam, tàn bạo, quân đội, nhanh chóng, chết, vạn, vẫn, kiên định, tranh giành.</t>
+          <t>Rợ Nguyên quen thói tham tàn, Quân năm mươi vạn, những toan tranh hành.</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Sắc lệnh, phái đi, đạo, tổng binh, Trần Quang, địch, các doanh, tiến vào địch.</t>
+          <t>Sắc sai Hưng Đạo tổng binh, Với Trần Quang Khải các dinh tiến vào.</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Chương Dương, mất trận, gió lớn. Cờ, bụi, cướp giáo, ẩn nấp, kiên cố, công lao.</t>
+          <t>Chương Dương một trận phong đào, Kìa ai cướp giáo ra vào có công?</t>
         </is>
       </c>
     </row>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Hàm ĐIỀU, mất trận, điều khiển, tụ tập. Cờ, bụi, cướp bóc, uy phong, truyền tụng.</t>
+          <t>Hàm Quan một trận ruổi giong, Kìa ai bắt giặc uy phong còn truyền?</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Giặc Nguyên, nhóm, ngạc nhiên, báo cáo, lấp đầy. Gây rối, ao, hộ tống, thuyền binh, quan lại, Bào.</t>
+          <t>Giặc Nguyên còn muốn báo đền, Mượn đường hộ tống binh thuyền lại sang.</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Bạch Đằng, mất, rơi, chiến trường, thân thể, nghỉ ngơi, đồng bằng, bao la, quan sát, ngập.</t>
+          <t>Bạch Đằng một cõi chiến tràng, Xương bày trắng đất, máu màng đỏ sông.</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Trần Hưng Đạo, anh hùng, Trần, mắt, mụn nhọt, lừa dối, công lao, mưu lược.</t>
+          <t>Trần Hưng Đạo đã anh hùng, Mà Trần Nhật Duật kể công cũng nhiều.</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Hoài Văn, tuổi, chúc mừng, chí cao, cờ, ghi công, tướng, quyết định, địch, lập công.</t>
+          <t>Hoài Văn tuổi trẻ chí cao, Cờ đề sáu chữ quyết vào lập công.</t>
         </is>
       </c>
     </row>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Trần Bình Trọng, cung kính, bãi chức, trung thành, học tập, ít, quỷ Nam, trống rỗng, biết, vua Bắc.</t>
+          <t>Trần Bình Trọng cũng là trung, Đành làm Nam quỷ, không lòng Bắc vương.</t>
         </is>
       </c>
     </row>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Đại bàng, nhóm, nghĩa, phá, ngựa, nghỉ ngơi, kiêu ngạo, voi rừng, ăn, cào, cung kính, kiêu ngạo.</t>
+          <t>Khuyển ưng còn nghĩa đá vàng, Yết Kiêu, Dã Tượng hai chàng cũng ghê!</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Mờ nhạt, lá ngọc, cành vàng, ủy thác, Trần Ích Tắc, che phủ, kỵ binh, chạy, đầu hàng.</t>
+          <t>Mà trong ngọc diệp kim chi, Lũ Trần Ích Tắc sao đi đầu hàng?</t>
         </is>
       </c>
     </row>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Vì lừa dối, biến cố, gấp bội, núi, oán thù, trung thành, tập hợp, nịnh hót, đẩy, xay, tro, mực.</t>
+          <t>Nhân khi biến cố vội vàng, Kẻ trung, người nịnh đôi đàng tỏ ra.</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Trùng hưng, quỷ, quan lại, núi sông, cùng nhau, gọi, thiên tướng, cung kính, tài năng khác thường, sinh ra.</t>
+          <t>Trùng hưng đem lại sơn hà, Đã hay thiên tướng cũng là tài sinh.</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Hạo nhiên, lừa dối, ý định, thanh bình, truyền ngôi, thái tử, khác, cưỡi ngựa, nằm trên mây.</t>
+          <t>Nước nhà khi ấy thanh bình, Truyền ngôi thái tử, lánh mình Ngọa Vân.</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Anh Tông, kế vị, sự nghiệp, Trần, tu sửa, văn đức, bên ngoài, cần cù, võ công.</t>
+          <t>Anh Tông nối giữ nghiệp Trần, Trong tu văn đức, ngoài cần vũ công.</t>
         </is>
       </c>
     </row>
@@ -9745,7 +9745,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Kiên cố, khuyên bảo, chống lại, ánh sáng, Đông cung, nước, mây, kiên cố, tập hợp, thuyền, cùng nhau, bút, mực.</t>
+          <t>Có châm để dạy Đông cung, Thủy Vân có tập vui cùng bút nghiên.</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Trống rỗng, đêm, Phật, tỉnh táo, thiền, cung kính, thành, không sai, hy vọng, mua, phía đông, gì.</t>
+          <t>Ví không mến phật, say thiền, Cũng nên một đứng vua hiền Đông A.</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Mệt mỏi, chưa, quan lại, xuất gia, Minh Tông, kế vị, buộc, cung kính, khác, hiền vương.</t>
+          <t>Quyện cần rồi lại xuất gia, Minh Tông kế thống cũng là hiền vương.</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Gần, thái, từ chức, phù hợp, pháp luật, thường, lật lại, trách mắng, một mình, nhìn, bay, kinh, biển, nghệ thuật.</t>
+          <t>Mười lăm năm giữ phép thường, Rạng nền nếp cũ, mở giường mối sau.</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Tiếc, trống rỗng, phân biệt, ngọc trai, chống lại, Chu, tà nịnh, ở, đầu, bậc, lớp.</t>
+          <t>Tiếc không biện biệt ngư châu, Để cho tà nịnh ở đầu giai ban.</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Khắc Chung, dệt, bóc lột, gian dối, quốc gia, bịt tai, che đậy, hào phóng, keo kiệt, tránh, lưỡi, ly.</t>
+          <t>Khắc Chung thêm dệt lời gian, Quốc Chân mắc phải tiếng oan thiệt mình.</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Huệ Tông, ít, tổn thất, ngọc, đẹp, kiểm nghiệm, sao, độ, vận hành, trống rỗng, sai lệch.</t>
+          <t>Hiến Tông làm máy lung linh, Nghiệm xem tinh độ vận hành không sai.</t>
         </is>
       </c>
     </row>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Đê đá, mua, tháp, ao, kim, chảy, thuận lợi, đất, kỹ thuật, đến, chất lỏng, đông.</t>
+          <t>Thạch đê mới đắp đường dài, Nước sông thuận lối về ngoài biển Đông.</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Thừa Bình, quan lại, giỏi, võ công, Đà Giang, xe ngựa, Nam Nhung, cờ hiệu.</t>
+          <t>Thừa bình lại hiếu vũ công, Đà Giang xa mã, Nam Nhung tinh kỳ.</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Trẫm, cánh tay, còn đói, đi theo, ngươi, hòa hợp, Chiêu, Khương, điều khiển, thuật, cung thủy.</t>
+          <t>Cổ quăng mấy kẻ truy tùy, Nhữ Hài, Chiêu Nghĩa đều về thủy cung.</t>
         </is>
       </c>
     </row>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Mặc Châu, kiên cố, chết, ghi công, tiếng xấu, ghi chép, sầu, đông, vết tích, tươi tốt.</t>
+          <t>Kiềm Châu có đá kỷ công, Oán dày vẻ triện, sầu đông ngấn rều.</t>
         </is>
       </c>
     </row>
@@ -9932,7 +9932,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Dụ Tông, phi tần, quan lại, thừa kế, đào, trẻ thơ, đài, anh hùng, kỳ lạ, quyền lực, dấu vết, Thượng Hoàng.</t>
+          <t>Dụ Tông em lại thừa diêu, Ngôi thay anh cả, quyền theo Thượng Hoàng.</t>
         </is>
       </c>
     </row>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Thượng thư, mua, đạt, tỉnh đường, đề hình, chuyển vận, chức vụ, thường, kiên cố, man rợ.</t>
+          <t>Thượng thư mới đặt tỉnh đường, Đề hình, chuyển vận chức thường có tên.</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>勸農差使屯田</t>
+          <t>勸農差使屯田，雲屯達鎮查船客人</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Khinh minh vào động Ky Mang,</t>
+          <t>Khuyến nông sai sứ đồn điền, Vân Đồn đặt trấn tra thuyền khách nhân.</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Tinh kỳ tan tác gió sương mịt mù.</t>
+          <t>Khu tào thống lĩnh cấm quân, Phong đoàn lại mới kén dần các đô.</t>
         </is>
       </c>
     </row>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Em là Phế Đế hôn ngu,</t>
+          <t>Uy thanh xa động biên ngu, Chiêm Thành Chế Mộ dâng đồ thổ nghi.</t>
         </is>
       </c>
     </row>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Chôn tiền giấu của như trò trẻ chơi.</t>
+          <t>Mong nhờ đưa lối về quê, Hay đâu gặp gió trở về luống công.</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Quý Ly quyền lấn trong ngoài,</t>
+          <t>Thượng Hoàng đã vắng mặt trong, Nào ai kiêng sợ mà lòng chẳng di?</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Buông lời sàm gián quên bài tôn thân.</t>
+          <t>Đền Song Quế, ao Thanh Trì, Muông chim hoa cỏ thiếu gì trò chơi!</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Truyền vời Phế Đế vào sân,</t>
+          <t>Trong cung cờ bạc chơi bời, Tiệc vui chuốc chén, trận cười leo dây.</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Lụa đào một tấm bể trần kết oan.</t>
+          <t>Đạo thường chẳng cẩn phòng vi, Chị em chung chạ loạn bề đại luân.</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Thuận Tông tuổi mọn tài hèn,</t>
+          <t>Truyền ngôi con đứa ưu nhân, Để Dương Nhật Lễ tiếm Trần dựng lên.</t>
         </is>
       </c>
     </row>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Ngôi không mà để chính quyền mặc ai.</t>
+          <t>Thói nhà bài hước đã quen, Tiếng hoà nhịp phách, hát chen cung đàn.</t>
         </is>
       </c>
     </row>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Phải chăng bởi tại mưu người,</t>
+          <t>Hiến Từ đã phải hàm oan, Trần Công mưu hở thân tàn cũng thương!</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Mà điềm trẫm triệu cơ trời lạ sao!</t>
+          <t>Nghệ Tông dòng dõi thiên hoàng, Đà Giang lánh dấu liệu đường khuất thân.</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Thượng Hoàng một giấc chiêm bao,</t>
+          <t>Tiềm mưu với kẻ tôn thần, Đem về xã tắc nhà Trần thủa xưa.</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Bạch kê, xích chuỷ ứng vào câu thơ.</t>
+          <t>Yêu phân đành đã tảo trừ, Cũng là nối một mối thừa lại sau.</t>
         </is>
       </c>
     </row>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Loạn trưng đã hiện từ giờ,</t>
+          <t>Tiếc sao một mực ưu nhu, Đông A từ ấy cơ đồ mới suy.</t>
         </is>
       </c>
     </row>
@@ -10221,7 +10221,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Mà đồ tứ phụ ai ngờ vẽ ra!</t>
+          <t>Giậu phên trống trải biên thuỳ, Giặc Chiêm giong ruổi đô kỳ xôn xao.</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Chim con đem gửi ác già,</t>
+          <t>Quý Ly quyền lấn trong ngoài, Buông lời sàm gián quên bài tôn thân.</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Chắc đâu phó thác hẳn là đắc nhân!</t>
+          <t>Duệ Tông hăm hở phục thù, Đánh Chiêm nào quản trì khu dặm trường.</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Quý Ly nhăm nhe vạc Trần,</t>
+          <t>Khinh minh vào động Ky Mang, Tinh kỳ tan tác gió sương mịt mù.</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Quyết dời kẻ chợ về gần An Tôn.</t>
+          <t>Em là Phế Đế hôn ngu, Chôn tiền giấu của như trò trẻ chơi.</t>
         </is>
       </c>
     </row>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Đã xui truyền vị cho con,</t>
+          <t>Quý Ly quyền lấn trong ngoài, Buông lời sàm gián quên bài tôn thân.</t>
         </is>
       </c>
     </row>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Ngọc Thanh lại kết oan hồn một dây.</t>
+          <t>Truyền vời Phế Đế vào sân, Lụa đào một tấm bể trần kết oan.</t>
         </is>
       </c>
     </row>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Gặp khi Thiếu Đế thơ ngây,</t>
+          <t>Thuận Tông tuổi mọn tài hèn, Ngôi không mà để chính quyền mặc ai.</t>
         </is>
       </c>
     </row>
@@ -10357,7 +10357,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Khát Chân, Trần Hãng đem ngày hợp mưu.</t>
+          <t>Phải chăng bởi tại mưu người, Mà điềm trẫm triệu cơ trời lạ sao!</t>
         </is>
       </c>
     </row>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Hội minh vừa mới lên lầu,</t>
+          <t>Thượng Hoàng một giấc chiêm bao, Bạch kê, xích chuỷ ứng vào câu thơ.</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Ba trăm đồ đảng cùng nhau hiệp tình.</t>
+          <t>Loạn trưng đã hiện từ giờ, Mà đồ tứ phụ ai ngờ vẽ ra!</t>
         </is>
       </c>
     </row>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Dùng dằng chưa kịp cất binh,</t>
+          <t>Chim con đem gửi ác già, Chắc đâu phó thác hẳn là đắc nhân!</t>
         </is>
       </c>
     </row>
@@ -10420,12 +10420,12 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>李聲聰騎護陳決邀仇幫術賊安孫</t>
+          <t>李聲聰騎護陳　決邀仇幫術賊安孫</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Hở cơ một phút tan tành như tro.</t>
+          <t>Quý Ly nhăm nhe vạc Trần, Quyết dời kẻ chợ về gần An Tôn.</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Quý Ly mới đổi họ Hồ,</t>
+          <t>Đã xui truyền vị cho con, Ngọc Thanh lại kết oan hồn một dây.</t>
         </is>
       </c>
     </row>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Quốc danh là hiệu Đại Ngu chương hoàng.</t>
+          <t>Gặp khi Thiếu Đế thơ ngây, Khát Chân, Trần Hãng đem ngày hợp mưu.</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Truyền ngôi con cả Hán Thương,</t>
+          <t>Hội minh vừa mới lên lầu, Ba trăm đồ đảng cùng nhau hiệp tình.</t>
         </is>
       </c>
     </row>
@@ -10493,7 +10493,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Tự xưng là Thái Thượng Hoàng ở trong.</t>
+          <t>Dùng dằng chưa kịp cất binh, Hở cơ một phút tan tành như tro.</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Sai người dâng biểu cầu phong,</t>
+          <t>Quý Ly mới đổi họ Hồ, Quốc danh là hiệu Đại Ngu chương hoàng.</t>
         </is>
       </c>
     </row>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Dối Minh xin để nối dòng quốc quân.</t>
+          <t>Truyền ngôi con cả Hán Thương, Tự xưng là Thái Thượng Hoàng ở trong.</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Nguyễn Khang giả tiếng họ Trần,</t>
+          <t>Sai người dâng biểu cầu phong, Dối Minh xin để nối dòng quốc quân.</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Sang Minh xin lấy viện quân đưa về.</t>
+          <t>Nguyễn Khang giả tiếng họ Trần, Sang Minh xin lấy viện quân đưa về.</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Chi Lăng nghe động cổ bề,</t>
+          <t>Chi Lăng nghe động cổ bề, Lý Bân, Mộc Thạnh trỏ cờ tới nơi.</t>
         </is>
       </c>
     </row>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Lý Bân, Mộc Thạnh trỏ cờ tới nơi.</t>
+          <t>Quân Minh nhân thế đuổi dài, Nhị Hồ mới chạy ra ngoài phương xa.</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Quân Minh nhân thế đuổi dài,</t>
+          <t>Núi Cao Vọng, bến Kỳ La, Đường cùng phải bắt cũng là trời xui!</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Nhị Hồ mới chạy ra ngoài phương xa.</t>
+          <t>Tôn vinh kể được mấy hơi, Sáu năm tiếm vị, muôn đời ô danh.</t>
         </is>
       </c>
     </row>
@@ -10641,12 +10641,12 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>季聲罪惡色寧。</t>
+          <t>季聲罪惡色寧。來墨吏返歇明凶殘</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Người trí thức, kẻ tài danh, Nam Sơn đào độn, Bắc Đình câu lưu.</t>
+          <t>Quý Ly tội ác đã đành, Rồi ra lại gặp người Minh hung tàn.</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Thuế tơ, thuế thóc tham cầu, Mỏ vàng mỏ bạc, trưng thâu cũng nhiều;</t>
+          <t>Chia phủ, huyện, đặt quân quan, Cỏ cây đều phải lầm than hội này.</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10680,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Săn bạch tượng, hái hồ tiêu, Mò châu, cấm muối, lắm điều hại dân.</t>
+          <t>Dòng Trần chưa dứt một dây, Triệu Cơ còn rắp ra tay đồ hồi.</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Mới hay cơ tạo xoay vần, Có khi bĩ cực đến tuần thái lai.</t>
+          <t>Lại phù Giản Định lên ngôi, Cảnh Chân, Đặng Tất vua tôi hiệp tình.</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Thiếu chi hào kiệt trong đời, Non xanh nước bạc có người kinh luân.</t>
+          <t>Mở cờ đánh với quân Minh, Phá đồn Cổ Lộng, đốt thành Bô Cô.</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Lương Giang trời mở chân nhân, Vua Lê Thái Tổ ứng tuần mới ra.</t>
+          <t>Ví hay nhân thế tráng khu, May ra khôi phục cơ đồ cũng nên.</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10748,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Lam Sơn khởi nghĩa từ nhà, Phong trần lắm lúc kể đà gian nguy.</t>
+          <t>Trùng hưng cơ tự chưa bền, Bỗng không đem kẻ tướng hiền giết đi.</t>
         </is>
       </c>
     </row>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Lạc Xuyên đầu giết Mã Kỳ, Nghệ, Thanh một giải thu về bản chương.</t>
+          <t>Cho nên hào kiệt bạn ly, Cánh vây không có, còn gì mà mong?</t>
         </is>
       </c>
     </row>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Chia quân kinh lược mọi đường, Hai kinh đã định, bốn phương cũng bình.</t>
+          <t>Tướng môn lại có con dòng, Đặng Dung, Cảnh Dị mới cùng hợp mưu.</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Vương Thông bền giữ cô thành, Viện binh hai đạo Bắc Đình tiếp sang.</t>
+          <t>Một hai quyết chí đồng cừu, Cùng đem binh sĩ ruổi vào Chi La.</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Trời Nam đã có chủ trương, Mà cơ chế thắng miếu đường cũng tinh.</t>
+          <t>Lại tìm dòng dõi Trần gia, Tôn phù Quý Khoáng, ấy là Trùng Quang.</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Chi Lăng các đạo phục binh, Liễu Thăng, Mộc Thạnh liều mình nẻo xa.</t>
+          <t>Đem binh vào phủ Thiên Trường, Đón vua Giản Định về đàng Nghệ An.</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Vương Thông thế túng cầu hòa, Quyền phong Trần Cảo gọi là Quốc Vương.</t>
+          <t>Cùng nhau gánh việc gian nan, Hạ Hồng tế ngựa Bình Than đỗ thuyền.</t>
         </is>
       </c>
     </row>
@@ -10867,7 +10867,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Ngôi thiêng sao xứng tài thường, Trần công trẫm sát để nhường long phi.</t>
+          <t>Quân Minh cố giữ thành bền, Bỗng đâu Trương Phụ băng miền lại sang.</t>
         </is>
       </c>
     </row>
@@ -10879,12 +10879,12 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>自欺簡定投降。</t>
+          <t>自欺簡定投降。人安坦覲重光吏術</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Thuận Thiên niên hiệu cải đề, Non sông mới thuộc về Lê từ rầy.</t>
+          <t>Từ khi Giản Định đầu hàng, Nghệ An đất cũ Trùng Quang lại về.</t>
         </is>
       </c>
     </row>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Quan danh, quân hiệu mới thay, Bản đồ đổi lại huyện này, phủ kia.</t>
+          <t>Quân Minh chiếm giữ Bắc Kỳ, Vua Trần lánh ở Nam Thùy một nơi.</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Dựng nhà học, mở khoa thi, Triều nghi, quốc luật một kỳ giảng tu.</t>
+          <t>Đặng Dung, Cảnh Dị mấy người, Thế cùng dù có tướng tài cũng thua.</t>
         </is>
       </c>
     </row>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Mười năm khai sáng cơ đồ, Sáu năm bình trị qui mô cũng tường.</t>
+          <t>Trước sau mười bốn đời vua, Một trăm tám chục xuân thu chưa chầy.</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Chín năm nối nghiệp cơ cần, Viễn di mến đức, cường thần sợ uy.</t>
+          <t>Quý Ly tiếm thiết tội lây muôn đời.</t>
         </is>
       </c>
     </row>
@@ -10964,12 +10964,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>搔戈臘樹效遨。</t>
+          <t>搔戈臘樹效遨。笑墨朱侵姦同榮稱</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Tuổi xanh hoang túng nhiều bề, Vườn xuân lắm lúc say mê vì tình.</t>
+          <t>Chẳng qua lịch đổi, số dời, Xui ra cho đứa gian hồi nhuốm tay.</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Đông tuần về đến Bắc Ninh, Riêng tình Thị Lộ quên mình bởi ai?</t>
+          <t>Cốc Lăng trời khéo đổi thay, Giận riêng bờ cõi từ rầy thuộc Minh.</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Nhân Tông tuổi mới lên hai, Quyền trong mẫu hậu chính ngoài thần công.</t>
+          <t>Người trí thức, kẻ tài danh, Nam Sơn đào độn, Bắc Đình câu lưu.</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Mười năm một hội đại đồng, Văn mô rạng trước, vũ công phục ngoài.</t>
+          <t>Thuế tơ, thuế thóc tham cầu, Mỏ vàng mỏ bạc, trưng thâu cũng nhiều;</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Đánh Chiêm Thành, bắt Bí Cai, Đồ Bàn, Cổ Lũy các nơi hướng tiền.</t>
+          <t>Săn bạch tượng, hái hồ tiêu, Mò châu, cấm muối, lắm điều hại dân.</t>
         </is>
       </c>
     </row>
@@ -11054,7 +11054,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Diên Ninh vừa độ trung niên, Nhân Tông tuổi cả mới lên ngự trào.</t>
+          <t>Mới hay cơ tạo xoay vần, Có khi bĩ cực đến tuần thái lai.</t>
         </is>
       </c>
     </row>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Nghi Dân cốt nhục nỡ nào, Tiềm mưu đêm bắc thang vào nội cung.</t>
+          <t>Thiếu chi hào kiệt trong đời, Non xanh nước bạc có người kinh luân.</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Mẹ con đương thuở giấc nồng, Hồn tiên liều với gian hùng một tay.</t>
+          <t>Lương Giang trời mở chân nhân, Vua Lê Thái Tổ ứng tuần mới ra.</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Nghi Dân chuyên tiếm từ đây, Lương tâm đã dứt: ác cai lại nồng.</t>
+          <t>Lam Sơn khởi nghĩa từ nhà, Phong trần lắm lúc kể đà gian nguy.</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Đình thần nghị tội truất phong, Rước Gia Vương ngự đền rồng cải nguyên.</t>
+          <t>Lạc Xuyên đầu giết Mã Kỳ, Nghệ, Thanh một giải thu về bản chương.</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Thánh Tông cốt cách thần tiên, Lại thêm kinh thánh truyện hiền gia công.</t>
+          <t>Chia quân kinh lược mọi đường, Hai kinh đã định, bốn phương cũng bình.</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11156,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Quốc âm, Đường luật tinh thông, Thiên văn, toán pháp, binh nhung cũng tường.</t>
+          <t>Vương Thông bền giữ cô thành, Viện binh hai đạo Bắc Đình tiếp sang.</t>
         </is>
       </c>
     </row>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Tài cao mại, đức thù thường, Kiến văn đã rộng, thi trương cũng già.</t>
+          <t>Trời Nam đã có chủ trương, Mà cơ chế thắng miếu đường cũng tinh.</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Ba năm lại mở một khoa, Tân hưng đại tị theo nhà Thành Châu.</t>
+          <t>Chi Lăng các đạo phục binh, Liễu Thăng, Mộc Thạnh liều mình nẻo xa.</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Nhạc âm, lễ chế giảng cầu, Quan danh, phục sắc theo trào triều Đại Minh.</t>
+          <t>Vương Thông thế túng cầu hòa, Quyền phong Trần Cảo gọi là Quốc Vương.</t>
         </is>
       </c>
     </row>
@@ -11224,7 +11224,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Mở Quảng Nam, đặt Trấn Ninh, Đề phong muôn dặm uy linh ai bì.</t>
+          <t>Ngôi thiêng sao xứng tài thường, Trần công trẫm sát để nhường long phi.</t>
         </is>
       </c>
     </row>
@@ -11241,7 +11241,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Kỷ công núi có đá bia, Thi văn các tập Thần Khuê còn truyền.</t>
+          <t>Thuận Thiên niên hiệu cải đề, Non sông mới thuộc về Lê từ rầy.</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Thừa diêu lại có con hiền, Hiến Tông nhân thứ rạng nền tiền huy.</t>
+          <t>Quan danh, quân hiệu mới thay, Bản đồ đổi lại huyện này, phủ kia.</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Túc Tông số lẻ vận suy, Để cho Uy Mục thứ chi nối đời.</t>
+          <t>Dựng nhà học, mở khoa thi, Triều nghi, quốc luật một kỳ giảng tu.</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Đêm ngày tửu sắc vui chơi, Tin bè ngoại thích hại người từ thân.</t>
+          <t>Mười năm khai sáng cơ đồ, Sáu năm bình trị qui mô cũng tường.</t>
         </is>
       </c>
     </row>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Văn Lang xướng suất phủ quân, Thần Phù nổi áng phong trần một phương.</t>
+          <t>Thái Tông rộng mở khoa trường, Lập bia Tiến Sĩ trọng đường tư văn.</t>
         </is>
       </c>
     </row>
@@ -11321,12 +11321,12 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>簡修拱派銀潢創溝合貝文郎結警</t>
+          <t>孕茄孝鄉科試朝傴國律沒期講修 近輒開創基圖勸解平治規模拱詳 太宗穫覲科場立碑進士重塘斯文</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Giản Tu cũng phái Ngân Hoàng, Vào Thanh hợp với Văn Lang kết thề.</t>
+          <t>Mười năm khai sáng cơ đồ, Sáu năm bình trị qui mô cũng tường. Thái Tông rộng mở khoa trường, Lập bia Tiến Sĩ trọng đường tư văn. Chín năm nối nghiệp cơ cần, Viễn di mến đức, cường thần sợ uy.</t>
         </is>
       </c>
     </row>
@@ -11338,12 +11338,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>鬼兵圍逼都畿鬼王屈麵權衛豬王</t>
+          <t>於解踐業基勤造夷晚德彊臣悼威</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Đem binh vây bức đô kỳ, Quỷ Vương khuất mặt, quyền về Trư Vương.</t>
+          <t>Tuổi xanh hoang túng nhiều bề, Vườn xuân lắm lúc say mê vì tình.</t>
         </is>
       </c>
     </row>
@@ -11355,12 +11355,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>吏強淫虐驕荒累間斬屋宮牆奢華</t>
+          <t>歲擇荒緝韃交圖春穀張醒迷術情</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Lại càng dâm ngược kiêu hoang, Trăm gian, nghìn nóc, cung tường xa hoa.</t>
+          <t>Đông tuần về đến Bắc Ninh, Riêng tình Thị Lộ quên mình bởi ai?</t>
         </is>
       </c>
     </row>
@@ -11372,12 +11372,12 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>吏彊利削戶眾梗鬱萼玉諭眾彫零</t>
+          <t>東巡術禰北寧積共氏路瘡翁黜埃</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Lại càng bác tước họ nhà, Cành vàng lá ngọc đều là điêu linh.</t>
+          <t>Nhân Tông tuổi mới lên hai, Quyền trong mẫu hậu chính ngoài thần công.</t>
         </is>
       </c>
     </row>
@@ -11389,12 +11389,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>方邪陳嵩弄兵 𠄌馳惟愜愜情叛君</t>
+          <t>仁宗歲買鐵仁權懿母后政外臣工</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Phương ngoài Trần Cảo lộng binh, Mà trong Duy Sản mống tình bạn quân.</t>
+          <t>Mười năm một hội đại đồng, Văn mô rạng trước, vũ công phục ngoài.</t>
         </is>
       </c>
     </row>
@@ -11406,12 +11406,12 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>恍兵忿禪北宸碧溝沒人象塵黝埃</t>
+          <t>近辭沒會大同文謨翻耀武功服郊</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Đem binh vào cửa Bắc Thần, Bích Câu một phút mông trần bởi ai.</t>
+          <t>Đánh Chiêm Thành, bắt Bí Cai, Đồ Bàn, Cổ Lũy các nơi hướng tiền.</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>經黎歎缶拊箳默竊惟懐建影主張</t>
+          <t>打占城扒貢諒。閤樂古壘各尼向前</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Giềng Lê khi đã đổi dời, Mặc tay Duy Sản đặt người chủ trương.</t>
+          <t>Diên Ninh vừa độ trung niên, Nhân Tông tuổi cả mới lên ngự trào.</t>
         </is>
       </c>
     </row>
@@ -11440,12 +11440,12 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>奄尊緝穆懿王。吏謀扶立昭皇據輿</t>
+          <t>庭寧效度中年。仁宗歲奇員蓮御朝</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Đã tôn con Mục Ý Vương, Lại mưu phù lập Chiêu Hoàng cờ sao?</t>
+          <t>Nghi Dân cốt nhục nỡ nào, Tiềm mưu đêm bắc thang vào nội cung.</t>
         </is>
       </c>
     </row>
@@ -11457,12 +11457,12 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>市城鈴鼓擊鼓吏盜車駕騷紛撲西</t>
+          <t>宜民骨肉女帝濡謀賭牝湯飲內宮</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Thị thành vừa lúc xôn xao, Lại đưa xa giá ruổi vào cõi Tây.</t>
+          <t>Mẹ con đương thuở giấc nồng, Hồn tiên liều với gian hùng một tay.</t>
         </is>
       </c>
     </row>
@@ -11474,12 +11474,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>恙歪去疾買啗折惟瘧吏擾麵賊陳</t>
+          <t>疑鬼當課職農塊仙料貝姦雄沒穢</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Lòng trời khứ tật mới hay, Giết Duy Sản lại mượn tay giặc Trần.</t>
+          <t>Nghi Dân chuyên tiếm từ đây, Lương tâm đã dứt: ác cai lại nồng.</t>
         </is>
       </c>
     </row>
@@ -11491,12 +11491,12 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>將木群固陳真月江據貝賊陳余番</t>
+          <t>宜民專潛自低良心每揔惡荊吏燼</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Tướng tài còn có Trần Chân, Nguyệt Giang chống với giặc Trần mấy phen. Ngụy Trần vào cứ Đồng Nguyên, Truyền ngôi con cả, cải nguyên Tuyên Hòa.</t>
+          <t>Đình thần nghị tội truất phong, Rước Gia Vương ngự đền rồng cải nguyên.</t>
         </is>
       </c>
     </row>
@@ -11508,12 +11508,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>偽陳尅據同源傳龜琨奇改元宣和</t>
+          <t>廷臣擬罪黜封遵嘉王御覲蠅改元</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Cạo đầu vào cửa Thích Già, Y quy nương bóng Di Đà độ thân.</t>
+          <t>Thánh Tông cốt cách thần tiên, Lại thêm kinh thánh truyện hiền gia công.</t>
         </is>
       </c>
     </row>
@@ -11525,12 +11525,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>盛頭尒闡釋迦依飯娘釋跡陀度身</t>
+          <t>聖宗骨格神仙吏添經聖傳貲加功</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Trời sinh ra hội phong trần, Mạc Đăng Dung lại cường thần nổi lên.</t>
+          <t>Quốc âm, Đường luật tinh thông, Thiên văn, toán pháp, binh nhung cũng tường.</t>
         </is>
       </c>
     </row>
@@ -11542,12 +11542,12 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>至生靈會風塵莫登庸夷彊臣沒蓮</t>
+          <t>國音唐律精通天文算法兵戎棋譜</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Trần Chân tay giữ binh quyền, Trên ngờ thế cả, dưới ghen tài lành.</t>
+          <t>Tài cao mại, đức thù thường, Kiến văn đã rộng, thi trương cũng già.</t>
         </is>
       </c>
     </row>
@@ -11559,12 +11559,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>陳真麵將兵權連疑芳奇鄴愷才屢</t>
+          <t>才高邁德殊常見聞垂績施張拱魏</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Tiếc thay có tướng can thành, Tin sàm mà nỡ dứt tình chẳng tha.</t>
+          <t>Ba năm lại mở một khoa, Tân hưng đại tị theo nhà Thành Châu.</t>
         </is>
       </c>
     </row>
@@ -11576,12 +11576,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>惜台固將千城信籠麻女揔情極他</t>
+          <t>匹解吏翻沒科寶興大比號茄成周</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Vì ai gây nỗi oan gia, Để cho Nguyễn Kính lại ra báo thù.</t>
+          <t>Nhạc âm, lễ chế giảng cầu, Quan danh, phục sắc theo trào triều Đại Minh.</t>
         </is>
       </c>
     </row>
@@ -11593,12 +11593,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>為埃醮內冤家抵朱阮敬吏墨報讐</t>
+          <t>象音礼制講求，宦各服色朝跪大明</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Kinh sư khói lửa mịt mù, Xe loan ra cõi Bảo Châu tỵ trần.</t>
+          <t>Mở Quảng Nam, đặt Trấn Ninh, Đề phong muôn dặm uy linh ai bì.</t>
         </is>
       </c>
     </row>
@@ -11610,12 +11610,12 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>京師婉煒靈霧車鑾墨煥宝州避塵</t>
+          <t>翔廣南建鎮寧，提封詞跋威靈埃及</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Nguyễn Sư cũng đảng nghịch thần, Nửa năm phù lập hai lần quốc vương.</t>
+          <t>Mở Quảng Nam, đặt Trấn Ninh, Đề phong muôn dặm uy linh ai bì.</t>
         </is>
       </c>
     </row>
@@ -11627,12 +11627,12 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>阮瑯拱黨逆臣婉辭扶立仁各國王</t>
+          <t>紀功崗固磎碑詩文各集宸奎群傳</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Ngàn Tây một cõi chiến trường, Phó cho Mạc Súy sửa sang một mình.</t>
+          <t>Kỷ công núi có đá bia, Thi văn các tập Thần Khuê còn truyền.</t>
         </is>
       </c>
     </row>
@@ -11644,12 +11644,12 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>岸西沒墜戰場付朱莫師折郵沒斂</t>
+          <t>承桃吏固混貲憲宗仁恕襃坪前微</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Đăng Dung cậy có công danh, Thuyền rồng, tán phượng lộng hành sợ chi.</t>
+          <t>Thừa diêu lại có con hiền, Hiến Tông nhân thứ rạng nền tiền huy.</t>
         </is>
       </c>
     </row>
@@ -11661,12 +11661,12 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>登庸惄固功名船蠱傘鳳弄行慒忽</t>
+          <t>肅宗效進運衰抵朱威穆次支燉荒</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Chiêu Tông gặp lúc hiềm nghi, Nửa đêm lẻn bước chạy về Tây phương.</t>
+          <t>Túc Tông số lẻ vận suy, Để cho Uy Mục thứ chi nối đời.</t>
         </is>
       </c>
     </row>
@@ -11678,12 +11678,12 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>昭宗返張嫌疑婢張蹤馳發術西方</t>
+          <t>眩暘酒色恆邀。陰笈怨戚害歇慈親</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Đăng Dung lại lập Cung Hoàng, Hành cung tạm trú Hải Dương cõi ngoài.</t>
+          <t>Đêm ngày tửu sắc vui chơi, Tin bè ngoại thích hại người từ thân.</t>
         </is>
       </c>
     </row>
@@ -11695,12 +11695,12 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>登庸更立泰皇。行宮暫住海陽境外</t>
+          <t>文郎倡卒府軍神符沒盜風塵沒方</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Xe loan về đến kinh đài, Sẵn sàng thiền chiếu ép bài sách phong.</t>
+          <t>Văn Lang xướng suất phủ quân, Thần Phù nổi áng phong trần một phương.</t>
         </is>
       </c>
     </row>
@@ -11712,12 +11712,12 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>順天年號改題嶽淹買屬術黎自罰</t>
+          <t>簡修拱派銀潢創溝合貝文郎結警</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Họa tâm từ ấy càng nồng, Lương Châu Tây Nội cam lòng cho đang.</t>
+          <t>Giản Tu cũng phái Ngân Hoàng, Vào Thanh hợp với Văn Lang kết thề.</t>
         </is>
       </c>
     </row>
@@ -11729,12 +11729,12 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>官名單號買台版圖樹吏縣冠府箕</t>
+          <t>鬼兵圍逼都畿鬼王屈麵權衛豬王</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Mạc rầy rõ mặt tiếm cường, Thăng Long truyền nước, Nghi Dương dựng nhà.</t>
+          <t>Đem binh vây bức đô kỳ, Quỷ Vương khuất mặt, quyền về Trư Vương.</t>
         </is>
       </c>
     </row>
@@ -11746,12 +11746,12 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>孕茄孝鄉科試朝傴國律沒期講修</t>
+          <t>吏強淫虐驕荒累間斬屋宮牆奢華</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Dỗ người lấy vẻ vinh hoa, Nhưng lòng trung nghĩa ai mà sá theo.</t>
+          <t>Lại càng dâm ngược kiêu hoang, Trăm gian, nghìn nóc, cung tường xa hoa.</t>
         </is>
       </c>
     </row>
@@ -11763,12 +11763,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>近輒開創基圖勸解平治規模拱詳</t>
+          <t>吏彊利削戶眾梗鬱萼玉諭眾彫零</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Cầu phong sai sứ Bắc triều, Dâng vàng, nộp đất nhiều điều dối Minh.</t>
+          <t>Lại càng bác tước họ nhà, Cành vàng lá ngọc đều là điêu linh.</t>
         </is>
       </c>
     </row>
@@ -11780,12 +11780,12 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>太宗穫覲科場立碑進士重塘斯文</t>
+          <t>方邪陳嵩弄兵 𠄌馳惟愜愜情叛君</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Lê thần có kẻ trung trinh, Trịnh Ngung sang đến Bắc đình tỏ kêu.</t>
+          <t>Phương ngoài Trần Cảo lộng binh, Mà trong Duy Sản mống tình bạn quân.</t>
         </is>
       </c>
     </row>
@@ -11797,12 +11797,12 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>於解踐業基勤造夷晚德彊臣悼威</t>
+          <t>恍兵忿禪北宸碧溝沒人象塵黝埃</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Minh tham lễ hậu của nhiều, Phụ tình trung nghĩa, quên điều thị phi.</t>
+          <t>Đem binh vào cửa Bắc Thần, Bích Câu một phút mông trần bởi ai.</t>
         </is>
       </c>
     </row>
@@ -11814,12 +11814,12 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>歲擇荒緝韃交圖春穀張醒迷術情</t>
+          <t>經黎歎缶拊箳默竊惟懐建影主張</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Đăng Dung thỏa chước gian khi, Tuổi cao rồi lại truyền về Đăng Doanh.</t>
+          <t>Giềng Lê khi đã đổi dời, Mặc tay Duy Sản đặt người chủ trương.</t>
         </is>
       </c>
     </row>
@@ -11831,12 +11831,12 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>東巡術禰北寧積共氏路瘡翁黜埃</t>
+          <t>奄尊緝穆懿王。吏謀扶立昭皇據輿</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Mã Giang đầu xướng nghĩa thanh, Gần xa đâu chẳng nức tình cần vương.</t>
+          <t>Đã tôn con Mục Ý Vương, Lại mưu phù lập Chiêu Hoàng cờ sao?</t>
         </is>
       </c>
     </row>
@@ -11848,12 +11848,12 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>仁宗歲買鐵仁權懿母后政外臣工</t>
+          <t>市城鈴鼓擊鼓吏盜車駕騷紛撲西</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Được thua mấy trận chiến trường, Nghìn thu tiết nghĩa đá vàng lưu danh.</t>
+          <t>Thị thành vừa lúc xôn xao, Lại đưa xa giá ruổi vào cõi Tây.</t>
         </is>
       </c>
     </row>
@@ -11865,12 +11865,12 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>近辭沒會大同文謨翻耀武功服郊</t>
+          <t>恙歪去疾買啗折惟瘧吏擾麵賊陳</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Cành Lê có độ tái vinh, Xui nên tá mệnh trời sinh thánh hiền.</t>
+          <t>Lòng trời khứ tật mới hay, Giết Duy Sản lại mượn tay giặc Trần.</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>打占城扒貢諒。閤樂古壘各尼向前</t>
+          <t>將木群固陳真月江據貝賊陳余番</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Đức vua Triệu Tổ ta lên, Cất quân phù nghĩa giúp nền trung hưng.</t>
+          <t>Tướng tài còn có Trần Chân, Nguyệt Giang chống với giặc Trần mấy phen.</t>
         </is>
       </c>
     </row>
@@ -11899,12 +11899,12 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>庭寧效度中年。仁宗歲奇員蓮御朝</t>
+          <t>偽陳尅據同源傳龜琨奇改元宣和</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Sầm Châu ỷ thế nguồn rừng, Mười năm khai thác mấy từng nước non.</t>
+          <t>Ngụy Trần vào cứ Đồng Nguyên, Truyền ngôi con cả, cải nguyên Tuyên Hòa.</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>宜民骨肉女帝濡謀賭牝湯飲內宮</t>
+          <t>盛頭尒闡釋迦依飯娘釋跡陀度身</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Dù khi đỉnh tộ suy mòn, Cương trù chưa nát vẫn còn tôn Lê.</t>
+          <t>Cạo đầu vào cửa Thích Già, Y quy nương bóng Di Đà độ thân.</t>
         </is>
       </c>
     </row>
@@ -11933,12 +11933,12 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>疑鬼當課職農塊仙料貝姦雄沒穢</t>
+          <t>至生靈會風塵莫登庸夷彊臣沒蓮</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Trang Tông lưu lạc tìm về, Chia binh Thúy Đạn, mở cờ Ai Lao.</t>
+          <t>Trời sinh ra hội phong trần, Mạc Đăng Dung lại cường thần nổi lên.</t>
         </is>
       </c>
     </row>
@@ -11950,12 +11950,12 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>宜民專潛自低良心每揔惡荊吏燼</t>
+          <t>陳真麵將兵權連疑芳奇鄴愷才屢</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Lôi Dương một trận binh giao, Phá tan nghịch đảng tiến vào Nghệ An.</t>
+          <t>Trần Chân tay giữ binh quyền, Trên ngờ thế cả, dưới ghen tài lành.</t>
         </is>
       </c>
     </row>
@@ -11967,12 +11967,12 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>廷臣擬罪黜封遵嘉王御覲蠅改元</t>
+          <t>惜台固將千城信籠麻女揔情極他</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Cỏ hoa mừng rước xe loan, Thổ hào ứng nghĩa, dân gian nức lòng.</t>
+          <t>Tiếc thay có tướng can thành, Tin sàm mà nỡ dứt tình chẳng tha.</t>
         </is>
       </c>
     </row>
@@ -11984,12 +11984,12 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>聖宗骨格神仙吏添經聖傳貲加功</t>
+          <t>為埃醮內冤家抵朱阮敬吏墨報讐</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Tây Đô quét sạch bụi hồng, Dặm tràng thẳng trỏ ngọn đòng tràng khu.</t>
+          <t>Vì ai gây nỗi oan gia, Để cho Nguyễn Kính lại ra báo thù.</t>
         </is>
       </c>
     </row>
@@ -12001,12 +12001,12 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>阮瑯拱黨逆臣婉辭扶立仁各國王</t>
+          <t>京師婉煒靈霧車鑾墨煥宝州避塵</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>阮郎 cùng đảng nghịch thần, oán từ dẹp loạn, lập vua mới lên.</t>
+          <t>Kinh sư khói lửa mịt mù, Xe loan ra cõi Bảo Châu tỵ trần.</t>
         </is>
       </c>
     </row>
@@ -12018,12 +12018,12 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>岸西沒墜戰場付朱莫師折郵沒斂</t>
+          <t>阮瑯拱黨逆臣婉辭扶立仁各國王</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Bờ cõi tan tác chiến trường, Mạc tan, Trịnh lại, thu đường về dinh.</t>
+          <t>Nguyễn Sư cũng đảng nghịch thần, Nửa năm phù lập hai lần quốc vương.</t>
         </is>
       </c>
     </row>
@@ -12035,12 +12035,12 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>登庸惄固功名船蠱傘鳳弄行慒忽</t>
+          <t>岸西沒墜戰場付朱莫師折郵沒斂</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Đăng Dung lòng những tính mưu, Công danh sự nghiệp, mờ như sương tan.</t>
+          <t>Ngàn Tây một cõi chiến trường, Phó cho Mạc Súy sửa sang một mình.</t>
         </is>
       </c>
     </row>
@@ -12052,12 +12052,12 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>昭宗返張嫌疑婢張蹤馳發術西方</t>
+          <t>登庸惄固功名船蠱傘鳳弄行慒忽</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Chiêu Tông về, Trương nghi kỵ, Bày tôi Trương lại, chạy về phương Tây.</t>
+          <t>Đăng Dung cậy có công danh, Thuyền rồng, tán phượng lộng hành sợ chi.</t>
         </is>
       </c>
     </row>
@@ -12069,12 +12069,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>登庸更立泰皇。行宮暫住海陽境外</t>
+          <t>昭宗返張嫌疑婢張蹤馳發術西方</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Đăng Dung lập Thái Hoàng, vua mới, Cung điện tạm trú, ngoài Hãi Dương.</t>
+          <t>Chiêu Tông gặp lúc hiềm nghi, Nửa đêm lẻn bước chạy về Tây phương.</t>
         </is>
       </c>
     </row>
@@ -12086,12 +12086,12 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>車盡衛鍊京臺產麻禪詔押碑冊封</t>
+          <t>登庸更立泰皇。行宮暫住海陽境外</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Xe ngựa đầy đường, vệ binh nghiêm, Lập vua, ban chiếu, sách phong vua.</t>
+          <t>Đăng Dung lại lập Cung Hoàng, Hành cung tạm trú Hải Dương cõi ngoài.</t>
         </is>
       </c>
     </row>
@@ -12103,12 +12103,12 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>禍心自意強驟良州西內甘悉朱當</t>
+          <t>車盡衛鍊京臺產麻禪詔押碑冊封</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Lòng gian tự ý, mạnh dồn về, Lương Châu, Tây Nội, đều theo Mạc.</t>
+          <t>Xe loan về đến kinh đài, Sẵn sàng thiền chiếu ép bài sách phong.</t>
         </is>
       </c>
     </row>
@@ -12120,12 +12120,12 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>莫覊繕麵彊。異竜傳諾宜陽孕茄</t>
+          <t>禍心自意強驟良州西內甘悉朱當</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Mạc vào, sửa soạn, mạnh dồn về, Dị Long, Truy Nặc, đều theo Mạc.</t>
+          <t>Họa tâm từ ấy càng nồng, Lương Châu Tây Nội cam lòng cho đang.</t>
         </is>
       </c>
     </row>
@@ -12137,12 +12137,12 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>壯歌蘇軾榮華，仍悉忠美埃麻詭驟</t>
+          <t>莫覊繕麵彊。異竜傳諾宜陽孕茄</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Hát ca vinh hiển, vẫn còn đó, Vẫn theo Mạc, dối gian, mưu đồ.</t>
+          <t>Mạc rầy rõ mặt tiếm cường, Thăng Long truyền nước, Nghi Dương dựng nhà.</t>
         </is>
       </c>
     </row>
@@ -12154,12 +12154,12 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>求風差使北朝，登廣納坦慤誦對明</t>
+          <t>壯歌蘇軾榮華，仍悉忠美埃麻詭驟</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Cầu xin sai khiến, Bắc triều đến, Đăng Quảng, Nạp Thản, đều theo Mạc.</t>
+          <t>Dỗ người lấy vẻ vinh hoa, Nhưng lòng trung nghĩa ai mà sá theo.</t>
         </is>
       </c>
     </row>
@@ -12171,12 +12171,12 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>黎臣固仇忠貞，鄭顯邀鍊北庭賚曰</t>
+          <t>求風差使北朝，登廣納坦慤誦對明</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Lê thần trung nghĩa, giữ thù nhà, Trịnh Hiển, mời gọi, Bắc đình ban thưởng.</t>
+          <t>Cầu phong sai sứ Bắc triều, Dâng vàng, nộp đất nhiều điều dối Minh.</t>
         </is>
       </c>
     </row>
@@ -12188,12 +12188,12 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>明貪礼厚貼韜貧情忠姜痛調是非</t>
+          <t>黎臣固仇忠貞，鄭顯邀鍊北庭賚曰</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Minh tham lễ hậu, giấu tình nghèo, Trung, Khương, đau đớn, phân biệt phải trái.</t>
+          <t>Lê thần có kẻ trung trinh, Trịnh Ngung sang đến Bắc đình tỏ kêu.</t>
         </is>
       </c>
     </row>
@@ -12205,12 +12205,12 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>登庸安酌姦欺歲高未夷傳術登瀛</t>
+          <t>明貪礼厚貼韜貧情忠姜痛調是非</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Đăng Dung an bài, gian dối, Lừa dối năm tháng, chưa yên dân.</t>
+          <t>Minh tham lễ hậu của nhiều, Phụ tình trung nghĩa, quên điều thị phi.</t>
         </is>
       </c>
     </row>
@@ -12222,12 +12222,12 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>馬江頭唱美聲賜賒飛極懸情勤王</t>
+          <t>登庸安酌姦欺歲高未夷傳術登瀛</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Ngựa sông đầu hát, tiếng hay, Ban thưởng, xa xôi, tình thương vua.</t>
+          <t>Đăng Dung thỏa chước gian khi, Tuổi cao rồi lại truyền về Đăng Doanh.</t>
         </is>
       </c>
     </row>
@@ -12239,12 +12239,12 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>特輸余陣戰塲廓秋節菱發蘋流名</t>
+          <t>馬江頭唱美聲賜賒飛極懸情勤王</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Đặc biệt thua trận, chiến trường, Mùa thu, sen nổi, tên bay.</t>
+          <t>Mã Giang đầu xướng nghĩa thanh, Gần xa đâu chẳng nức tình cần vương.</t>
         </is>
       </c>
     </row>
@@ -12256,12 +12256,12 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>梗黎固度再榮吹誠佐命至生聖賢</t>
+          <t>特輸余陣戰塲廓秋節菱發蘋流名</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Cương Lê giữ vững, lại vinh quang, Thổi sáo, giúp mệnh, sinh thánh hiền.</t>
+          <t>Được thua mấy trận chiến trường, Nghìn thu tiết nghĩa đá vàng lưu danh.</t>
         </is>
       </c>
     </row>
@@ -12273,12 +12273,12 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>德希</t>
+          <t>梗黎固度再榮吹誠佐命至生聖賢</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Đức cao.</t>
+          <t>Cành Lê có độ tái vinh, Xui nên tá mệnh trời sinh thánh hiền.</t>
         </is>
       </c>
     </row>
@@ -12290,12 +12290,12 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>筆祖些連拾軍扶義鬱坼中興</t>
+          <t>德希</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Bút tổ, liên quân, phù nghĩa, Uất hận, rạn nứt, trung hưng.</t>
+          <t>Đức vua Triệu Tổ ta lên,</t>
         </is>
       </c>
     </row>
@@ -12307,12 +12307,12 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>岑州倚芳源馥近辭開招余魯浩嶽</t>
+          <t>筆祖些連拾軍扶義鬱坼中興</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Cẩm Châu, Ỷ Phương, Nguyên Phục, Gần gũi, từ chức, chiêu dụ.</t>
+          <t>Cất quân phù nghĩa giúp nền trung hưng.</t>
         </is>
       </c>
     </row>
@@ -12324,12 +12324,12 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>咄歎鼎祿衰病網鷗渚漁吻群尊黎</t>
+          <t>岑州倚芳源馥近辭開招余魯浩嶽</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Than ôi, đỉnh lộc, suy yếu, Lưới chim, bãi cá, tôn vinh Lê.</t>
+          <t>Sầm Châu ỷ thế nguồn rừng, Mười năm khai thác mấy từng nước non.</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>莊宗流落尋術動兵翠舞翻旗突卒</t>
+          <t>咄歎鼎祿衰病網鷗渚漁吻群尊黎</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Trang Tông lưu lạc, tìm thuật, Động binh, múa lụa, cờ bay, quân đột.</t>
+          <t>Dù khi đỉnh tộ suy mòn, Cương trù chưa nát vẫn còn tôn Lê.</t>
         </is>
       </c>
     </row>
@@ -12358,12 +12358,12 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>雷陽沒陣兵交破散逆黨進寇乂安</t>
+          <t>莊宗流落尋術動兵翠舞翻旗突卒</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Lôi Dương, trận chiến, binh giao, Phá tan nghịch đảng, tiến vào Nghệ An.</t>
+          <t>Trang Tông lưu lạc tìm về, Chia binh Thúy Đạn, mở cờ Ai Lao.</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>乾花惆蓮車齋土豪應美民間懸恙</t>
+          <t>雷陽沒陣兵交破散逆黨進寇乂安</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Cỏ hoa, buồn bã, xe loan, Thổ hào, ứng nghĩa, dân gian.</t>
+          <t>Lôi Dương một trận binh giao, Phá tan nghịch đảng tiến vào Nghệ An.</t>
         </is>
       </c>
     </row>
@@ -12392,12 +12392,12 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>西都挾滄滄紅縣長徜擣荒嗣長驅</t>
+          <t>乾花惆蓮車齋土豪應美民間懸恙</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Tây Đô, quét sạch, bụi hồng, Dặm trường, thẳng trỏ, ngọn đồng.</t>
+          <t>Cỏ hoa mừng rước xe loan, Thổ hào ứng nghĩa, dân gian nức lòng.</t>
         </is>
       </c>
     </row>
@@ -12409,12 +12409,12 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>限覲威細東都沒仁收復基圖課響</t>
+          <t>西都挾滄滄紅縣長徜擣荒嗣長驅</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Hạn chế, uy thế, Đông Đô, thu phục, cơ đồ.</t>
+          <t>Tây Đô quét sạch bụi hồng, Dặm tràng thẳng trỏ ngọn đòng tràng khu.</t>
         </is>
       </c>
     </row>
@@ -12426,12 +12426,12 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>毒韁陏將進徐熠營五丈侍霧將星</t>
+          <t>限覲威細東都沒仁收復基圖課響</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Độc sao, hàng tướng, tiến dưa, Ngũ Trượng, mờ tướng tinh.</t>
+          <t>Hẹn ngày vào tới Đông Đô, Một hai thu phục cơ đồ thủa xưa.</t>
         </is>
       </c>
     </row>
@@ -12443,12 +12443,12 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>惜自功業垂成抵朱鄭檢台騎綻軍</t>
+          <t>毒韁陏將進徐熠營五丈侍霧將星</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Tiếc thay, công nghiệp, thành, Trịnh Kiểm, thay mình, thống quân.</t>
+          <t>Độc sao hàng tướng tiến dưa, Trước dinh Ngũ Trượng bỗng mờ tướng tinh.</t>
         </is>
       </c>
     </row>
@@ -12460,12 +12460,12 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>歡辭站會亨屯門湖飛奄鏢旬燼雯</t>
+          <t>惜自功業垂成抵朱鄭檢台騎綻軍</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Vui mừng, hội họp, Đồn Môn, Hồ bay, ám hiệu.</t>
+          <t>Tiếc thay công nghiệp thùy thành, Để cho Trịnh Kiểm thay mình thống quân.</t>
         </is>
       </c>
     </row>
@@ -12477,12 +12477,12 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>中宗悔懼餘威莫臣余仇拱衛效忠</t>
+          <t>歡辭站會亨屯門湖飛奄鏢旬燼雯</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Trung Tông, hối hận, sợ hãi, Mạc thần, hiệu trung.</t>
+          <t>Sáu năm vừa hội hanh truân, Đỉnh hồ đâu đã đến tuần mây che.</t>
         </is>
       </c>
     </row>
@@ -12494,12 +12494,12 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>汗營軍猛將雄畢方豪傑隱悉依光</t>
+          <t>中宗悔懼餘威莫臣余仇拱衛效忠</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>Biện dinh, quân mạnh, tướng hùng, Bốn phương, hào kiệt, y quang.</t>
+          <t>Trung Tông nhờ cậy dư uy, Mạc thần mấy kẻ cũng về hiệu trung.</t>
         </is>
       </c>
     </row>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>東京擣荒戚嶺福源莫主凝鄕金城</t>
+          <t>汗營軍猛將雄畢方豪傑隱悉依光</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Đông Kinh, trỏ ngọn, Phúc Nguyên, Mạc chúa, Kim Thành.</t>
+          <t>Biện dinh quân mạnh, tướng hùng, Bốn phương hào kiệt nức lòng y quang.</t>
         </is>
       </c>
     </row>
@@ -12528,12 +12528,12 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>神符船赭冷汀吏群敬典切情野嘹</t>
+          <t>東京擣荒戚嶺福源莫主凝鄕金城</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Thần phù, thuyền giã, lạnh lùng, Kính điển, tình nghĩa, hoang dã.</t>
+          <t>Đông Kinh trỏ ngọn việt vàng, Phúc Nguyên Mạc chúa chạy sang Kim Thành.</t>
         </is>
       </c>
     </row>
@@ -12545,12 +12545,12 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>官兵號荒水潮沿江沒陣浩艤訖散</t>
+          <t>神符船赭冷汀吏群敬典切情野嘹</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Quan binh, thủy triều, Duyên Giang, tan tác.</t>
+          <t>Thần Phù thuyền giã lênh đênh, Lại còn Kính Điển đeo tình quấy trêu.</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>吳宗織業很難西都沒帶江山癸亥</t>
+          <t>官兵號荒水潮沿江沒陣浩艤訖散</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Ngô Tông, khó khăn, Tây Đô, giang san.</t>
+          <t>Quan binh theo ngọn thủy triều, Duyên Giang một trận, nước bèo chảy tan.</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>莫啟侵擾清華。太師鄭檢吏墨剿平</t>
+          <t>吳宗織業很難西都沒帶江山癸亥</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Mạc vào, xâm nhiễu, Thanh Hoa, Thái sư, Trịnh Kiểm, tiễu bình.</t>
+          <t>Anh Tông nối nghiệp gian nan, Tây Đô một giải giang san cõi nhà.</t>
         </is>
       </c>
     </row>
@@ -12596,12 +12596,12 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>化州固坦边成罪皮山海至賀金湯</t>
+          <t>莫啟侵擾清華。太師鄭檢吏墨剿平</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Hóa Châu, biên thành, sơn hải, kim thang.</t>
+          <t>Mạc vào xâm nhiễu Thanh Hoa, Thái sư Trịnh Kiểm lại ra tiễu bình.</t>
         </is>
       </c>
     </row>
@@ -12613,12 +12613,12 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>鄭公嘆貝黎皇，揺歇異將沒方城毀</t>
+          <t>化州固坦边成罪皮山海至賀金湯</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Trịnh công, than thở, Lê hoàng, Dẹp loạn, thành trì, bị hủy.</t>
+          <t>Hóa Châu có đất biên thành, Bốn bề sơn hải trời dành kim thang.</t>
         </is>
       </c>
     </row>
@@ -12630,12 +12630,12 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>本朝太祖雄才，探嶺略嶺揆外自低</t>
+          <t>鄭公嘆貝黎皇，揺歇異將沒方城毀</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Bản triều, Thái Tổ, hùng tài, Trấn cõi ngoài.</t>
+          <t>Trịnh công tâu với Lê hoàng, Chọn người ra giữ một phương thành dài.</t>
         </is>
       </c>
     </row>
@@ -12647,12 +12647,12 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>威旄欺奄鏹穫橫山沒緯買酪基圖</t>
+          <t>本朝太祖雄才，探嶺略嶺揆外自低</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Uy thế, lấn át, Hoành Sơn, gây dựng, cơ đồ.</t>
+          <t>Bản triều Thái Tổ hùng tài, Gióng cờ ra trấn cõi ngoài từ đây.</t>
         </is>
       </c>
     </row>
@@ -12664,12 +12664,12 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>穎韻寧缶塊壺鄭公專意馳驅撲</t>
+          <t>威旄欺奄鏹穫橫山沒緯買酪基圖</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Quận Gia, quận Định, Trịnh công, chuyên ý, trì khu.</t>
+          <t>Việt mao khi đã đến tay, Hoành Sơn một giải mới gây cơ đồ.</t>
         </is>
       </c>
     </row>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>郡嘉郡定余歌與宣兵合各尼添蕭</t>
+          <t>穎韻寧缶塊壺鄭公專意馳驅撲</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Phùng Khoan sứ tiết cũng già, Biểu từ biện chiết thật đà thiết minh.</t>
+          <t>Mặt trong đành đã khỏi lo, Trịnh công chuyên ý trì khu cõi ngoài.</t>
         </is>
       </c>
     </row>
@@ -12698,12 +12698,12 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>莫寅衷要自尼運黎玷缶鏌銗重亨</t>
+          <t>郡嘉郡定余歌與宣兵合各尼添蕭</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Mấy lời ôn dụ đinh ninh, Phong vương còn đợi biểu tinh có ngày.</t>
+          <t>Quận Gia, quận Định mấy người, Hưng, Tuyên binh hợp các nơi thêm dầy.</t>
         </is>
       </c>
     </row>
@@ -12715,12 +12715,12 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>挽軍衛狩西京。漱清吏潮沁蘊如空</t>
+          <t>莫寅衷要自尼運黎玷缶鏌銗重亨</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Hổ lui, lang tới khéo thay! Mạc kia vừa dẹp, Trịnh này lại lên.</t>
+          <t>Mạc dần suy yếu từ nay, Vận Lê xem đã đến ngày trùng hanh.</t>
         </is>
       </c>
     </row>
@@ -12732,12 +12732,12 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>因欺茂洽訒中。翔塘庸葛戈淹善提</t>
+          <t>挽軍衛狩西京。漱清吏潮沁蘊如空</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>Tùng xem căn cứ đã bền, Công danh càng thịnh, uy quyền càng cao.</t>
+          <t>Đem quân về giữ Tây Kinh, Bể thanh lại lặng tăm kình như không.</t>
         </is>
       </c>
     </row>
@@ -12749,12 +12749,12 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>莫執軍吏挾術莫蹈軍吏眾交撫要</t>
+          <t>因欺茂洽訒中。翔塘庸葛戈淹善提</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Rỡ ràng ngọc sách tinh bao, Gia phong nguyên súy, dự vào sủng chương.</t>
+          <t>Nhân khi Mậu Hợp ấu trùng, Mở đường Phố Cát, qua sông Bồ Đề.</t>
         </is>
       </c>
     </row>
@@ -12766,12 +12766,12 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>雪霜泉陣衝坡鄭公為諾拱它勤勞</t>
+          <t>莫執軍吏挾術莫蹈軍吏眾交撫要</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Bình An lại tiến tước vương, Gầy nền tiếm thiết mở đường khải du.</t>
+          <t>Mạc vào, quân lại rút về, Mạc lui, quân lại bốn bề kéo ra.</t>
         </is>
       </c>
     </row>
@@ -12783,12 +12783,12 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>歲巍茲解節旄羯眾鄭檜吏敘童戎</t>
+          <t>雪霜泉陣衝坡鄭公為諾拱它勤勞</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Kính Tông còn độ ấu cô, Đống lương ai kẻ xanh phù vạc Lê.</t>
+          <t>Tuyết sương trăm trận xông pha, Trịnh công vì nước cũng đà cần lao.</t>
         </is>
       </c>
     </row>
@@ -12800,12 +12800,12 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>驕荒悵腿混兵權吏抵鄭松台英</t>
+          <t>歲巍茲解節旄羯眾鄭檜吏敘童戎</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Triều thần những lũ Bùi Khuê, Lại tìm Mạc nghiệt theo về Kính Cung.</t>
+          <t>Tuổi già vừa giải tiết mao, Con là Trịnh Cối lại vào đổng nhung.</t>
         </is>
       </c>
     </row>
@@ -12817,12 +12817,12 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>擒松沒拾堆梗縈枯奄恪恩情拱睽</t>
+          <t>驕荒悵腿混兵權吏抵鄭松台英</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Nghi Dương tro tắt lại nồng, Thị thành nổi áng bụi hồng bởi ai?</t>
+          <t>Kiêu hoang quen thói con dòng, Binh quyền lại để Trịnh Tùng thay anh.</t>
         </is>
       </c>
     </row>
@@ -12834,12 +12834,12 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>莫施矛盾仁交乘机莫吏橋術內侵</t>
+          <t>擒松沒拾堆梗縈枯奄恪恩情拱睽</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Nhân khi giá ngự ra ngoài, Thừa hư Mạc lại vào nơi đô thành.</t>
+          <t>Cối, Tùng một gốc đôi cành, Vinh khô đã khác, ân tình cũng khuê.</t>
         </is>
       </c>
     </row>
@@ -12851,12 +12851,12 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>莫蹈松買萌心。非張聲芳齰拎權綱</t>
+          <t>莫施矛盾仁交乘机莫吏橋術內侵</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Quan quân ra đánh lại bình, Thặng dư mới phát tự Thanh ngự về.</t>
+          <t>Anh em mâu thuẫn hai bề, Thừa cơ Mạc lại kéo về nội xâm.</t>
         </is>
       </c>
     </row>
@@ -12868,12 +12868,12 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>吏謀殘害忠良鐵遂外禦節張衛幔</t>
+          <t>莫蹈松買萌心。非張聲芳齰拎權綱</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Chông gai tuy sạch mọi bề, Mà trong quyền cả chuyên về một tay.</t>
+          <t>Mạc lui, Tùng mới manh tâm, Ngoài trương thanh thế, trong cầm quyền cương.</t>
         </is>
       </c>
     </row>
@@ -12885,12 +12885,12 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>謝情負沁念丹先黎及第拆冤女帝</t>
+          <t>吏謀殘害忠良鐵遂外禦節張衛幔</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Bốn phương tai biến đã đầy, Đầm khô, núi lở, cát bay mù trời.</t>
+          <t>Lại mưu tàn hại trung lương, Vàng đưa ngoài cửa, búa trương dưới màn.</t>
         </is>
       </c>
     </row>
@@ -12902,12 +12902,12 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>平空漫陣波濤。祇宋車駕凝顧乂安</t>
+          <t>謝情負沁念丹先黎及第拆冤女帝</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>Chẳng qua trăm sự tại người, Gẫm cơ hưu cữu biết đời thịnh suy.</t>
+          <t>Tạ tình phụ tấm niềm đan, Đem Lê Cập Đệ giết oan nỡ nào!</t>
         </is>
       </c>
     </row>
@@ -12919,12 +12919,12 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>蔗田務買田盡雷楊屯浚皆冤神鴻</t>
+          <t>平空漫陣波濤。祇宋車駕凝顧乂安</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Súng đâu phục trước đường đi, Để cho Trịnh chúa lại nghi Lê hoàng.</t>
+          <t>Bằng không nổi trận ba đào, Để cho xa giá chạy vào Nghệ An.</t>
         </is>
       </c>
     </row>
@@ -12936,12 +12936,12 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>世宗鼎次踐荒鄭松扶立拱類假名</t>
+          <t>蔗田務買田盡雷楊屯浚皆冤神鴻</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Sinh con gặp đứa vô lương, Châu liên sao nỡ quên đường quân thân?</t>
+          <t>Giá điền vừa mới hồi loan, Lôi Dương đã nổi tiếng oan giữa vời.</t>
         </is>
       </c>
     </row>
@@ -12953,12 +12953,12 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>樊北賊莫縱橫。北河割據余城人民</t>
+          <t>世宗鼎次踐荒鄭松扶立拱類假名</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Thừa gia theo lối cường thần, Vua Lê, chúa Trịnh nhân tuần đã quen.</t>
+          <t>Thế Tông con thứ nối đời, Trịnh Tùng phù lập cùng loài giả danh.</t>
         </is>
       </c>
     </row>
@@ -12970,12 +12970,12 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>降威恀固雷神固期茂洽鍊旬天謀</t>
+          <t>樊北賊莫縱橫。北河割據余城人民</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>Thần Tông vừa mới cải nguyên, Sách phong Trịnh Tráng đã ban từ giờ.</t>
+          <t>Cõi ngoài giặc Mạc tung hoành, Bắc hà cát cứ mấy thành nhân dân.</t>
         </is>
       </c>
     </row>
@@ -12987,12 +12987,12 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>莫臣余仇武夫翳晨落霹兗秋用漆</t>
+          <t>降威恀固雷神固期茂洽鍊旬天謀</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>Thành đô quyền trọng hơn xưa, Nước nhà đang buổi yên vui,</t>
+          <t>Giáng uy nhờ có lôi thần, Nhân khi Mậu Hợp đến tuần thiên tru.</t>
         </is>
       </c>
     </row>
@@ -13004,12 +13004,12 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>出兵効迟机歪塘惊蹤躡罨外天閘</t>
+          <t>莫臣余仇武夫翳晨落霹兗秋用漆</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Xin vua xuống chiếu truyền ngôi nhẽ gì? Chẳng qua là dạ gian khi,</t>
+          <t>Mạc thần mấy kẻ vũ phu, Sao mai lác đác, lá thu rụng rời.</t>
         </is>
       </c>
     </row>
@@ -13021,12 +13021,12 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>長驅沒壘沿山縣州隱冽長安焰燼</t>
+          <t>出兵効迟机歪塘惊蹤躡罨外天閘</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Làm cho rõ mặt phúc uy tự nhà. Nhân Tông tuổi mới mười ba,</t>
+          <t>Xuất binh vừa gặp cơ trời, Đường ghềnh len lỏi ra ngoài Thiên Quan.</t>
         </is>
       </c>
     </row>
@@ -13038,12 +13038,12 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>繡城莫疑戈澠劍鯉鳳眼塘窩買催</t>
+          <t>長驅沒壘沿山縣州隱冽長安焰燼</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Hững hờ quyền chúa, ngôi cha mặc lòng. Quốc vương Minh mới cải phong,</t>
+          <t>Tràng khu một lối duyên san, Huyện châu gió lướt, Tràng An lửa nồng.</t>
         </is>
       </c>
     </row>
@@ -13055,12 +13055,12 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>詐自偽莫僭龜齋裝傳緯恕此齋退</t>
+          <t>繡城莫疑戈澠劍鯉鳳眼塘窩買催</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>Bẩy năm lịch số vừa chung một đời. Xoay quanh mới tỏ đạo trời,</t>
+          <t>Bỏ thành Mạc chạy qua sông, Đuổi sang Phượng Nhỡn đường cùng mới thôi.</t>
         </is>
       </c>
     </row>
@@ -13072,12 +13072,12 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>塵埃挾滲自剔術京頒宴席排賞功</t>
+          <t>詐自偽莫僭龜齋裝傳緯恕此齋退</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Báu thiêng đem lại cho người truyền gia. Thần Tông thay giữ nghiệp nhà,</t>
+          <t>Kể từ ngụy Mạc tiếm ngôi, Năm đời truyền kế, sáu mươi năm chầy.</t>
         </is>
       </c>
     </row>
@@ -13089,12 +13089,12 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>買差使者求封，賠讒明嘆群悉信疑</t>
+          <t>塵埃挾滲自剔術京頒宴席排賞功</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Thượng hoàng lại đổi mặt ra tân hoàng. Thờ ơ cờ đạo nhà vàng,</t>
+          <t>Trần ai quét sạch từ rầy, Về kinh ban yến, tiệc bầy thưởng công.</t>
         </is>
       </c>
     </row>
@@ -13106,12 +13106,12 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>差官會勘沒期封叄都統覊縻嘗異</t>
+          <t>買差使者求封，賠讒明嘆群悉信疑</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Chính quyền phó mặc Trịnh vương, biết gì? Nhà Minh thủa ấy đã suy,</t>
+          <t>Mới sai sứ giả cầu phong, V12: Nghe gièm Minh hãy là còn lòng tín nghi.</t>
         </is>
       </c>
     </row>
@@ -13123,12 +13123,12 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>馮寬使節拱魏表詞辨折辤阨切明</t>
+          <t>差官會勘沒期封叄都統覊縻嘗異</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Mượn binh lại rắp nhờ uy cường thần. Sắc phong chiếu dụ ân cần,</t>
+          <t>Sai quan hội khám một kỳ, Phong làm Đô thống, cơ mi gọi là!</t>
         </is>
       </c>
     </row>
@@ -13140,12 +13140,12 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>余剿溫諭丁寧。封王群待袁旌固駒</t>
+          <t>馮寬使節拱魏表詞辨折辤阨切明</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>Phó vương Trịnh lại thêm phần tôn vinh. Cả giầu sang, lớn quyền hành,</t>
+          <t>Phùng Khoan sứ tiết cũng già, Biểu từ biện chiết thật đà thiết minh.</t>
         </is>
       </c>
     </row>
@@ -13157,12 +13157,12 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>虎鱗狼細空台莫異魘擇鄭尼吏連</t>
+          <t>余剿溫諭丁寧。封王群待袁旌固駒</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Giang sơn chung một, triều đình chia đôi. Tiếm phong Trịnh Tạc nối ngôi,</t>
+          <t>Mấy lời ôn dụ đinh ninh, Phong vương còn đợi biểu tinh có ngày.</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>松紘根據缶紬功名強盛威權強高</t>
+          <t>虎鱗狼細空台莫異魘擇鄭尼吏連</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Tước vương mình lại tài bồi cho con. Càn cương ngày một suy mòn,</t>
+          <t>Hổ lui, lang tới khéo thay! Mạc kia vừa dẹp, Trịnh này lại lên.</t>
         </is>
       </c>
     </row>
@@ -13191,12 +13191,12 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>贈煉玉冊旌褒加封元帥預啟章</t>
+          <t>松紘根據缶紬功名強盛威權強高</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Bản triều mở dấu Kỳ phong, Thánh thần truyền dõi một lòng tôn Lê.</t>
+          <t>Tùng xem căn cứ đã bền, Công danh càng thịnh, uy quyền càng cao.</t>
         </is>
       </c>
     </row>
@@ -13208,12 +13208,12 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>平安吏進爵王鯤坪僭窃翻塘凱覦</t>
+          <t>贈煉玉冊旌褒加封元帥預啟章</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Quyền gian giận Trịnh nhiều bề, Sắc sai Chiêu, Thuận khắc kỳ tiến chinh.</t>
+          <t>Rỡ ràng ngọc sách tinh bao, Gia phong nguyên súy, dự vào sủng chương.</t>
         </is>
       </c>
     </row>
@@ -13225,12 +13225,12 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>敬宗群度劔孤棟樑埃仉擇扶護黎</t>
+          <t>平安吏進爵王鯤坪僭窃翻塘凱覦</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Sáu năm rồi mới bãi binh, Lũy dài còn dấu uy linh để truyền.</t>
+          <t>Bình An lại tiến tước vương, Gầy nền tiếm thiết mở đường khải du.</t>
         </is>
       </c>
     </row>
@@ -13242,12 +13242,12 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>朝臣仍屢裴奎吏尋莫孽蹺術徵泰</t>
+          <t>敬宗群度劔孤棟樑埃仉擇扶護黎</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>Vận Lê còn buổi truân chuyên, Huyền Tông thơ ấu để quyền Tây vương. Đẳng uy đã biến lễ thường, Vào chầu không lạy, miếu đường có ai?</t>
+          <t>Kính Tông còn độ ấu cô, Đống lương ai kẻ xanh phù vạc Lê.</t>
         </is>
       </c>
     </row>
@@ -13259,12 +13259,12 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>宜陽豳燧吏牘市城浚盎擔紅黜埃</t>
+          <t>朝臣仍屢裴奎吏尋莫孽蹺術徵泰</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Thiên nhan lại muốn sánh vai, Giường ngồi đem đặt bên nơi ngự tiền.</t>
+          <t>Triều thần những lũ Bùi Khuê, Lại tìm Mạc nghiệt theo về Kính Cung.</t>
         </is>
       </c>
     </row>
@@ -13276,12 +13276,12 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>因欺駕御墨彩乘虛莫吏餓不都城</t>
+          <t>宜陽豳燧吏牘市城浚盎擔紅黜埃</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Dọc ngang dưới phủ trên đền, Mống tình cải bộ gầy nền tranh vương.</t>
+          <t>Nghi Dương tro tắt lại nồng, Thị thành nổi áng bụi hồng bởi ai?</t>
         </is>
       </c>
     </row>
@@ -13293,12 +13293,12 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>官軍罨打吏平。乘輿買券自清御術</t>
+          <t>因欺駕御墨彩乘虛莫吏餓不都城</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Vũ công lại muốn phấn dương, Đem quân đánh Mạc tiến sang Cao Bằng.</t>
+          <t>Nhân khi giá ngự ra ngoài, Thừa hư Mạc lại vào nơi đô thành.</t>
         </is>
       </c>
     </row>
@@ -13310,12 +13310,12 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>葵葵雖潛每友麻蟄權奇專術沒弼</t>
+          <t>官軍罨打吏平。乘輿買券自清御術</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>Mạc vào cầu viện Yên Kinh, Phong làm Đô thống tung hoành cõi xa.</t>
+          <t>Quan quân ra đánh lại bình, Thặng dư mới phát tự Thanh ngự về.</t>
         </is>
       </c>
     </row>
@@ -13327,12 +13327,12 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>眾方災變奄滄潭枯齒堰枯總震至</t>
+          <t>葵葵雖潛每友麻蟄權奇專術沒弼</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Bốn châu riêng một sơn hà, Danh tuy phụ Hán, thực là thê Ngô.</t>
+          <t>Chông gai tuy sạch mọi bề, Mà trong quyền cả chuyên về một tay.</t>
         </is>
       </c>
     </row>
@@ -13344,12 +13344,12 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>拯戈募事在歇鶴機休咎別荒盛衰</t>
+          <t>眾方災變奄滄潭枯齒堰枯總震至</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Gia Tông vừa nối cơ đồ, Xe loan đã giục trì khu ra ngoài.</t>
+          <t>Bốn phương tai biến đã đầy, Đầm khô, núi lở, cát bay mù trời.</t>
         </is>
       </c>
     </row>
@@ -13361,12 +13361,12 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>歲兇伏耀塘謬抵朱鄭主吏疑黎皇</t>
+          <t>拯戈募事在歇鶴機休咎別荒盛衰</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Phòng biên đã có tướng tài, Quân ta một trận, lũy dài phá tan.</t>
+          <t>Chẳng qua trăm sự tại người, Gẫm cơ hưu cữu biết đời thịnh suy.</t>
         </is>
       </c>
     </row>
@@ -13378,12 +13378,12 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>生混返盜無良桂連輿女禱壇君親</t>
+          <t>歲兇伏耀塘謬抵朱鄭主吏疑黎皇</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Mã đầu đã trở quy an, Hà Trung Trịnh lại đặt quan lưu đồn.</t>
+          <t>Súng đâu phục trước đường đi, Để cho Trịnh chúa lại nghi Lê hoàng.</t>
         </is>
       </c>
     </row>
@@ -13395,12 +13395,12 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>承家號磊強臣希黎主鄭因循奄悄</t>
+          <t>生混返盜無良桂連輿女禱壇君親</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Về nhà lại lập Trịnh Căn, Nam vương theo lối quyền môn một dòng.</t>
+          <t>Sinh con gặp đứa vô lương, Châu liên sao nỡ quên đường quân thân?</t>
         </is>
       </c>
     </row>
@@ -13412,12 +13412,12 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>神宗訪買改元冊封鄭紳奄頒自暴</t>
+          <t>承家號磊強臣希黎主鄭因循奄悄</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Đêm ngày bí các thong dong, Văn thần thay đổi vào trong chực hầu.</t>
+          <t>Thừa gia theo lối cường thần, Vua Lê, chúa Trịnh nhân tuần đã quen.</t>
         </is>
       </c>
     </row>
@@ -13429,12 +13429,12 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>清都權重斂磬，笳黎拱沒端承麻催</t>
+          <t>神宗訪買改元冊封鄭紳奄頒自暴</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Quốc Trinh tham tụng ở đầu, Bởi sao nên nỗi gây thù ưu binh?</t>
+          <t>Thần Tông vừa mới cải nguyên, Sách phong Trịnh Tráng đã ban từ giờ.</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>浣花當闕安監頃希範詔傳魑鍾之</t>
+          <t>清都權重斂磬，笳黎拱沒端承麻催</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Hy Tông hoàng đệ thay anh, Ngôi không luống giữ, quyền hành mặc ai!</t>
+          <t>Thành đô quyền trọng hơn xưa, Nước nhà đang buổi yên vui, Xin vua xuống chiếu truyền ngôi nhẽ gì?</t>
         </is>
       </c>
     </row>
@@ -13463,12 +13463,12 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>拯戈男脃姦欺乡朱蠙穫福威自茄</t>
+          <t>浣花當闕安監頃希範詔傳魑鍾之</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Bấy lâu chiếm cứ cõi ngoài, Hãy còn Mạc nghiệt mấy đời đến nay.</t>
+          <t>Chẳng qua là dạ gian khi, Làm cho rõ mặt phúc uy tự nhà.</t>
         </is>
       </c>
     </row>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>真宗歲買近匹頃有權主魃吒默悉</t>
+          <t>拯戈男脃姦欺乡朱蠙穫福威自茄</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Di thư sang với Quảng Tây, Một lần hội tiễu từ này chạy xa.</t>
+          <t>Nhân Tông tuổi mới mười ba, Hững hờ quyền chúa, ngôi cha mặc lòng.</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>國王明買改封，點辭歷效終沒蔑</t>
+          <t>真宗歲買近匹頃有權主魃吒默悉</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Quân Thanh xâm chiếm đất ta, Vị Xuyên, Bảo Lạc, Nà Oa, Lộc Bình.</t>
+          <t>Quốc vương Minh mới cải phong, Bẩy năm lịch số vừa chung một đời.</t>
         </is>
       </c>
     </row>
@@ -13514,12 +13514,12 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>磋選買燻道歪宝疑寇吏朱敍傳家</t>
+          <t>國王明買改封，點辭歷效終沒蔑</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>Thổ quan lại có tư tình, Tham vàng đem giới kệ mình chuyển di.</t>
+          <t>Quốc vương Minh mới cải phong, Bẩy năm lịch số vừa chung một đời.</t>
         </is>
       </c>
     </row>
@@ -13531,12 +13531,12 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>神宗台符業茄上皇吏樹穫蚤親皇</t>
+          <t>磋選買燻道歪宝疑寇吏朱敍傳家</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Bên ngoài xâm tước nhiều bề, Ở trong chính sự chỉnh tề được bao?</t>
+          <t>Xoay quanh mới tỏ đạo trời, Báu thiêng đem lại cho người truyền gia.</t>
         </is>
       </c>
     </row>
@@ -13548,12 +13548,12 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>餘於旗纛品鎮政權付黔鄭王別之</t>
+          <t>神宗台符業茄上皇吏樹穫蚤親皇</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Lễ gì hơn lễ bang giao, Mà cho quan thị đứng vào đầu ban.</t>
+          <t>Thần Tông thay giữ nghiệp nhà, Thượng hoàng lại đổi mặt ra tân hoàng.</t>
         </is>
       </c>
     </row>
@@ -13565,12 +13565,12 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>武功吏訩奮楊，擁軍打莫進趣高平</t>
+          <t>餘於旗纛品鎮政權付黔鄭王別之</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Thế mà những kẻ cư quan, Cũng đành ngoảnh mặt cho toàn tôn vinh.</t>
+          <t>Thờ ơ cờ đạo nhà vàng, Chính quyền phó mặc Trịnh vương, biết gì?</t>
         </is>
       </c>
     </row>
@@ -13582,12 +13582,12 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>莫飲求援燕京，封夕都綻縱橫揆賒</t>
+          <t>武功吏訩奮楊，擁軍打莫進趣高平</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Tại triều mấy kẻ trâm anh, Nguyễn Đăng, Đồng Trạch công thanh một đường.</t>
+          <t>Vũ công lại muốn phấn dương, Đem quân đánh Mạc tiến sang Cao Bằng.</t>
         </is>
       </c>
     </row>
@@ -13599,12 +13599,12 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>眾州縉汶山河，名雖附漢皇署棲吳</t>
+          <t>莫飲求援燕京，封夕都綻縱橫揆賒</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Thế Vinh tài học ưu trường, Nguyễn Hành, Hà Mục văn chương cũng già.</t>
+          <t>Mạc vào cầu viện Yên Kinh, Phong làm Đô thống tung hoành cõi xa.</t>
         </is>
       </c>
     </row>
@@ -13616,12 +13616,12 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>嘉宗効踐基圖車鑑証題馳驅罷外</t>
+          <t>眾州縉汶山河，名雖附漢皇署棲吳</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Bởi ai thiên hạ âu ca, Chẳng quan tham tụng Vãn Hà là chi?</t>
+          <t>Bốn châu riêng một sơn hà, Danh tuy phụ Hán, thực là thê Ngô.</t>
         </is>
       </c>
     </row>
@@ -13633,12 +13633,12 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>防邊奄固將才，軍些沒陣壘殲破敵</t>
+          <t>嘉宗効踐基圖車鑑証題馳驅罷外</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Bởi ai thiên hạ sầu bi, Chẳng quan tham tụng Lê Hy hãnh thần?</t>
+          <t>Gia Tông vừa nối cơ đồ, Xe loan đã giục trì khu ra ngoài.</t>
         </is>
       </c>
     </row>
@@ -13650,12 +13650,12 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>馬頭屯阻歸鞍河中鄭吏達官留屯</t>
+          <t>防邊奄固將才，軍些沒陣壘殲破敵</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Tính đi nghĩ lại xa gần, Nhiều phần vì Trịnh, ít phần vì Lê.</t>
+          <t>Phòng biên đã có tướng tài, Quân ta một trận, lũy dài phá tan.</t>
         </is>
       </c>
     </row>
@@ -13667,12 +13667,12 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>術巖吏立鄭根南王蹺磊權門沒淵</t>
+          <t>馬頭屯阻歸鞍河中鄭吏達官留屯</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Mồi giầu sang đã say mê, Lấy ai chỉ trụ làm bia trong đời!</t>
+          <t>Mã đầu đã trở quy an, Hà Trung Trịnh lại đặt quan lưu đồn.</t>
         </is>
       </c>
     </row>
@@ -13684,12 +13684,12 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>皓鼎秘闥從容。文臣台榭敘直侯</t>
+          <t>術巖吏立鄭根南王蹺磊權門沒淵</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Dụ Tông nối giữ ngôi trời, Trịnh Cương chuyên chế theo loài cố gia.</t>
+          <t>Về nhà lại lập Trịnh Căn, Nam vương theo lối quyền môn một dòng.</t>
         </is>
       </c>
     </row>
@@ -13701,12 +13701,12 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>國禎參從於頭</t>
+          <t>皓鼎秘闥從容。文臣台榭敘直侯</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Lục phiên lại đặt tư nha, Bao nhiêu tài phú đều là về tay. Các quan trấn thủ mới thay, Hưng, Tuyên thống hạt, từ rầy chia hai.</t>
+          <t>Đêm ngày bí các thong dong, Văn thần thay đổi vào trong chực hầu.</t>
         </is>
       </c>
     </row>
@@ -13718,12 +13718,12 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>勳弼城內醲警優兵</t>
+          <t>國禎參從於頭</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>Vũ thần mỗi trấn một người, Để cho vững thế mặt ngoài phiên ly.</t>
+          <t>Quốc Trinh tham tụng ở đầu, Bởi sao nên nỗi gây thù ưu binh?</t>
         </is>
       </c>
     </row>
@@ -13735,12 +13735,12 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>熙宗皇第台英魁空隠守權衡默埃</t>
+          <t>勳弼城內醲警優兵</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Lấy năm điều khảo trấn ti, Cứ trong điến tối mà suy hay hèn.</t>
+          <t>Bởi ai thiên hạ âu ca, Chẳng quan tham tụng Vãn Hà là chi?</t>
         </is>
       </c>
     </row>
@@ -13752,12 +13752,12 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>訊數占據揆來唉群莫奪余茂興矜</t>
+          <t>熙宗皇第台英魁空隠守權衡默埃</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Thẩm hình đặt viện phủ tiền, Sai quan tra kiện thay quyền pháp ti.</t>
+          <t>Hy Tông hoàng đệ thay anh, Ngôi không luống giữ, quyền hành mặc ai!</t>
         </is>
       </c>
     </row>
@@ -13769,12 +13769,12 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>移書鄴貝廣西沒荅會剿自尼継賒</t>
+          <t>訊數占據揆來唉群莫奪余茂興矜</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Vũ khoa mới đặt phép thi, Hỏi đường thao lược, thử nghề đao cung.</t>
+          <t>Bấy lâu chiếm cứ cõi ngoài, Hãy còn Mạc nghiệt mấy đời đến nay.</t>
         </is>
       </c>
     </row>
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>官清侵占坦些渴川保樂那窩祿平</t>
+          <t>移書鄴貝廣西沒荅會剿自尼継賒</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Ba trường phúc thí đã xong, Đề danh tạo sĩ bảng rồng cũng vinh.</t>
+          <t>Di thư sang với Quảng Tây, Một lần hội tiễu từ này chạy xa.</t>
         </is>
       </c>
     </row>
@@ -13803,12 +13803,12 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>土官吏固私情貧穢冤界碣騎轉務</t>
+          <t>官清侵占坦些渴川保樂那窩祿平</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Kén thêm tứ trấn binh đinh, Vệ quân mới đặt sáu dinh từ rầy.</t>
+          <t>Quân Thanh xâm chiếm đất ta, Vị Xuyên, Bảo Lạc, Nà Oa, Lộc Bình.</t>
         </is>
       </c>
     </row>
@@ -13820,12 +13820,12 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>邊外侵削韃交於蝕政事整育特包</t>
+          <t>土官吏固私情貧穢冤界碣騎轉務</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Công tư điền thổ xưa nay, Sai quân khám đạc san tay dân cùng.</t>
+          <t>Thổ quan lại có tư tình, Tham vàng đem giới kệ mình chuyển di.</t>
         </is>
       </c>
     </row>
@@ -13837,12 +13837,12 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>礼也脩礼邦交麻朱官侍舘倉頭班</t>
+          <t>邊外侵削韃交於蝕政事整育特包</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Tuần hành có sứ khuyến nông, Giữ gìn đê lộ, xét trong dân tình.</t>
+          <t>Bên ngoài xâm tước nhiều bề, Ở trong chính sự chỉnh tề được bao?</t>
         </is>
       </c>
     </row>
@@ -13854,12 +13854,12 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>世麻仍飢居官拱尊曝穫朱金尊榮</t>
+          <t>礼也脩礼邦交麻朱官侍舘倉頭班</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Đem thư biện với nhà Thanh, Mỏ đồng, mỏ kẽm lại giành về ta.</t>
+          <t>Lễ gì hơn lễ bang giao, Mà cho quan thị đứng vào đầu ban.</t>
         </is>
       </c>
     </row>
@@ -13871,12 +13871,12 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>在朝余仇簪纓阮當同澤公清沒塘</t>
+          <t>世麻仍飢居官拱尊曝穫朱金尊榮</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Lập bia trên Đổ Chú hà, Giới cương tự đó mới là phân minh.</t>
+          <t>Thế mà những kẻ cư quan, Cũng đành ngoảnh mặt cho toàn tôn vinh.</t>
         </is>
       </c>
     </row>
@@ -13888,12 +13888,12 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>世榮才孝優長院游何穆文章拱賜</t>
+          <t>在朝余仇簪纓阮當同澤公清沒塘</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Qui mô cũng muốn sức bình, Mà lòng lăng tiếm tự mình ra chi?</t>
+          <t>Tại triều mấy kẻ trâm anh, Nguyễn Đăng, Đồng Trạch công thanh một đường.</t>
         </is>
       </c>
     </row>
@@ -13905,12 +13905,12 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>黜埃天下謳歌拯官參從挽河野之</t>
+          <t>世榮才孝優長院游何穆文章拱賜</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Lập phủ đường ở Cổ Bi, Toan đem kinh quốc dời về cố hương.</t>
+          <t>Thế Vinh tài học ưu trường, Nguyễn Hành, Hà Mục văn chương cũng già.</t>
         </is>
       </c>
     </row>
@@ -13922,12 +13922,12 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>黜埃天下愁悲挺官參從黎僖侍臣</t>
+          <t>黜埃天下謳歌拯官參從挽河野之</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Đông cung đã lập Duy Tường, Bỗng không lại đổi Duy Phường cớ sao?</t>
+          <t>Bởi ai thiên hạ âu ca, Chẳng quan tham tụng Vãn Hà là chi?</t>
         </is>
       </c>
     </row>
@@ -13939,12 +13939,12 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>併彫擬吏賒貯。鬱分為鄭匹分為黎</t>
+          <t>黜埃天下愁悲挺官參從黎僖侍臣</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Trịnh Giang quen lối gian hào, Truất ngôi Vĩnh Khánh hãm vào tội nhân.</t>
+          <t>Bởi ai thiên hạ sầu bi, Chẳng quan tham tụng Lê Hy hãnh thần?</t>
         </is>
       </c>
     </row>
@@ -13956,12 +13956,12 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>將霸郡奄醒迷祠埃砥柱夕碑龜菟</t>
+          <t>併彫擬吏賒貯。鬱分為鄭匹分為黎</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Thuần Tông đặt bỏ mấy lần, Phúc uy mặc sức cường thần mới ghê.</t>
+          <t>Tính đi nghĩ lại xa gần, Nhiều phần vì Trịnh, ít phần vì Lê.</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>裕宗踐寳韞丕鄭禰專制號頌故家</t>
+          <t>將霸郡奄醒迷祠埃砥柱夕碑龜菟</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Ý Tông còn tuổi hài đề, Danh tuy chính thống, quyền về phó vương.</t>
+          <t>Mồi giầu sang đã say mê, Lấy ai chỉ trụ làm bia trong đời!</t>
         </is>
       </c>
     </row>
@@ -13990,12 +13990,12 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>六番吏達私衙包怒財賦調界術施</t>
+          <t>裕宗踐寳韞丕鄭禰專制號頌故家</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Trịnh càng dâm ngược kiêu hoang, Đêm ngày luống những tham đường vui chơi.</t>
+          <t>Dụ Tông nối giữ ngôi trời, Trịnh Cương chuyên chế theo loài cố gia.</t>
         </is>
       </c>
     </row>
@@ -14007,12 +14007,12 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>各官顧守買台興宣綂轄自勵勤台</t>
+          <t>六番吏達私衙包怒財賦調界術施</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Dấu xe giong ruổi quanh trời, Sửa sang cảnh Phật, vẽ vời động tiên.</t>
+          <t>Lục phiên lại đặt tư nha, Bao nhiêu tài phú đều là về tay.</t>
         </is>
       </c>
     </row>
@@ -14024,12 +14024,12 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>武臣每顧沒影低朱伉芳麵來番離</t>
+          <t>各官顧守買台興宣綂轄自勵勤台</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Quỳnh Lâm, Hương Hải, Hồ Thiên, Của thiên hạ chất cửa thiền biết bao?</t>
+          <t>Các quan trấn thủ mới thay, Hưng, Tuyên thống hạt, từ rầy chia hai.</t>
         </is>
       </c>
     </row>
@@ -14041,12 +14041,12 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>痺蔵韞沒消耗半科謨爵廕哀愁宮</t>
+          <t>武臣每顧沒影低朱伉芳麵來番離</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Kho tàng ngày một tiêu hao, Bán khoa, mua tước tiền vào sáu cung.</t>
+          <t>Vũ thần mỗi trấn một người, Để cho vững thế mặt ngoài phiên ly.</t>
         </is>
       </c>
     </row>
@@ -14058,12 +14058,12 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>副王群渚甘悉上王吏假勅螭茄清</t>
+          <t>祕齋像考鎮司攜馳毀最寐推咍貿</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Phó vương còn chửa cam lòng, Thượng vương lại giả sắc rồng nhà Thanh.</t>
+          <t>Các quan trấn thủ mới thay, Hưng, Tuyên thống hạt, từ rầy chia hai.</t>
         </is>
       </c>
     </row>
@@ -14075,12 +14075,12 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>罪至訟色貫盈輿朱業報興窮買催</t>
+          <t>審形幸院府前，差官查件台權法司</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Tội trời kể đã quán doanh, Sao cho nghiệp báo đến mình mới thôi.</t>
+          <t>Vũ thần mỗi trấn một người, Để cho vững thế mặt ngoài phiên ly.</t>
         </is>
       </c>
     </row>
@@ -14092,12 +14092,12 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>偉竟淡皆天雷失驚魚悸如歇癲</t>
+          <t>武科買建法試每塘韜醫此芸刀弓</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Bỗng đâu một tiếng thiên lôi, Thất kinh ngơ ngác như người chứng điên.</t>
+          <t>Lấy năm điều khảo trấn ti, Cứ trong điến tối mà suy hay hèn.</t>
         </is>
       </c>
     </row>
@@ -14109,12 +14109,12 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>於諭吏嘗宮仙低團內豎專權弄威</t>
+          <t>匹場覆誠危衡，題名進士榜螭拱榮</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Ở hang lại gọi cung tiên, Để đoàn nội thụ chuyên quyền lộng uy.</t>
+          <t>Thẩm hình đặt viện phủ tiền, Sai quan tra kiện thay quyền pháp ti.</t>
         </is>
       </c>
     </row>
@@ -14126,12 +14126,12 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>悉歇兇極殲離螢呌鷗合少之所賒</t>
+          <t>規漆四鎮兵丁術軍買幸愁營自剝</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Lòng người đâu chẳng bạn ly, Ếch kêu, ác họp thiếu gì gần xa!</t>
+          <t>Vũ khoa mới đặt phép thi, Hỏi đường thao lược, thử nghề đao cung.</t>
         </is>
       </c>
     </row>
@@ -14143,12 +14143,12 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>山南固賊鼠茄阮蕩阮選意異賊東</t>
+          <t>公秘田土磬啓差官勘度刊穫民窮</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Sơn Nam có giặc Ngân Già, Nguyễn Cừ, Nguyễn Tuyển ấy là giặc Đông.</t>
+          <t>Ba trường phúc thí đã xong, Đề danh tạo sĩ bảng rồng cũng vinh.</t>
         </is>
       </c>
     </row>
@@ -14160,12 +14160,12 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>山西並清並蓬動來巳麵隨鈍眾皮</t>
+          <t>巡行固使勸農。弊屢提路察馳民情</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Sơn Tây: nghịch Tế, nghịch Bồng; Động ngoài ba mặt, nhộn trong bốn bề.</t>
+          <t>Kén thêm tứ trấn binh đinh, Vệ quân mới đặt sáu dinh từ rầy.</t>
         </is>
       </c>
     </row>
@@ -14177,12 +14177,12 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>解豁鄭固別也郡泡郡植都攻爭功</t>
+          <t>愧書辨貝茄清、埭嗣埭驗吏爭術些</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Nằm hang Trịnh có biết gì! Quận Bào, quận Thực đua bì tranh công.</t>
+          <t>Công tư điền thổ xưa nay, Sai quân khám đạc san tay dân cùng.</t>
         </is>
       </c>
     </row>
@@ -14194,12 +14194,12 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>副王愷搖茄淵極扶鄭氏輿衝役芪</t>
+          <t>立碑蓮賭呪河界強自意員異分明</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Phó vương quen lối nhà dòng, Chẳng phò Trịnh thị sao xong việc đời?</t>
+          <t>Tuần hành có sứ khuyến nông, Giữ gìn đê lộ, xét trong dân tình.</t>
         </is>
       </c>
     </row>
@@ -14211,12 +14211,12 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>阮公貴慈余馭危艫定萊環外耀兵</t>
+          <t>規模拱閥勵平，麻悉陵僭自斂墨之</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Nguyễn Công, Quý Cảnh mấy người, Vào trong định sách, ra ngoài diệu binh.</t>
+          <t>Đem thư biện với nhà Thanh, Mỏ đồng, mỏ kẽm lại giành về ta.</t>
         </is>
       </c>
     </row>
@@ -14228,12 +14228,12 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>共饒扶立鄭楹</t>
+          <t>立府堂於古碑箕魄京國強術故鄉</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Cùng nhau phù lập Trịnh Doanh, Thái vương Trịnh lại tôn anh làm vì. Sai quan kinh lược bốn bề, Khải ca mấy khúc đều về tấu công.</t>
+          <t>Lập bia trên Đổ Chú hà, Giới cương tự đó mới là phân minh.</t>
         </is>
       </c>
     </row>
@@ -14245,12 +14245,12 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>差官經略眾皮凱敵余曲調術奏功</t>
+          <t>東宮奄立維祥傳空吏樹維紗縷韝</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>Cơ mưu Trịnh cũng gian hùng, Nghĩ mình chuyên tiếm ắt lòng ai ưa.</t>
+          <t>Qui mô cũng muốn sức bình, Mà lòng lăng tiếm tự mình ra chi?</t>
         </is>
       </c>
     </row>
@@ -14262,12 +14262,12 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>机謀鄭拱姦雄擬騎專僭眇恚埃際</t>
+          <t>鄭杜愬姦女姦豪點斂永慶陷倉罪人</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Có Lê mới có đến giờ, Phải cầu hiền đức để nhờ phúc chung.</t>
+          <t>Lập phủ đường ở Cổ Bi, Toan đem kinh quốc dời về cố hương.</t>
         </is>
       </c>
     </row>
@@ -14279,12 +14279,12 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>固黎余固彊暴。沛求貞德抵恆福鍾</t>
+          <t>純宗奉補余荅。福威默勵強臣買緒</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>Kìa người mắt phượng, râu rồng, Duy Diêu vốn cũng là dòng thần minh.</t>
+          <t>Đông cung đã lập Duy Tường, Bỗng không lại đổi Duy Phường cớ sao?</t>
         </is>
       </c>
     </row>
@@ -14296,12 +14296,12 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>其馭親鳳鬢蠅維淝本拱冥淵神明</t>
+          <t>懿宗群歲弦提名雖正綂權術副王</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Hạ đài khuất bóng tiền tinh, Khuôn thiêng còn để một cành phúc chi.</t>
+          <t>Trịnh Giang quen lối gian hào, Truất ngôi Vĩnh Khánh hãm vào tội nhân.</t>
         </is>
       </c>
     </row>
@@ -14313,12 +14313,12 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>夏臺星釋前星園韻群抵沒梗福枝</t>
+          <t>鄭強淫驕虐荒，皓駟隱仍貪塘悟遡</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Hay đâu cầu ứng cũng kỳ, Bỗng xui Trịnh chúa tạm di ra ngoài.</t>
+          <t>Thuần Tông đặt bỏ mấy lần, Phúc uy mặc sức cường thần mới ghê.</t>
         </is>
       </c>
     </row>
@@ -14330,12 +14330,12 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>啓魄求應拱奇，停哭鄭主暫緩異處</t>
+          <t>蹏車黎臨逸歪撕擲景佛甕舞洞仙</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Vũ công một giấc hiên mai, Mơ màng đường thấy phong tài đế vương.</t>
+          <t>Dấu xe giong ruổi quanh trời, Sửa sang cảnh Phật, vẽ vời động tiên.</t>
         </is>
       </c>
     </row>
@@ -14347,12 +14347,12 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>武公沒賤斬枚憐愷樣覽風裁帝王</t>
+          <t>瓊林香海盡天貼天下質禪別色</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Tinh kỳ nhã nhạc lạ nhường, Thái bình nghi vệ rõ ràng chẳng ngoa.</t>
+          <t>Quỳnh Lâm, Hương Hải, Hồ Thiên, Của thiên hạ chất cửa thiền biết bao?</t>
         </is>
       </c>
     </row>
@@ -14364,12 +14364,12 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>旌旗雅樂眾樣太平俊術贍賜極詔</t>
+          <t>痺蔵韞沒消耗半科謨爵廕哀愁宮</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Sáng mai vừa mới tỉnh ra, Duy Diêu xảy đến chơi nhà lạ sao?</t>
+          <t>Kho tàng ngày một tiêu hao, Bán khoa, mua tước tiền vào sáu cung.</t>
         </is>
       </c>
     </row>
@@ -14381,12 +14381,12 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>創晨舫買醒墨維襖俊鍊麴茄還鞘</t>
+          <t>副王群渚甘悉上王吏假勅螭茄清</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>Thấy người mà nghiệm chiêm bao, Mới hay trẫm triệu ứng vào tự nhiên.</t>
+          <t>Phó vương còn chửa cam lòng, Thượng vương lại giả sắc rồng nhà Thanh.</t>
         </is>
       </c>
     </row>
@@ -14398,12 +14398,12 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>覧馭麻驗占色買啓朕兆應剱自然</t>
+          <t>罪至訟色貫盈　輿朱業報興窮買催</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>Nghe lời Trịnh mới phù lên, Hiển Tông từ ấy chịu truyền nối ngôi.</t>
+          <t>Tội trời kể đã quán doanh, Sao cho nghiệp báo đến mình mới thôi.</t>
         </is>
       </c>
     </row>
@@ -14415,12 +14415,12 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>殖剔鄭買扶蓮頭宗自意齋傳毀鱉</t>
+          <t>偉竟淡皆天雷失驚魚悸如歇癲</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>Vận Lê đến lúc suy đồi, Chắp tay rủ áo lặng ngồi mặc ai.</t>
+          <t>Bỗng đâu một tiếng thiên lôi, Thất kinh ngơ ngác như người chứng điên.</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>運黎鍊狀褒顏披穢撫禎潮嶺黔埃</t>
+          <t>於諭吏嘗宮仙低團內豎專權弄威</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>Gặp khi nhiều việc chông gai, Văn thần có kẻ phấn dương,</t>
+          <t>Ở hang lại gọi cung tiên, Để đoàn nội thụ chuyên quyền lộng uy.</t>
         </is>
       </c>
     </row>
@@ -14449,12 +14449,12 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>返欺慤役苓菱亂帥巳府賊非眾方</t>
+          <t>悉歇兇極殲離螢呌鷗合少之所賒</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Phạm Công Đình Trọng gồm đường lược thao. Phao Sơn trỏ ngọn cờ đào,</t>
+          <t>Lòng người đâu chẳng bạn ly, Ếch kêu, ác họp thiếu gì gần xa!</t>
         </is>
       </c>
     </row>
@@ -14466,12 +14466,12 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>文臣固仇舊揚范公廷重鏌塘畧韻</t>
+          <t>山南固賊鼠茄阮蕩阮選意異賊東</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Nguyễn Cừ đã phá, Nguyễn Cầu cũng tan. Nguyễn Phương cứ Độc Tôn Sơn,</t>
+          <t>Sơn Nam có giặc Ngân Già, Nguyễn Cừ, Nguyễn Tuyển ấy là giặc Đông.</t>
         </is>
       </c>
     </row>
@@ -14483,12 +14483,12 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>拋山擕荒旗桃阮蘧奄破阮求棋散</t>
+          <t>山西並清並蓬動來巳麵隨鈍眾皮</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Tuyên, Hưng là đất, lâm man là nhà. Trịnh vương quyết chí xông pha,</t>
+          <t>Sơn Tây: nghịch Tế, nghịch Bồng; Động ngoài ba mặt, nhộn trong bốn bề.</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>將霸郡奄醒迷祠埃砥柱夕碑龜菟</t>
+          <t>解豁鄭固別也郡泡郡植都攻爭功</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Huyệt sào quét sạch, binh xa mới về. Quyền gian kế tập quen lề,</t>
+          <t>Nằm hang Trịnh có biết gì! Quận Bào, quận Thực đua bì tranh công.</t>
         </is>
       </c>
     </row>
@@ -14517,12 +14517,12 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>裕宗踐寳韞丕鄭禰專制號頌故家</t>
+          <t>副王愷搖茄淵極扶鄭氏輿衝役芪</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Trịnh Sâm lại cũng sính nghề vũ công. Mạnh Thiên hang thẳm núi cùng,</t>
+          <t>Phó vương quen lối nhà dòng, Chẳng phò Trịnh thị sao xong việc đời?</t>
         </is>
       </c>
     </row>
@@ -14534,12 +14534,12 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>六番吏達私衙包怒財賦調界術施</t>
+          <t>阮公貴慈余馭危艫定萊環外耀兵</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>Hãy còn Hoàng Chất lâm tùng ẩn thân. Sai Đoàn Nguyễn Thục đem quân,</t>
+          <t>Nguyễn Công, Quý Cảnh mấy người, Vào trong định sách, ra ngoài diệu binh.</t>
         </is>
       </c>
     </row>
@@ -14551,12 +14551,12 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>各官顧守買台興宣綂轄自勵勤台</t>
+          <t>共饒扶立鄭楹</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>Cùng rừng săn thú một lần mới thanh. Lại toan dẹp cõi Trấn Ninh,</t>
+          <t>Cùng nhau phù lập Trịnh Doanh, Thái vương Trịnh lại tôn anh làm vì.</t>
         </is>
       </c>
     </row>
@@ -14568,12 +14568,12 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>武臣每顧沒影低朱伉芳麵來番離</t>
+          <t>差官經略眾皮凱敵余曲調術奏功</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>Chỉn e địa thế, dân tình chưa quen. Địa đồ ai khéo vẽ nên,</t>
+          <t>Sai quan kinh lược bốn bề, Khải ca mấy khúc đều về tấu công.</t>
         </is>
       </c>
     </row>
@@ -14585,12 +14585,12 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>審形幸院府前，差官查件台權法司</t>
+          <t>机謀鄭拱姦雄擬騎專僭眇恚埃際</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Thu ngoài man cảnh về bên khuyết đình. Gần xa đã tỏ tình hình,</t>
+          <t>Cơ mưu Trịnh cũng gian hùng, Nghĩ mình chuyên tiếm ắt lòng ai ưa.</t>
         </is>
       </c>
     </row>
@@ -14602,12 +14602,12 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>武科買建法試每塘韜醫此芸刀弓</t>
+          <t>固黎余固彊暴。沛求貞德抵恆福鍾</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Mới sai chư tướng đề binh đánh liền. Chiềng Quang thành lũy vững bền,</t>
+          <t>Có Lê mới có đến giờ, Phải cầu hiền đức để nhờ phúc chung.</t>
         </is>
       </c>
     </row>
@@ -14619,12 +14619,12 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>匹場覆誠危衡，題名進士榜螭拱榮</t>
+          <t>其馭親鳳鬢蠅維淝本拱冥淵神明</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Bồ Chông núi cả cũng nên hiểm trời. Biến đâu trửu dịch lạ đời!</t>
+          <t>Kìa người mắt phượng, râu rồng, Duy Diêu vốn cũng là dòng thần minh.</t>
         </is>
       </c>
     </row>
@@ -14636,12 +14636,12 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>規漆四鎮兵丁術軍買幸愁營自剝</t>
+          <t>夏臺星釋前星園韻群抵沒梗福枝</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>Nửa đêm mở lũy cho người tiến sang. Bởi mưu Ngũ Phúc chiêu hàng,</t>
+          <t>Hạ đài khuất bóng tiền tinh, Khuôn thiêng còn để một cành phúc chi.</t>
         </is>
       </c>
     </row>
@@ -14653,12 +14653,12 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>公秘田土磬啓差官勘度刊穫民窮</t>
+          <t>啓魄求應拱奇，停哭鄭主暫緩異處</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Nguyễn Thiều trong lại đem đàng nội công. Vậy nên Duy Mật thế cùng, Hỏa Viêm một phút cô dung cũng liều. Cậy công Trịnh mới thêm kiêu,</t>
+          <t>Hay đâu cầu ứng cũng kỳ, Bỗng xui Trịnh chúa tạm di ra ngoài.</t>
         </is>
       </c>
     </row>
@@ -14670,12 +14670,12 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>巡行固使勸農。弊屢提路察馳民情</t>
+          <t>武公沒賤斬枚憐愷樣覽風裁帝王</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>Càng dầy đức sắc, càng nhiều ác cai. Vu oan nỡ đặt nên lời,</t>
+          <t>Vũ công một giấc hiên mai, Mơ màng đường thấy phong tài đế vương.</t>
         </is>
       </c>
     </row>
@@ -14687,12 +14687,12 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>愧書辨貝茄清、埭嗣埭驗吏爭術些</t>
+          <t>旌旗雅樂眾樣太平俊術贍賜極詔</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>Để cho thái tử thiệt tài thông minh. Phúc uy chuyên tiếm một mình,</t>
+          <t>Tinh kỳ nhã nhạc lạ nhường, Thái bình nghi vệ rõ ràng chẳng ngoa.</t>
         </is>
       </c>
     </row>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>立碑蓮賭呪河界強自意員分明</t>
+          <t>創晨舫買醒墨維襖俊鍊麴茄還鞘</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>Mạo giầy điên đảo, nghĩa danh còn gì? Thế mà vạc cả duy trì,</t>
+          <t>Sáng mai vừa mới tỉnh ra, Duy Diêu xảy đến chơi nhà lạ sao?</t>
         </is>
       </c>
     </row>
@@ -14721,12 +14721,12 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>殖剔鄭買扶蓮頭宗自意齋傳毀鱉</t>
+          <t>覧馭麻驗占色買啓朕兆應剱自然</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Bởi tiên liệt thánh Nam kỳ nối ngôi. Nền danh phận, đạo vua tôi,</t>
+          <t>Thấy người mà nghiệm chiêm bao, Mới hay trẫm triệu ứng vào tự nhiên.</t>
         </is>
       </c>
     </row>
@@ -14738,12 +14738,12 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>運黎鍊狀褒顏披穢撫禎潮嶺黔埃</t>
+          <t>殖剔鄭買扶蓮頭宗自意齋傳毀鱉</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Gian hùng mất vía đứng ngồi sao an? Bấy giờ có giặc Tây Sơn,</t>
+          <t>Nghe lời Trịnh mới phù lên, Hiển Tông từ ấy chịu truyền nối ngôi.</t>
         </is>
       </c>
     </row>
@@ -14755,12 +14755,12 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>返欺慤役苓菱亂帥巳府賊非眾方</t>
+          <t>運黎鍊狀褒顏披穢撫禎潮嶺黔埃</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>Ở trong lại có Phúc Loan lộng hành. Thừa cơ Trịnh mới sai binh,</t>
+          <t>Vận Lê đến lúc suy đồi, Chắp tay rủ áo lặng ngồi mặc ai.</t>
         </is>
       </c>
     </row>
@@ -14772,12 +14772,12 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>文臣固仇舊揚范公廷重鏌塘畧韻</t>
+          <t>返欺慤役苓菱亂帥巳府賊非眾方</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Đưa thư vào trước kể tình ngoại thân. Rằng: Toan trừ đứa lộng thần,</t>
+          <t>Gặp khi nhiều việc chông gai,</t>
         </is>
       </c>
     </row>
@@ -14789,12 +14789,12 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>拋山擕荒旗桃阮蘧奄破阮求棋散</t>
+          <t>文臣固仇舊揚范公廷重鏌塘畧韻</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Cùng nhau quét sạch bụi trần cõi Tây. Lá cờ theo ngọn gió bay,</t>
+          <t>Văn thần có kẻ phấn dương, Phạm Công Đình Trọng gồm đường lược thao.</t>
         </is>
       </c>
     </row>
@@ -14806,12 +14806,12 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>阮芳據獨尊山，宣興界坦林密界旅</t>
+          <t>拋山擕荒旗桃阮蘧奄破阮求棋散</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Thừa hư trực để vào ngay Nhà Hồ. Phúc Loan đem lại hiến phù,</t>
+          <t>Phao Sơn trỏ ngọn cờ đào, Nguyễn Cừ đã phá, Nguyễn Cầu cũng tan.</t>
         </is>
       </c>
     </row>
@@ -14823,12 +14823,12 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>鄭王決志衝坡之巢挾滌兵車買衛</t>
+          <t>阮芳據獨尊山，宣興界坦林密界旅</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Trịnh binh nhân thế tràng khu dưới thành. Đôi bên lập lũy phân dinh,</t>
+          <t>Nguyễn Phương cứ Độc Tôn Sơn, Tuyên, Hưng là đất, lâm man là nhà.</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>權姦維禦惕例鄭森吏拱逞武功</t>
+          <t>鄭王決志衝坡之巢挾滌兵車買衛</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Trầm Than mấy trận quan binh hiểm nghèo. Độ quân nọ bắc phù kiều,</t>
+          <t>Trịnh vương quyết chí xông pha, Huyệt sào quét sạch, binh xa mới về.</t>
         </is>
       </c>
     </row>
@@ -14857,12 +14857,12 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>孟天豁瀟冸劔，喚群黃質林松隱身</t>
+          <t>權姦維禦惕例鄭森吏拱逞武功</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>Thúy Hoa phất phới qua đèo Hải Vân. Quảng Nam đồn trú lục quân,</t>
+          <t>Quyền gian kế tập quen lề, Trịnh Sâm lại cũng sính nghề vũ công.</t>
         </is>
       </c>
     </row>
@@ -14874,12 +14874,12 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>差段阮徹鬼軍劳嶺繻獸沒參買清</t>
+          <t>孟天豁瀟冸劔，喚群黃質林松隱身</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>Trong Tây ngoài Trịnh, xa gần với ai? Thuyền rồng vào bến Đồng Nai,</t>
+          <t>Mạnh Thiên hang thẳm núi cùng, Hãy còn Hoàng Chất lâm tùng ẩn thân.</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>吏算揲揆頒寧令災地葛人情渚帽</t>
+          <t>差段阮徹鬼軍劳嶺繻獸沒參買清</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Long Hưng còn đợi cơ trời có khi. Gió thu lần úa cành Lê,</t>
+          <t>Sai Đoàn Nguyễn Thục đem quân, Cùng rừng săn thú một lần mới thanh.</t>
         </is>
       </c>
     </row>
@@ -14908,12 +14908,12 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>地圖埃窖賡鍼收外蛮境術边開庭</t>
+          <t>吏算揲揆頒寧令災地葛人情渚帽</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Ác bay chưa biết đỗ về nhà ai. Ngụy Tây gắm ghé mặt ngoài,</t>
+          <t>Lại toan dẹp cõi Trấn Ninh, Chỉn e địa thế, dân tình chưa quen.</t>
         </is>
       </c>
     </row>
@@ -14925,12 +14925,12 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>斂賒乞燼情形買差諸將提兵打連</t>
+          <t>地圖埃窖賡鍼收外蛮境術边開庭</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Trịnh Sâm trong lại sai người cầu phong. Vũ Trần Thiệu kể là trung,</t>
+          <t>Địa đồ ai khéo vẽ nên, Thu ngoài man cảnh về bên khuyết đình.</t>
         </is>
       </c>
     </row>
@@ -14942,12 +14942,12 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>呈光城壘伉紂蒲葵尚奇拱鉞險至</t>
+          <t>斂賒乞燼情形買差諸將提兵打連</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>Mặt tuy ứng mệnh, nhưng lòng vẫn kiên. Động Đình xa vượt bè tiên,</t>
+          <t>Gần xa đã tỏ tình hình, Mới sai chư tướng đề binh đánh liền.</t>
         </is>
       </c>
     </row>
@@ -14959,12 +14959,12 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>変竟時腋選茯婢脹翹壘朱歇進鄭</t>
+          <t>呈光城壘伉紂蒲葵尚奇拱鉞險至</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Trên trời dưới nước tấm nguyền sạch trong. Biểu tiên phó ngọn đuốc hồng,</t>
+          <t>Chiềng Quang thành lũy vững bền, Bồ Chông núi cả cũng nên hiểm trời.</t>
         </is>
       </c>
     </row>
@@ -14976,12 +14976,12 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>點謀五福報降院環敵吏掩塘內攻</t>
+          <t>変竟時腋選茯婢脹翹壘朱歇進鄭</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>Ngậm cười thề với chén nồng cho xuôi. Làm cho vỡ mật gian hồi,</t>
+          <t>Biến đâu trửu dịch lạ đời! Nửa đêm mở lũy cho người tiến sang.</t>
         </is>
       </c>
     </row>
@@ -14993,12 +14993,12 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>五轍維襖芳旁火炎沒張瘡拱料</t>
+          <t>點謀五福報降院環敵吏掩塘內攻</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>Mà người chìm nổi trong đời thẹn riêng. Xoay vần hay có khuôn thiêng,</t>
+          <t>Bởi mưu Ngũ Phúc chiêu hàng, Nguyễn Thiều trong lại đem đàng nội công.</t>
         </is>
       </c>
     </row>
@@ -15010,12 +15010,12 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>惱功鄭買漆驕強諦德色強慾惡茇</t>
+          <t>五轍維襖芳旁火炎沒張瘡拱料</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Càng già cỗi ác, càng nghiêng sóng tình. Tuyên phi là gái khuynh thành,</t>
+          <t>Vậy nên Duy Mật thế cùng, Hỏa Viêm một phút cô dung cũng liều.</t>
         </is>
       </c>
     </row>
@@ -15027,12 +15027,12 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>證冤女達鋮剝抵朱太子舌才聰明</t>
+          <t>惱功鄭買漆驕強諦德色強慾惡茇</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Đem bề ân ái chuyên vành phúc uy. Đêm ngày riêng một buồng the,</t>
+          <t>Cậy công Trịnh mới thêm kiêu, Càng dầy đức sắc, càng nhiều ác cai.</t>
         </is>
       </c>
     </row>
@@ -15044,12 +15044,12 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>福威專僭沒軸帽踣顱倒美各群也</t>
+          <t>證冤女達鋮剝抵朱太子舌才聰明</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>Cướp quyền đích trưởng dựng bè đồng mông. Yên cơ khí diễm càng nồng,</t>
+          <t>Vu oan nỡ đặt nên lời, Để cho thái tử thiệt tài thông minh.</t>
         </is>
       </c>
     </row>
@@ -15061,12 +15061,12 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>世麻巖奇維持黝先</t>
+          <t>福威專僭沒軸帽踣顱倒美各群也</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Khiến nên Trịnh Khải sinh lòng âm mưu. E khi sự thế đáo đầu,</t>
+          <t>Phúc uy chuyên tiếm một mình, Mạo giầy điên đảo, nghĩa danh còn gì?</t>
         </is>
       </c>
     </row>
@@ -15078,12 +15078,12 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>列聖南畿蹤跡</t>
+          <t>世麻巖奇維持黝先</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Ước cùng các trấn đều vào giúp công. Điển thư có đứa hầu trong,</t>
+          <t>Thế mà vạc cả duy trì, Bởi tiên liệt thánh Nam kỳ nối ngôi.</t>
         </is>
       </c>
     </row>
@@ -15095,14 +15095,10 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>坼名分道希碎，姦雄壯驄蹲蛛鞠安</t>
-        </is>
-      </c>
-      <c r="C864" t="inlineStr">
-        <is>
-          <t>Tin lòng nên mới ngỏ cùng Ngô Nhâm. Người sao chẳng chút lương tâm!</t>
-        </is>
-      </c>
+          <t>列聖南畿蹤跡</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr"/>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -15112,12 +15108,12 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>閉關固賊西山，於帥吏固福壺弄行</t>
+          <t>坼名分道希碎，姦雄壯驄蹲蛛鞠安</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Khoa danh đã nhục, quan trâm cũng hoài! Lòng riêng tham đắm mùi đời,</t>
+          <t>Nền danh phận, đạo vua tôi, Gian hùng mất vía đứng ngồi sao an?</t>
         </is>
       </c>
     </row>
@@ -15129,12 +15125,12 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>乘機鄭買差兵。遊書急耀訃情外親</t>
+          <t>閉關固賊西山，於帥吏固福壺弄行</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Phụ tình thày tớ, cãi lời phụ thân. Quyết đem sự ấy củ trần,</t>
+          <t>Bấy giờ có giặc Tây Sơn, Ở trong lại có Phúc Loan lộng hành.</t>
         </is>
       </c>
     </row>
@@ -15146,12 +15142,12 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>浪算除撥弄臣共韜挾滌堀麼揆西</t>
+          <t>乘機鄭買差兵。 遊書急耀訃情外親</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>Làm cho Trịnh Khải một lần châu liên. Sâm già, Cán lại thiếu niên,</t>
+          <t>Thừa cơ Trịnh mới sai binh, Đưa thư vào trước kể tình ngoại thân.</t>
         </is>
       </c>
     </row>
@@ -15163,12 +15159,12 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>萬旗號荒愈懸乘虛真抵敵豈胡</t>
+          <t>浪算除撥弄臣共韜挾滌堀麼揆西</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Phó cho Hoàng Bảo giúp nên sao đành? Tuyên phi học thói buông mành,</t>
+          <t>Rằng: Toan trừ đứa lộng thần, Cùng nhau quét sạch bụi trần cõi Tây.</t>
         </is>
       </c>
     </row>
@@ -15180,12 +15176,12 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>福蠱鬼吏獻俘鄭兵因芳長驅鄴城</t>
+          <t>萬旗號荒愈懸乘虛真抵敵豈胡</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Trong dưa dưới mận nhân tình đều nghi. Ở trong Khải mới thừa ky,</t>
+          <t>Lá cờ theo ngọn gió bay, Thừa hư trực để vào ngay Nhà Hồ.</t>
         </is>
       </c>
     </row>
@@ -15197,12 +15193,12 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>堆边立壘分營沉漚余陣官兵險鬱</t>
+          <t>福蠱鬼吏獻俘鄭兵因芳長驅鄴城</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Ngoài quân ba phủ nhân khi lộng hành. Cùng nhau sáp huyết hội minh,</t>
+          <t>Phúc Loan đem lại hiến phù, Trịnh binh nhân thế tràng khu dưới thành.</t>
         </is>
       </c>
     </row>
@@ -15214,12 +15210,12 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>渡兵奴北浮橋，翠花法派戈宮海雲</t>
+          <t>堆边立壘分營沉漚余陣官兵險鬱</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Trống hồi chửa dứt, các dinh đã vào. Cửa thành binh lửa xôn xao,</t>
+          <t>Đôi bên lập lũy phân dinh, Trầm Than mấy trận quan binh hiểm nghèo.</t>
         </is>
       </c>
     </row>
@@ -15231,12 +15227,12 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>廣南苑駐藏六軍馳西北鄭縣斯貝埃</t>
+          <t>渡兵奴北浮橋，翠花法派戈宮海雲</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>Một cơn cỏ nội cá ao còn gì! Cán vong, Khải lại tiếm vì,</t>
+          <t>Độ quân nọ bắc phù kiều, Thúy Hoa phất phới qua đèo Hải Vân.</t>
         </is>
       </c>
     </row>
@@ -15248,12 +15244,12 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>船蠅忿渡同犯龜與群待机至固欺</t>
+          <t>廣南苑駐藏六軍馳西北鄭縣斯貝埃</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>Phủ binh từ ấy nhiều bề tuyên kiêu. Hung hăng ngoài phố trong triều,</t>
+          <t>Quảng Nam đồn trú lục quân, Trong Tây ngoài Trịnh, xa gần với ai?</t>
         </is>
       </c>
     </row>
@@ -15265,12 +15261,12 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>頤秋苦慮梗黎鴻懸渚別杜術為埃</t>
+          <t>船蠅忿渡同犯龜與群待机至固欺</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>Phá nhà cướp của, dập dìu vào ra. Đầy đường những tiếng oán ta,</t>
+          <t>Thuyền rồng vào bến Đồng Nai, Long Hưng còn đợi cơ trời có khi.</t>
         </is>
       </c>
     </row>
@@ -15282,12 +15278,12 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>偽西聯騎麵外鄭森帥吏差馭求封</t>
+          <t>頤秋苦慮梗黎鴻懸渚別杜術為埃</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>Văn thần, võ tướng đều là bó tay. Tiếng đồn nghe đến giặc Tây,</t>
+          <t>Gió thu lần úa cành Lê, Ác bay chưa biết đỗ về nhà ai.</t>
         </is>
       </c>
     </row>
@@ -15299,12 +15295,12 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>武陳紹詐邪忠穂雖應命仍義勿堅</t>
+          <t>偽西聯騎麵外鄭森帥吏差馭求封</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Tiềm mưu còn rắp đợi ngày xuất chinh. Có tên Nguyễn Chỉnh tài danh,</t>
+          <t>Ngụy Tây gắm ghé mặt ngoài, Trịnh Sâm trong lại sai người cầu phong.</t>
         </is>
       </c>
     </row>
@@ -15316,12 +15312,12 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>洞庭縣蹤愛仙蓮歪鄴浩心願瀝澀</t>
+          <t>武陳紹詐邪忠穂雖應命仍義勿堅</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Nhân khi tao loạn đem mình hàng Tây. Cơ quan mưu lược vẽ bầy, Cam lòng nước cũ, mượn tay người ngoài. Tây Sơn biết tỏ một hai,</t>
+          <t>Vũ Trần Thiệu kể là trung, Mặt tuy ứng mệnh, nhưng lòng vẫn kiên.</t>
         </is>
       </c>
     </row>
@@ -15333,12 +15329,12 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>表箋付荒燭烘吟興誓貝殻艙朱渙</t>
+          <t>洞庭縣蹤愛仙蓮歪鄴浩心願瀝澀</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Chia quân thủy bộ quyết bài kéo ra. Ngọn cờ trỏ lối sơn pha,</t>
+          <t>Động Đình xa vượt bè tiên, Trên trời dưới nước tấm nguyền sạch trong.</t>
         </is>
       </c>
     </row>
@@ -15350,12 +15346,12 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>少朱碗腔姦回麻臥泥沒鈴蔑穢</t>
+          <t>表箋付荒燭烘吟興誓貝殻艙朱渙</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>Hải Vân đồn trấn, đâu là chẳng tan? Cánh buồm đè lớp cuồng lan,</t>
+          <t>Biểu tiên phó ngọn đuốc hồng, Ngậm cười thề với chén nồng cho xuôi.</t>
         </is>
       </c>
     </row>
@@ -15367,12 +15363,12 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>磋運呂固園韻強魏禬惡強迎涇情</t>
+          <t>少朱碗腔姦回麻臥泥沒鈴蔑穢</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Cát Dinh, Động Hải quân quan chạy dài. Ngụy Tây còn sợ mặt ngoài,</t>
+          <t>Làm cho vỡ mật gian hồi, Mà người chìm nổi trong đời thẹn riêng.</t>
         </is>
       </c>
     </row>
@@ -15384,12 +15380,12 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>宣妃異妨傾城恍友恩愛專徵福威</t>
+          <t>磋運呂固園韻強魏禬惡強迎涇情</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>Rắp ngăn Tràng Lũy tính bài phân vương. Khéo đâu Chỉnh lại đưa đường,</t>
+          <t>Xoay vần hay có khuôn thiêng, Càng già cỗi ác, càng nghiêng sóng tình.</t>
         </is>
       </c>
     </row>
@@ -15401,12 +15397,12 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>賭韋禎沒雛絶切權嫡長孕愛童蒙</t>
+          <t>宣妃異妨傾城恍友恩愛專徵福威</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>Rằng: Trong sự thế chi nhường cho ai? Tướng công uy nhức bên trời,</t>
+          <t>Tuyên phi là gái khuynh thành, Đem bề ân ái chuyên vành phúc uy.</t>
         </is>
       </c>
     </row>
@@ -15418,12 +15414,12 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>效姖彞熖強皰違賊鄭楷生悉陰謀</t>
+          <t>賭韋禎沒雛絶切權嫡長孕愛童蒙</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>Nay cơ phá trúc hẳn mười chẳng xa. Bấy lâu họ Trịnh gian tà,</t>
+          <t>Đêm ngày riêng một buồng the, Cướp quyền đích trưởng dựng bè đồng mông.</t>
         </is>
       </c>
     </row>
@@ -15435,12 +15431,12 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>哭欺事勞到頭約共各頸調尫勤功</t>
+          <t>效姖彞熖強皰違賊鄭楷生悉陰謀</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>Binh kiêu, dân oán ắt là bại vong. Uy trời ai dám tranh phong,</t>
+          <t>Yên cơ khí diễm càng nồng, Khiến nên Trịnh Khải sinh lòng âm mưu.</t>
         </is>
       </c>
     </row>
@@ -15452,12 +15448,12 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>典書固質侯融信悉誠買昨共吳士</t>
+          <t>哭欺事勞到頭約共各頸調尫勤功</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>Hãy xin thừa thắng ruổi giong cõi ngoài. Phải chăng, Huệ mới nghe lời,</t>
+          <t>E khi sự thế đáo đầu, Ước cùng các trấn đều vào giúp công.</t>
         </is>
       </c>
     </row>
@@ -15469,12 +15465,12 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>彖輿極拙良心科名無辱冠簪拱懷</t>
+          <t>典書固質侯融信悉誠買昨共吳士</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Lại cho Nguyễn Chỉnh lĩnh bài tiên phong. Lá buồm theo ngọn gió đông,</t>
+          <t>Điển thư có đứa hầu trong, Tin lòng nên mới ngỏ cùng Ngô Nhâm.</t>
         </is>
       </c>
     </row>
@@ -15486,12 +15482,12 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>悉禎貧瀨嘯荒負情傑個惡剝父親</t>
+          <t>彖輿極拙良心科名無辱冠簪拱懷</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Vượt qua cửa bể vào sông Vị Hoàng. Quân dung, đâu mới lạ nhường!</t>
+          <t>Người sao chẳng chút lương tâm! Khoa danh đã nhục, quan trâm cũng hoài!</t>
         </is>
       </c>
     </row>
@@ -15503,12 +15499,12 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>決宓事意斜陳：夕朱鄭楷沒吝棟連</t>
+          <t>悉禎貧瀨嘯荒負情傑個惡剝父親</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Mão mao, áo đỏ chật đường kéo ra. Bụi hồng mờ mịt kinh hoa,</t>
+          <t>Lòng riêng tham đắm mùi đời, Phụ tình thày tớ, cãi lời phụ thân.</t>
         </is>
       </c>
     </row>
@@ -15520,12 +15516,12 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>森巍嶽吏少年付朱黃宝鵟城韁鳴</t>
+          <t>決宓事意斜陳：夕朱鄭楷沒吝棟連</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Lục Môn, Thúy Ái gần xa tan tành. Quyết liều Trịnh mới thân chinh,</t>
+          <t>Quyết đem sự ấy củ trần, Làm cho Trịnh Khải một lần châu liên.</t>
         </is>
       </c>
     </row>
@@ -15537,12 +15533,12 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>豈妃李腿橈薦馳徐鄴櫻人情調疑</t>
+          <t>森巍嶽吏少年付朱黃宝鵟城韁鳴</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Tây Luông giáp trận, quân mình đảo qua. Nài voi toan trở lại nhà,</t>
+          <t>Sâm già, Cán lại thiếu niên, Phó cho Hoàng Bảo giúp nên sao đành?</t>
         </is>
       </c>
     </row>
@@ -15554,12 +15550,12 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>於鈔楷乘貿槸外軍匹府因欺弄行</t>
+          <t>豈妃李腿橈薦馳徐鄴櫻人情調疑</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Cờ Tây Sơn đã mở ra đầy thành. Qua Hạ Lôi rắp lánh mình,</t>
+          <t>Tuyên phi học thói buông mành, Trong dưa dưới mận nhân tình đều nghi.</t>
         </is>
       </c>
     </row>
@@ -15571,12 +15567,12 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>共饒戰血會盟犧同渚揺各營缶底</t>
+          <t>於鈔楷乘貿槸外軍匹府因欺弄行</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Giữa đường gặp đứa phụ tình bắt ra. Ngụy Tây vốn kẻ hung tà,</t>
+          <t>Ở trong Khải mới thừa ky, Ngoài quân ba phủ nhân khi lộng hành.</t>
         </is>
       </c>
     </row>
@@ -15588,12 +15584,12 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>圍城兵煖斂敵沒千韃內蠻渾群之</t>
+          <t>共饒戰血會盟犧同渚揺各營缶底</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Còn e người chốn Bắc Hà khó xong. Phù Lê có biểu mật phong,</t>
+          <t>Cùng nhau sáp huyết hội minh, Trống hồi chửa dứt, các dinh đã vào.</t>
         </is>
       </c>
     </row>
@@ -15605,12 +15601,12 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>衛亡楷吏借位府兵自意慾亥豈驕</t>
+          <t>圍城兵煖斂敵沒千韃內蠻渾群之</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Mặt ngoài trung nghĩa, trong lòng gian phi. Hiển Tông tuổi tác đã suy,</t>
+          <t>Cửa thành binh lửa xôn xao, Một cơn cỏ nội cá ao còn gì!</t>
         </is>
       </c>
     </row>
@@ -15622,12 +15618,12 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>凶興非庸帥朝破萊劫貼習戰敵番</t>
+          <t>衛亡楷吏借位府兵自意慾亥豈驕</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Nghe tin binh biến biết gì là đâu. Vừa khi Nguyễn Huệ vào hầu,</t>
+          <t>Cán vong, Khải lại tiếm vì, Phủ binh từ ấy nhiều bề tuyên kiêu.</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15635,12 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>浩塘仍嘗愁嗟文臣武將調界拚稱</t>
+          <t>凶興非庸帥朝破萊劫貼習戰敵番</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Vấn an lại kể gót đầu đinh ninh. Rằng: Nghe họ Trịnh cường hoành,</t>
+          <t>Hung hăng ngoài phố trong triều, Phá nhà cướp của, dập dìu vào ra.</t>
         </is>
       </c>
     </row>
@@ -15656,12 +15652,12 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>腎陀館鍾賊西潛謀群恠待詔出征</t>
+          <t>浩塘仍嘗愁嗟文臣武將調界拚稱</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>Vậy đem quân nghĩa quét thanh bụi trần. Chủ trương mừng thấy đông quân,</t>
+          <t>Đầy đường những tiếng oán ta, Văn thần, võ tướng đều là bó tay.</t>
         </is>
       </c>
     </row>
@@ -15673,12 +15669,12 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>固綴阮整才名因歎遺亂恍駕陥西</t>
+          <t>腎陀館鍾賊西　潛謀群恠待詔出征</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Thái bình cây cỏ được nhuần hơi mưa. Phúc lành chúc chữ cửu như,</t>
+          <t>Tiếng đồn nghe đến giặc Tây, Tiềm mưu còn rắp đợi ngày xuất chinh.</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15686,12 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>机開譜異蹤排情慧滲顴慢甕泉处</t>
+          <t>固綴阮整才名因歎遺亂恍駕陥西</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Của tin mấy quyển đồ thư dâng vào. Bệ rồng ban chiếu tinh bao,</t>
+          <t>Có tên Nguyễn Chỉnh tài danh, Nhân khi tao loạn đem mình hàng Tây.</t>
         </is>
       </c>
     </row>
@@ -15707,12 +15703,12 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>西山別驛沒舡劍軍水步決牌橋墨</t>
+          <t>机開譜異蹤排情慧滲顴慢甕泉处</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Gia phong Nguyễn Huệ đương trào quốc công. Ngọc Hân vừa trạc đào hồng,</t>
+          <t>Cơ quan mưu lược vẽ bầy, Cam lòng nước cũ, mượn tay người ngoài.</t>
         </is>
       </c>
     </row>
@@ -15724,12 +15720,12 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>荒旗擕搖山坂海雲屯鎮兇界挾散</t>
+          <t>西山別驛沒舡劍軍水步決牌橋墨</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>Ép duyên kim cải kết lòng sài lang. Đương cơn đòng bác ngổn ngang,</t>
+          <t>Tây Sơn biết tỏ một hai, Chia quân thủy bộ quyết bài kéo ra.</t>
         </is>
       </c>
     </row>
@@ -15741,12 +15737,12 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>鯤帆提笠枉瀾葛營洞海軍官綻颺</t>
+          <t>荒旗擕搖山坂海雲屯鎮兇界挾散</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Thực hư chửa tỏ, biến thường ai tin. Hơi tàn gần trở gót tiên,</t>
+          <t>Ngọn cờ trỏ lối sơn pha, Hải Vân đồn trấn, đâu là chẳng tan?</t>
         </is>
       </c>
     </row>
@@ -15758,12 +15754,12 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>偽西群慘麵外怯垠長壘併牌分王</t>
+          <t>鯤帆提笠枉瀾葛營洞海軍官綻颺</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Lại với Nguyễn Huệ gửi quyền quốc gia. Một hai xin trở về nhà,</t>
+          <t>Cánh buồm đè lớp cuồng lan, Cát Dinh, Động Hải quân quan chạy dài.</t>
         </is>
       </c>
     </row>
@@ -15775,12 +15771,12 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>害兇整吏盜塘，浪醉事芳之讎朱埃</t>
+          <t>偽西群慘麵外怯垠長壘併牌分王</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Bóng đèn, tiếng búa giám là di duyên. Bảo thành kinh lý đã yên,</t>
+          <t>Ngụy Tây còn sợ mặt ngoài, Rắp ngăn Tràng Lũy tính bài phân vương.</t>
         </is>
       </c>
     </row>
@@ -15792,12 +15788,12 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>將公戲或邊歪，咒機破竹罕過極險</t>
+          <t>害兇整吏盜塘，浪醉事芳之讎朱埃</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>Ngôi cao phó lại cháu hiền thừa gia. Duy Kỳ nối giữ nghiệp nhà,</t>
+          <t>Khéo đâu Chỉnh lại đưa đường, Rằng: Trong sự thế chi nhường cho ai?</t>
         </is>
       </c>
     </row>
@@ -15809,12 +15805,12 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>誦數戶鄭姦邪兵驕民恐凶罰敗亡</t>
+          <t>將公戲或邊歪，咒機破竹罕過極險</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>Cải nguyên Chiêu Thống mới là sơ niên. Huệ còn lưu ở Long Biên,</t>
+          <t>Tướng công uy nhức bên trời, Nay cơ phá trúc hẳn mười chẳng xa.</t>
         </is>
       </c>
     </row>
@@ -15826,12 +15822,12 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>威歪埃戰爭歸呆嗔乘勝驅騎撲外</t>
+          <t>誦數戶鄭姦邪兵驕民恐凶罰敗亡</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>Anh là Nguyễn Nhạc theo miền lại ra. Rước mời ngày tiếp đôi ba,</t>
+          <t>Bấy lâu họ Trịnh gian tà, Binh kiêu, dân oán ắt là bại vong.</t>
         </is>
       </c>
     </row>
@@ -15843,12 +15839,12 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>沛庄惠買贓剝吏阮朱整頗牌先辭</t>
+          <t>威歪埃戰爭歸呆嗔乘勝驅騎撲外</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Bệ từ Nhạc mới lân la tự tình: Đất, dân đâu cũng triều đình,</t>
+          <t>Uy trời ai dám tranh phong, Hãy xin thừa thắng ruổi giong cõi ngoài.</t>
         </is>
       </c>
     </row>
@@ -15860,12 +15856,12 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>羌帆蹏蕩臆東越戈禦潑釈淹渭漢</t>
+          <t>沛庄惠買贓剝吏阮朱整頗牌先辭</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>Giao lân rồi sẽ cất mình Nam quy. Nửa đêm ám hiệu cuốn kỳ,</t>
+          <t>Phải chăng, Huệ mới nghe lời, Lại cho Nguyễn Chỉnh lĩnh bài tiên phong.</t>
         </is>
       </c>
     </row>
@@ -15877,12 +15873,12 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>軍容宛貫眾樣帽毛襖覿質塘橋罌</t>
+          <t>羌帆蹏蕩臆東越戈禦潑釈淹渭漢</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Bao nhiêu tài hoá chuyên về sạch không. Bỏ Nguyễn Chỉnh ở Thăng Long,</t>
+          <t>Lá buồm theo ngọn gió đông, Vượt qua cửa bể vào sông Vị Hoàng.</t>
         </is>
       </c>
     </row>
@@ -15894,12 +15890,12 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>堆紅賺賤京華，綠門翠霧所賒散情</t>
+          <t>軍容宛貫眾樣　帽毛襖覿質塘橋罌</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>Cũng toan cắt cánh mở lồng với ai. Về quê Chỉnh mới giả bài,</t>
+          <t>Quân dung, đâu mới lạ nhường! Mão mao, áo đỏ chật đường kéo ra.</t>
         </is>
       </c>
     </row>
@@ -15911,12 +15907,12 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>次料鄭貝親征西竜夾陣軍騎倒戈</t>
+          <t>堆紅賺賤京華，綠門翠霧所賒散情</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Rằng vâng mật chỉ hồi sai đất nhà. Mộ quân hương dõng đem ra,</t>
+          <t>Bụi hồng mờ mịt kinh hoa, Lục Môn, Thúy Ái gần xa tan tành.</t>
         </is>
       </c>
     </row>
@@ -15928,12 +15924,12 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>捺鴻算阻夷笳</t>
+          <t>次料鄭貝親征西竜夾陣軍騎倒戈</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>Ngoài là chống giặc, trong là giữ kinh. Cựu thần mấy kẻ công khanh, Thoái hưu để việc miếu đình cho ai? Tân khoa còn có một hai,</t>
+          <t>Quyết liều Trịnh mới thân chinh, Tây Luông giáp trận, quân mình đảo qua.</t>
         </is>
       </c>
     </row>
@@ -15945,12 +15941,12 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>旗西山奄翔罨渾城</t>
+          <t>捺鴻算阻夷笳</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>Bùi Dương, Trần Án cũng ngươi trung trinh. Cùng nhau phụng sắc triệu binh,</t>
+          <t>Nài voi toan trở lại nhà, Cờ Tây Sơn đã mở ra đầy thành.</t>
         </is>
       </c>
     </row>
@@ -15962,12 +15958,12 @@
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>戈夏雷恆另駕弾塘返授負情扒墨</t>
+          <t>旗西山奄翔罨渾城</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Thổ hào củ tập vào kinh hộ tuỳ. Phân vân tranh lập nhiều bề,</t>
+          <t>Cờ Tây Sơn đã mở ra đầy thành.</t>
         </is>
       </c>
     </row>
@@ -15979,12 +15975,12 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>偽西本仇凶邪群聚歌淮北河難衝</t>
+          <t>戈夏雷恆另駕　　弾塘返授負情扒墨</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Kẻ phò Trịnh Lệ, người suy Trịnh Bồng. Yến Đô lại cứ tập phong,</t>
+          <t>Qua Hạ Lôi rắp lánh mình, Giữa đường gặp đứa phụ tình bắt ra.</t>
         </is>
       </c>
     </row>
@@ -15996,12 +15992,12 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>扶黎固袁密封麵成忠姜鈴悉姦</t>
+          <t>偽西本仇凶邪群聚歌淮北河難衝</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Những mưu phò Trịnh, quên lòng tôn Lê. Mậu Xưng, Tích Nhưỡng kể chi,</t>
+          <t>Ngụy Tây vốn kẻ hung tà, Còn e người chốn Bắc Hà khó xong.</t>
         </is>
       </c>
     </row>
@@ -16013,12 +16009,12 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>顯宗歲作色衰贈賀兵變別之野喪</t>
+          <t>扶黎固袁密封麵成忠姜鈴悉姦</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Phùng Cơ còn biết thị phi nhẽ thường. Trách thay Trọng Tế họ Dương,</t>
+          <t>Phù Lê có biểu mật phong, Mặt ngoài trung nghĩa, trong lòng gian phi.</t>
         </is>
       </c>
     </row>
@@ -16030,12 +16026,12 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>衛圭整買假牌浪鄂密白同差坦茄</t>
+          <t>顯宗歲作色衰贈賀兵變別之野喪</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Cũng trong khoa bảng, cùng phường đai cân. Sao không biết nghĩa quân thần,</t>
+          <t>Hiển Tông tuổi tác đã suy, Nghe tin binh biến biết gì là đâu.</t>
         </is>
       </c>
     </row>
@@ -16047,12 +16043,12 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>募軍鄉勇冤環外界探賊訝焉狩京</t>
+          <t>衛圭整買假牌浪鄂密白同差坦茄</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Bầy mưu phế lập sắp quân vây thành. Non sông còn mặt triều đình,</t>
+          <t>Vừa khi Nguyễn Huệ vào hầu, Vấn an lại kể gót đầu đinh ninh.</t>
         </is>
       </c>
     </row>
@@ -16064,12 +16060,12 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>首臣然公卿退休抵從廟庭默埃</t>
+          <t>募軍鄉勇冤環外界探賊訝焉狩京</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Bạc đen xem thấy nhân tình mà ghê. Lê hoàng căm giận nhiều bề,</t>
+          <t>Mộ quân hương dõng đem ra, Ngoài là chống giặc, trong là giữ kinh.</t>
         </is>
       </c>
     </row>
@@ -16081,12 +16077,12 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>新科郡固沒台裴楊陳案拱歇貞貞</t>
+          <t>首臣然公卿退休抵從廟庭默埃</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Mật thư sai sứ đưa về Nghệ An.</t>
+          <t>Cựu thần mấy kẻ công khanh, Thoái hưu để việc miếu đình cho ai?</t>
         </is>
       </c>
     </row>
@@ -16098,12 +16094,12 @@
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>共魏奉敕召兵土豪紏集危京護隨</t>
+          <t>新科郡固沒台裴楊陳案拱歇貞貞</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Chỉnh xưa tuy giả mưu gian, được thư rầy mới nở gan anh hùng.</t>
+          <t>Tân khoa còn có một hai, Bùi Dương, Trần Án cũng ngươi trung trinh.</t>
         </is>
       </c>
     </row>
@@ -16115,12 +16111,12 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>紛紜爭立鬱戾仇扶鄭棣馭推鄭樵</t>
+          <t>共魏奉敕召兵土豪紏集危京護隨</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>Hịch bay đâu cũng nức lòng, Tứ Thành tứ Đột quân ròng hơn muôn.</t>
+          <t>Cùng nhau phụng sắc triệu binh, Thổ hào củ tập vào kinh hộ tuỳ.</t>
         </is>
       </c>
     </row>
@@ -16132,12 +16128,12 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>晏都吏據裏封仍謀扶鄭齊悉尊黎</t>
+          <t>紛紜爭立鬱戾仇扶鄭棣馭推鄭樵</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Dặm trường thẳng ruổi chinh an, Nghệ, Thanh quét sạch mấy đoàn kiến ong.</t>
+          <t>Phân vân tranh lập nhiều bề, Kẻ phò Trịnh Lệ, người suy Trịnh Bồng.</t>
         </is>
       </c>
     </row>
@@ -16149,12 +16145,12 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>茂稱騶攘訃之為基群別是非熙常</t>
+          <t>晏都吏據裏封仍謀扶鄭齊悉尊黎</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>Yến Đô sức yếu thế cùng, theo Dương Trọng Tế qua vùng Bắc Ninh.</t>
+          <t>Yến Đô lại cứ tập phong, Những mưu phò Trịnh, quên lòng tôn Lê.</t>
         </is>
       </c>
     </row>
@@ -16166,12 +16162,12 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>責台仲濟戶楊拱齋科榜拱坊帶巾</t>
+          <t>茂稱騶攘訃之為基群別是非熙常</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Đại quân tiến đến kinh thành, Long Tân ngự duyệt, đại đình thưởng công.</t>
+          <t>Mậu Xưng, Tích Nhưỡng kể chi, Phùng Cơ còn biết thị phi nhẽ thường.</t>
         </is>
       </c>
     </row>
@@ -16183,12 +16179,12 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>韞空別菱君臣排謀廢立揮軍圍城</t>
+          <t>責台仲濟戶楊拱齋科榜拱坊帶巾</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Loan thư ban trước thềm rồng, Cha phong Bằng Quận, con phong tước hầu.</t>
+          <t>Trách thay Trọng Tế họ Dương, Cũng trong khoa bảng, cùng phường đai cân.</t>
         </is>
       </c>
     </row>
@@ -16200,12 +16196,12 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>穢滯群穊朝庭沾顛紕覧人情麻緜</t>
+          <t>韞空別菱君臣排謀廢立揮軍圍城</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Trăm quan ngôi thứ ở đầu, Cánh vây sum họp, phủ lầu nghênh ngang.</t>
+          <t>Sao không biết nghĩa quân thần, Bầy mưu phế lập sắp quân vây thành.</t>
         </is>
       </c>
     </row>
@@ -16217,12 +16213,12 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>黎皇悄憐慾疚密書差使返術乂安</t>
+          <t>穢滯群穊朝庭沾顛紕覧人情麻緜</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Bốn phương lại động khói lang, Ngụy Tây riêng mặt bá vương một trời.</t>
+          <t>Non sông còn mặt triều đình, Bạc đen xem thấy nhân tình mà ghê.</t>
         </is>
       </c>
     </row>
@@ -16234,12 +16230,12 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>整碧雖假謀奸特書覊買妄肝英雄</t>
+          <t>黎皇悄憐慾疚密書差使返術乂安</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Nhạc, Quy Nhơn; Lữ, Đồng Nai, Quảng Nam, Nguyễn Huệ; trong ngoài chia nhau.</t>
+          <t>Lê hoàng căm giận nhiều bề, Mật thư sai sứ đưa về Nghệ An.</t>
         </is>
       </c>
     </row>
@@ -16251,12 +16247,12 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>檄愁喪拱隂禿四成四突軍淵放仞</t>
+          <t>整碧雖假謀奸特書覊買妄肝英雄</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Nhân cơ lại dấy qua mâu, Văn Nhậm vâng lệnh quân phù kéo ra.</t>
+          <t>Chỉnh xưa tuy giả mưu gian, Được thư rầy mới nở gan anh hùng.</t>
         </is>
       </c>
     </row>
@@ -16268,12 +16264,12 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>戰長離轘征鞍乂清挾瀝余團蜆蠅</t>
+          <t>檄愁喪拱隂禿四成四突軍淵放仞</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Qua Nghệ An, đến Thanh Hoa, Thổ Sơn giáp trận, Trinh Hà áp binh.</t>
+          <t>Hịch bay đâu cũng nức lòng, Tứ Thành tứ Đột quân ròng hơn muôn.</t>
         </is>
       </c>
     </row>
@@ -16285,12 +16281,12 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>晏都飭要芳穷駭楊仲濟文進北寧</t>
+          <t>戰長離轘征鞍乂清挾瀝余團蜆蠅</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>Giặc ra đến đất Ninh Bình, Chỉnh đem hai vạn tinh binh quyết liều.</t>
+          <t>Dặm trường thẳng ruổi chinh an, Nghệ, Thanh quét sạch mấy đoàn kiến ong.</t>
         </is>
       </c>
     </row>
@@ -16302,12 +16298,12 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>大軍進興京城竜津御調大庭賞功</t>
+          <t>晏都飭要芳穷駭楊仲濟文進北寧</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Một đêm thuyền trái buồm xiêu, vì con sơ suất, đền điều thua công.</t>
+          <t>Yến Đô sức yếu thế cùng, Theo Dương Trọng Tế qua vùng Bắc Ninh.</t>
         </is>
       </c>
     </row>
@@ -16319,12 +16315,12 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>書書班耀墳蠅吐封鵬郡魏封爵侯</t>
+          <t>大軍進興京城竜津御調大庭賞功</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Văn Nhậm kéo đến Thăng Long, Lê Hoàng thảng thốt qua sông Nhị Hà.</t>
+          <t>Đại quân tiến đến kinh thành, Long Tân ngự duyệt, đại đình thưởng công.</t>
         </is>
       </c>
     </row>
@@ -16336,12 +16332,12 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>幕官魈次於頭翹圍森合府棲巡昂</t>
+          <t>書書班耀墳蠅吐封鵬郡魏封爵侯</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Bắc Ninh cũng đất dân nhà, Bạc thay Cảnh Thước sao mà bất nhân!</t>
+          <t>Loan thư ban trước thềm rồng, Cha phong Bằng Quận, con phong tước hầu.</t>
         </is>
       </c>
     </row>
@@ -16353,12 +16349,12 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>眾方吏動燭狼偽西禎穪覇王沒至</t>
+          <t>幕官魈次於頭翹圍森合府棲巡昂</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Nỡ nào quên nghĩa cố quân, đóng thành không rước, sai quân cướp đường.</t>
+          <t>Trăm quan ngôi thứ ở đầu, Cánh vây sum họp, phủ lầu nghênh ngang.</t>
         </is>
       </c>
     </row>
@@ -16370,12 +16366,12 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>岳歸仁侄同犯廣南阮惠誡求斂</t>
+          <t>眾方吏動燭狼偽西禎穪覇王沒至</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Ngự bào cũng nhuộm mầu sương, Nguyệt Giang, Mục Thị nhiều đường gian nguy.</t>
+          <t>Bốn phương lại động khói lang, Ngụy Tây riêng mặt bá vương một trời.</t>
         </is>
       </c>
     </row>
@@ -16387,12 +16383,12 @@
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>因機吏趣戈矛文士鄂頎軍符橋罌</t>
+          <t>岳歸仁侄同犯廣南阮惠誡求斂</t>
         </is>
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Tây binh thừa thế cùng truy, Cha con Nguyễn Chỉnh một kỳ trận vong.</t>
+          <t>Nhạc, Quy Nhơn; Lữ, Đồng Nai, Quảng Nam, Nguyễn Huệ; trong ngoài chia nhau.</t>
         </is>
       </c>
     </row>
@@ -16404,12 +16400,12 @@
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>戈乂安鍊清華土山夌陣貞河押兵</t>
+          <t>因機吏趣戈矛文士鄂頎軍符橋罌</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Bắt phu canh giữ bên sông, Kìa Dương Đình Tuấn cũng mong phù trì.</t>
+          <t>Nhân cơ lại dấy qua mâu, Văn Nhậm vâng lệnh quân phù kéo ra.</t>
         </is>
       </c>
     </row>
@@ -16421,12 +16417,12 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>賊盟鍥坦寧平整冤任萬精兵決料</t>
+          <t>戈乂安鍊清華土山夌陣貞河押兵</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Chước đâu phản gián mới kỳ, để cho xa giá chạy về Chí Linh.</t>
+          <t>Qua Nghệ An, đến Thanh Hoa, Thổ Sơn giáp trận, Trinh Hà áp binh.</t>
         </is>
       </c>
     </row>
@@ -16438,12 +16434,12 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>沒艦船債帆漂為掄踐率興調輸功</t>
+          <t>賊盟鍥坦寧平整冤任萬精兵決料</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Vội vàng chưa định hành dinh, mà Đinh Tích Nhưỡng nỡ tình đuổi theo!</t>
+          <t>Giặc ra đến đất Ninh Bình, Chỉnh đem hai vạn tinh binh quyết liều.</t>
         </is>
       </c>
     </row>
@@ -16455,12 +16451,12 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>文士撫鍵昇竈，黎皇簷猝戈淹珥河</t>
+          <t>沒艦船債帆漂為掄踐率興調輸功</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>Giải vây lại có thổ hào, Lũ Hoàng Xuân Tú cũng đều cần vương.</t>
+          <t>Một đêm thuyền trái buồm xiêu, Vì con sơ suất, đền điều thua công.</t>
         </is>
       </c>
     </row>
@@ -16472,12 +16468,12 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>地寧拱坦民茄。涓台景驟蝗麻不仁</t>
+          <t>文士撫鍵昇竈，黎皇簷猝戈淹珥河</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Thừa dư vừa đến Thủy Đường, Kẻ về tấu tiệp, người sang đầu thành. Bỗng đâu thuyền bạt vào Thanh,</t>
+          <t>Văn Nhậm kéo đến Thăng Long, Lê Hoàng thảng thốt qua sông Nhị Hà.</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16485,12 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>女帝寢姜故君操城空遠差軍劫塘</t>
+          <t>地寧拱坦民茄。涓台景驟蝗麻不仁</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Nước non man mác, quân tình ngẩn ngơ. Văn Nhậm tự ấy lại giờ,</t>
+          <t>Bắc Ninh cũng đất dân nhà, Bạc thay Cảnh Thước sao mà bất nhân!</t>
         </is>
       </c>
     </row>
@@ -16506,12 +16502,12 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>御絕洪染午霜月江日沛怒塘雉危</t>
+          <t>女帝寢姜故君操城空遠差軍劫塘</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Vỗ về sĩ tốt, đợi chờ chúa công. Huệ sao tàn nhẫn cam lòng,</t>
+          <t>Nỡ nào quên nghĩa cố quân, Đóng thành không rước, sai quân cướp đường.</t>
         </is>
       </c>
     </row>
@@ -16523,12 +16519,12 @@
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>西兵乘芳旁追。叱摠阮整沒期亡陣</t>
+          <t>御絕洪染午霜月江日沛怒塘雉危</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>Một gươm nỡ quyết chẳng dong tướng thần. Mới đòi hào mục xa gần,</t>
+          <t>Ngự bào cũng nhuộm mầu sương, Nguyệt Giang, Mục Thị nhiều đường gian nguy.</t>
         </is>
       </c>
     </row>
@@ -16540,12 +16536,12 @@
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>扒夫更狩邊境。箕楊庭俊拱懐扶持</t>
+          <t>西兵乘芳旁追。叱摠阮整沒期亡陣</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Xem nhân tình có mười phần thuận không? Nguyễn Huy Trạc cũng hào hùng,</t>
+          <t>Tây binh thừa thế cùng truy, Cha con Nguyễn Chỉnh một kỳ trận vong.</t>
         </is>
       </c>
     </row>
@@ -16557,12 +16553,12 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>酌燒反伺買奇，抵朱車駕縫術至靈</t>
+          <t>扒夫更狩邊境。箕楊庭俊拱懐扶持</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Một thang tiết nghĩa quyết lòng quyên sinh. Biết thiên hạ chẳng thuận tình,</t>
+          <t>Bắt phu canh giữ bên sông, Kìa Dương Đình Tuấn cũng mong phù trì.</t>
         </is>
       </c>
     </row>
@@ -16574,12 +16570,12 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>倍廣諸定行營，麻丁錫壤女情過疏</t>
+          <t>酌燒反伺買奇，抵朱車駕縫術至靈</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>Lập người giám quốc đem binh lại về. Lê hoàng truân kiển nhiều bề,</t>
+          <t>Chước đâu phản gián mới kỳ, Để cho xa giá chạy về Chí Linh.</t>
         </is>
       </c>
     </row>
@@ -16591,12 +16587,12 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>解圍吏固土豪婁黃春秀拱調勤王</t>
+          <t>倍廣諸定行營，麻丁錫壤女情過疏</t>
         </is>
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Mẹ con cách trở biết về nơi đâu? Thái từ lạc tới Long Châu,</t>
+          <t>Vội vàng chưa định hành dinh, Mà Đinh Tích Nhưỡng nỡ tình đuổi theo!</t>
         </is>
       </c>
     </row>
@@ -16608,12 +16604,12 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>乘興訪鍾水棠仇術奏捷獸趣投誠</t>
+          <t>解圍吏固土豪婁黃春秀拱調勤王</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Thổ quan dò hỏi tình đầu thủy chung. Cử lời đạt đến Quảng Đông,</t>
+          <t>Giải vây lại có thổ hào, Lũ Hoàng Xuân Tú cũng đều cần vương.</t>
         </is>
       </c>
     </row>
@@ -16625,12 +16621,12 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>停燒船拔釣清。滄嬝漫漠軍情良魚</t>
+          <t>乘興訪鍾水棠仇術奏捷獸趣投誠</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Gặp Tôn Sĩ Nghị cũng lòng mục lân. Một phong biểu tấu chín lần,</t>
+          <t>Thừa dư vừa đến Thủy Đường, Kẻ về tấu tiệp, người sang đầu thành.</t>
         </is>
       </c>
     </row>
@@ -16642,12 +16638,12 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>文士自意吏暴撫衛士卒待徐主公</t>
+          <t>停燒船拔釣清。滄嬝漫漠軍情良魚</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Càn Long có ý ân cần vì Lê. Đền rồng ban ấn tử nê,</t>
+          <t>Bỗng đâu thuyền bạt vào Thanh, Nước non man mác, quân tình ngẩn ngơ.</t>
         </is>
       </c>
     </row>
@@ -16659,12 +16655,12 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>惠輊殘忍甘恚沒鐮女災極容將臣</t>
+          <t>文士自意吏暴撫衛士卒待徐主公</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>Đem quân bốn tỉnh trao về một tay. Nam Quan thẳng lối đường mây,</t>
+          <t>Văn Nhậm tự ấy lại giờ, Vỗ về sĩ tốt, đợi chờ chúa công.</t>
         </is>
       </c>
     </row>
@@ -16676,12 +16672,12 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>買隊豪日賒斯祕人情固近分順空</t>
+          <t>惠輊殘忍甘恚　沒鐮女災極容將臣</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Tắt qua trấn Lạng, sang ngay sông Cầu. Tập công phá trại Nội Hầu,</t>
+          <t>Huệ sao tàn nhẫn cam lòng, Một gươm nỡ quyết chẳng dong tướng thần.</t>
         </is>
       </c>
     </row>
@@ -16693,12 +16689,12 @@
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>阮輝濯拱豪雄沒湯節姜決惡捐生</t>
+          <t>買隊豪日賒斯祕人情固近分順空</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Theo đường Kinh Bắc, tới đầu Nhị Giang. Rượu trâu đâu đã sẵn sàng,</t>
+          <t>Mới đòi hào mục xa gần, Xem nhân tình có mười phần thuận không?</t>
         </is>
       </c>
     </row>
@@ -16710,12 +16706,12 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>別天下強順情立歇監國擁兵吏術</t>
+          <t>阮輝濯拱豪雄沒湯節姜決惡捐生</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Vua Lê mừng thấy đón đàng khao binh. Tôn công quân lệnh túc thanh,</t>
+          <t>Nguyễn Huy Trạc cũng hào hùng, Một thang tiết nghĩa quyết lòng quyên sinh.</t>
         </is>
       </c>
     </row>
@@ -16727,12 +16723,12 @@
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>黎皇屯塞怒忈，燧飛隔阻別術厄聰</t>
+          <t>別天下強順情立歇監國擁兵吏術</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>Tơ hào chẳng phạm, tấm thành cũng phu. Qua sông mới bắc cầu phù,</t>
+          <t>Biết thiên hạ chẳng thuận tình, Lập người giám quốc đem binh lại về.</t>
         </is>
       </c>
     </row>
@@ -16744,12 +16740,12 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>太慈落細龜州，土官跴踐情頭始終</t>
+          <t>黎皇屯塞怒忈，燧飛隔阻別術厄聰</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Tây Luông quân đóng, Đông Đô ngự vào. Quốc vương sẵn ấn tay trao,</t>
+          <t>Lê hoàng truân kiển nhiều bề, Mẹ con cách trở biết về nơi đâu?</t>
         </is>
       </c>
     </row>
@@ -16761,12 +16757,12 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>掘剝達鍊廣東。返孫士殼拱悉睦鄰</t>
+          <t>太慈落細龜州，土官跴踐情頭始終</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>Đua nhau đều đến cửa quân đầu thầm.</t>
+          <t>Thái từ lạc tới Long Châu, Thổ quan dò hỏi tình đầu thủy chung.</t>
         </is>
       </c>
     </row>
@@ -16778,12 +16774,12 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>沒封表奏旭音乾隆固意毅勤為黎</t>
+          <t>掘剝達鍊廣東。 返孫士殼拱悉睦鄰</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Xưa sao vắng vẻ hơi tăm? Rầy sao hiệp lực đồng tâm lắm người?</t>
+          <t>Cử lời đạt đến Quảng Đông, Gặp Tôn Sĩ Nghị cũng lòng mục lân.</t>
         </is>
       </c>
     </row>
@@ -16795,12 +16791,12 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>蟲頌印紫泥挽軍眾省輕術沒稜</t>
+          <t>沒封表奏旭音乾隆固意毅勤為黎</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Viêm lương mới tỏ thói đời, Dạ trong đã chán, mặt ngoài cũng khinh.</t>
+          <t>Một phong biểu tấu chín lần, Càn Long có ý ân cần vì Lê.</t>
         </is>
       </c>
     </row>
@@ -16812,12 +16808,12 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>南開敞磊塘邊隱艾鬱諒鄉豈淹抹</t>
+          <t>蟲頌印紫泥挽軍眾省輕術沒稜</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Song mà ỷ thế nhà Thanh, Thờ ơ với kẻ nước mình mặc ai!</t>
+          <t>Đền rồng ban ấn tử nê, Đem quân bốn tỉnh trao về một tay.</t>
         </is>
       </c>
     </row>
@@ -16829,12 +16825,12 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>袁攻破寨內侯，曉塘京北細頭珥江</t>
+          <t>南開敞磊塘邊隱艾鬱諒鄉豈淹抹</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>Cơ mưu những chắc lưng người, Để cho đất nước trong ngoài mất trông!</t>
+          <t>Nam Quan thẳng lối đường mây, Tắt qua trấn Lạng, sang ngay sông Cầu.</t>
         </is>
       </c>
     </row>
@@ -16846,12 +16842,12 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>醃樓兇缶產床希黎幈覓逃塘牆兵</t>
+          <t>袁攻破寨內侯， 曉塘京北細頭珥江</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Quân Thanh đã được Thăng Long, Một hai rằng thế là xong việc mình.</t>
+          <t>Tập công phá trại Nội Hầu, Theo đường Kinh Bắc, tới đầu Nhị Giang.</t>
         </is>
       </c>
     </row>
@@ -16863,12 +16859,12 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>孫公軍令肅清，孫毫極犯就誠拱手</t>
+          <t>醃樓兇缶產床希黎幈覓逃塘牆兵</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>Dùng dằng chẳng chịu tiến binh, Nhác đường phòng thủ, mống tình đãi hoang.</t>
+          <t>Rượu trâu đâu đã sẵn sàng, Vua Lê mừng thấy đón đàng khao binh.</t>
         </is>
       </c>
     </row>
@@ -16880,12 +16876,12 @@
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>戈淹買北秣浮西竜軍挾東都御急</t>
+          <t>孫公軍令肅清， 孫毫極犯就誠拱手</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>Ngụy Tây nghe biết sơ phòng, Giả điều tạ tội quyết đường cất quân.</t>
+          <t>Tôn công quân lệnh túc thanh, Tơ hào chẳng phạm, tấm thành cũng phu.</t>
         </is>
       </c>
     </row>
@@ -16897,12 +16893,12 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>國王產印稫捭進隨賞飢功勞辱痾</t>
+          <t>戈淹買北秣浮西竜軍挾東都御急</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>Dặm tràng nào có ai ngăn, Thừa hư tiến bức đến gần Thăng Long.</t>
+          <t>Qua sông mới bắc cầu phù, Tây Luông quân đóng, Đông Đô ngự vào.</t>
         </is>
       </c>
     </row>
@@ -16914,12 +16910,12 @@
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>色醜豪傑賒斯撮醜調鍊闡軍拔燒</t>
+          <t>國王產印稫捭進隨賞飢功勞辱痾</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>Trực khu đến lũy Nam Đồng, Quan Thanh dẫu mấy anh hùng mà đang?</t>
+          <t>Quốc vương sẵn ấn tay trao, Truy tùy thưởng kẻ công lao nhọc nhằn.</t>
         </is>
       </c>
     </row>
@@ -16931,12 +16927,12 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>碧韞朱麾帝心副韞叫力同心穀影</t>
+          <t>色醜豪傑賒斯撮醜調鍊闡軍拔燒</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>Vua Lê khi ấy vội vàng, Cùng Tôn Sĩ Nghị sang đàng Bắc Kinh.</t>
+          <t>Bao nhiêu hào kiệt xa gần, Đua nhau đều đến cửa quân đầu thầm.</t>
         </is>
       </c>
     </row>
@@ -16948,12 +16944,12 @@
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>炎京買燻腿荳脆鈴奄懐麵外拱輕</t>
+          <t>碧韞朱麾帝心副韞叫力同心穀影</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Qua sông lại sợ truy binh, Phù kiều chém đứt, quân mình thác oan.</t>
+          <t>Xưa sao vắng vẻ hơi tăm? Rầy sao hiệp lực đồng tâm lắm người?</t>
         </is>
       </c>
     </row>
@@ -16965,12 +16961,12 @@
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>雙麻倚芳茄清嫌於貝饑滋騎默埃</t>
+          <t>炎京買燻腿荳脆鈴奄懐麵外拱輕</t>
         </is>
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Ngẩn ngơ đến ải Lạng Sơn, Theo sau còn có quân quan mấy người.</t>
+          <t>Viêm lương mới tỏ thói đời, Dạ trong đã chán, mặt ngoài cũng khinh.</t>
         </is>
       </c>
     </row>
@@ -16982,12 +16978,12 @@
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>机謀仍懶賤歇，抵朱坦諾鈍外壯翹</t>
+          <t>雙麻倚芳茄清嫌於貝饑滋騎默埃</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Cầm tay Sĩ Nghị than dài, Vì mình kiển bộ nên người luống công.</t>
+          <t>Song mà ỷ thế nhà Thanh, Thờ ơ với kẻ nước mình mặc ai!</t>
         </is>
       </c>
     </row>
@@ -16999,12 +16995,12 @@
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>軍清奄特昇竜没飄浪世界衡役騎</t>
+          <t>机謀仍懶賤歇， 抵朱坦諾鈍外壯翹</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>Nhẽ đâu lại dám bận lòng, Xin về đất cũ để mong tái đồ.</t>
+          <t>Cơ mưu những chắc lưng người, Để cho đất nước trong ngoài mất trông!</t>
         </is>
       </c>
     </row>
@@ -17016,12 +17012,12 @@
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>調驛挾鋋追兵，臨塘防守愜情怠荒</t>
+          <t>軍清奄特昇竜没飄浪世界衡役騎</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Tôn công cũng có tiên trù, Đã dâng một biểu xin cầu viện binh.</t>
+          <t>Quân Thanh đã được Thăng Long, Một hai rằng thế là xong việc mình.</t>
         </is>
       </c>
     </row>
@@ -17033,12 +17029,12 @@
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>偽西贖別疎防假調謝罪次壍拮軍</t>
+          <t>調驛挾鋋追兵， 臨塘防守愜情怠荒</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Quế Lâm còn tạm trú mình, Bỗng đâu nghe chiếu nhà Thanh triệu về.</t>
+          <t>Dùng dằng chẳng chịu tiến binh, Nhác đường phòng thủ, mống tình đãi hoang.</t>
         </is>
       </c>
     </row>
@@ -17050,12 +17046,12 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>毀長帝固垠埃乘虛進逼鋤斯異意</t>
+          <t>偽西贖別疎防假調謝罪次壍拮軍</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Phụng sai có sứ hộ tùy, Sự đâu lại gặp những bề trở nan.</t>
+          <t>Ngụy Tây nghe biết sơ phòng, Giả điều tạ tội quyết đường cất quân.</t>
         </is>
       </c>
     </row>
@@ -17067,12 +17063,12 @@
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>直驅強壘南同官清咄爾英雄當</t>
+          <t>毀長帝固垠埃乘虛進逼鋤斯異意</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Sứ thần là Phúc Khang An, Đã e xa cách, lại toan dối lừa.</t>
+          <t>Dặm tràng nào có ai ngăn, Thừa hư tiến bức đến gần Thăng Long.</t>
         </is>
       </c>
     </row>
@@ -17084,12 +17080,12 @@
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>希黎欺意倍鬱共孫士穀鄴塘北京</t>
+          <t>直驅強壘南同官清咄爾英雄當</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Dần dà ngày tháng thoi đưa, Lê hoàng luống những đợi chờ Yên Kinh.</t>
+          <t>Trực khu đến lũy Nam Đồng, Quan Thanh dẫu mấy anh hùng mà đang?</t>
         </is>
       </c>
     </row>
@@ -17101,12 +17097,12 @@
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>戈淹吏慄追兵浮橋卻搖軍官余歇</t>
+          <t>希黎欺意倍鬱共孫士穀鄴塘北京</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Tấc gang khôn tỏ sự tình, Dẽ xem con tạo giúp mình hay không?</t>
+          <t>Vua Lê khi ấy vội vàng, Cùng Tôn Sĩ Nghị sang đàng Bắc Kinh.</t>
         </is>
       </c>
     </row>
@@ -17118,12 +17114,12 @@
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>良魚鍊隘諒山魁嶽群固軍官余舉</t>
+          <t>戈淹吏慄追兵浮橋卻搖軍官余歇</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Từ khi tam phẩm gia phong, Mới hay Thanh đế cam lòng thế thôi.</t>
+          <t>Qua sông lại sợ truy binh, Phù kiều chém đứt, quân mình thác oan.</t>
         </is>
       </c>
     </row>
@@ -17135,12 +17131,12 @@
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>矜烈士戮嘆殲為觴蹇步鍼歇隱功</t>
+          <t>良魚鍊隘諒山魁嶽群固軍官余舉</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Lỡ làng đến bước xa xôi, Nhưng trong đạo chúa nghĩa tôi chẳng dời.</t>
+          <t>Ngẩn ngơ đến ải Lạng Sơn, Theo sau còn có quân quan mấy người.</t>
         </is>
       </c>
     </row>
@@ -17152,12 +17148,12 @@
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>銓亮吏戢綽恙賁術坦覩低懷再圖</t>
+          <t>矜烈士戮嘆殲為觴蹇步鍼歇隱功</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Lê Hân, Lê Quýnh mấy người, Như Tòng, Ích Hiểu cũng lời thệ minh.</t>
+          <t>Cầm tay Sĩ Nghị than dài, Vì mình kiển bộ nên người luống công.</t>
         </is>
       </c>
     </row>
@@ -17169,12 +17165,12 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>孫公拱固先籌，屯燈沒表嗔求援兵</t>
+          <t>銓亮吏戢綽恙賁術坦覩低懷再圖</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Tòng vong đều kẻ trung trinh, Mã đồng khen cũng có tình tôn quân.</t>
+          <t>Nhẽ đâu lại dám bận lòng, Xin về đất cũ để mong tái đồ.</t>
         </is>
       </c>
     </row>
@@ -17186,12 +17182,12 @@
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>桂林群曾駐翁侍兎蹤謐茹清召術</t>
+          <t>孫公拱固先籌，屯燈沒表嗔求援兵</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Vua Lê phút lánh cõi trần, Non sông cách diễn mấy lần xa xa.</t>
+          <t>Tôn công cũng có tiên trù, Đã dâng một biểu xin cầu viện binh.</t>
         </is>
       </c>
     </row>
@@ -17203,12 +17199,12 @@
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>奉差固使護隨事斃吏巡仍交阻難</t>
+          <t>桂林群曾駐翁侍兎蹤謐茹清召術</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>Bình Tây nhờ Thánh triều ta, Kẻ gần an chốn, người xa tìm về.</t>
+          <t>Quế Lâm còn tạm trú mình, Bỗng đâu nghe chiếu nhà Thanh triệu về.</t>
         </is>
       </c>
     </row>
@@ -17220,12 +17216,12 @@
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>使臣邪福康安乞哀賒隔吏算對聽</t>
+          <t>奉差固使護隨事斃吏巡仍交阻難</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Sang Thanh mấy kẻ theo Lê, Còn ai cũng động lòng quê ngậm ngùi.</t>
+          <t>Phụng sai có sứ hộ tùy, Sự đâu lại gặp những bề trở nan.</t>
         </is>
       </c>
     </row>
@@ -17237,12 +17233,12 @@
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>寅馳駕脅援迢黎皇隨仍待徐燕京</t>
+          <t>使臣邪福康安乞哀賒隔吏算對聽</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Vận Lê đến thế là thôi, Ba trăm sáu chục năm rồi còn chi?</t>
+          <t>Sứ thần là Phúc Khang An, Đã e xa cách, lại toan dối lừa.</t>
         </is>
       </c>
     </row>
@@ -17254,12 +17250,12 @@
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>粵粵坤臻事情巴袨猑造範翁能空</t>
+          <t>寅馳駕脅援迢黎皇隨仍待徐燕京</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Mới hay có thịnh, có suy, Hang sâu, núi cả có khi đổi dời.</t>
+          <t>Dần dà ngày tháng thoi đưa, Lê hoàng luống những đợi chờ Yên Kinh.</t>
         </is>
       </c>
     </row>
@@ -17271,12 +17267,12 @@
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>自欺三品加封買台清帝甘悉世催</t>
+          <t>粵粵坤臻事情巴袨猑造範翁能空</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>Trước sau tính lại trăm đời, Có trời, có đất, có người chủ trương.</t>
+          <t>Tấc gang khôn tỏ sự tình, Dẽ xem con tạo giúp mình hay không?</t>
         </is>
       </c>
     </row>
@@ -17288,12 +17284,12 @@
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>呂廓鍊趾賒斂仍蝕道主美碎極題</t>
+          <t>自欺三品加封買台清帝甘悉世催</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>Khai tiên là họ Hồng Bàng, Thục thay, Triệu đổi thường thường suy di.</t>
+          <t>Từ khi tam phẩm gia phong, Mới hay Thanh đế cam lòng thế thôi.</t>
         </is>
       </c>
     </row>
@@ -17305,12 +17301,12 @@
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>黎所黎個余歇如松藍號拱剝誓盟</t>
+          <t>呂廓鍊趾賒斂仍蝕道主美碎極題</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Rồi ra hợp hợp chia chia, Trải Đinh, Lê, Lý, Trần, Lê mấy đời.</t>
+          <t>Lỡ làng đến bước xa xôi, Nhưng trong đạo chúa nghĩa tôi chẳng dời.</t>
         </is>
       </c>
     </row>
@@ -17322,12 +17318,12 @@
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>從亡誦仇忠貞，馬童著拱固情尊君</t>
+          <t>黎所黎個余歇如松藍號拱剝誓盟</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>Thiếu chi chuyện vãn đầy vơi? Hiếm điều đắc thất, hiếm người thị phi?</t>
+          <t>Lê Hân, Lê Quýnh mấy người, Như Tòng, Ích Hiểu cũng lời thệ minh.</t>
         </is>
       </c>
     </row>
@@ -17339,12 +17335,12 @@
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>希黎，易埃塵。姦違隔演余咨縣縣</t>
+          <t>從亡誦仇忠貞，馬童著拱固情尊君</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Lại còn nhiều việc tín nghi, Sự muôn năm cũ chép ghi rành rành.</t>
+          <t>Tòng vong đều kẻ trung trinh, Mã đồng khen cũng có tình tôn quân.</t>
         </is>
       </c>
     </row>
@@ -17356,12 +17352,29 @@
       </c>
       <c r="B997" t="inlineStr">
         <is>
+          <t>希黎，易埃塵。姦違隔演余咨縣縣</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Vua Lê phút lánh cõi trần, Non sông cách diễn mấy lần xa xa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>HVB_004_0996</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
           <t>平西恢聖朝些飢斯安惟馭賒尋術</t>
         </is>
       </c>
-      <c r="C997" t="inlineStr">
-        <is>
-          <t>Bút son vàng mệnh đan đình, Gác Lê lần giở sử xanh muôn đời.</t>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Bình Tây nhờ Thánh triều ta, Kẻ gần an chốn, người xa tìm về.</t>
         </is>
       </c>
     </row>
